--- a/artfynd/A 3110-2025 artfynd.xlsx
+++ b/artfynd/A 3110-2025 artfynd.xlsx
@@ -2599,10 +2599,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122733126</v>
+        <v>122729831</v>
       </c>
       <c r="B20" t="n">
-        <v>78762</v>
+        <v>57478</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2615,34 +2615,39 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Stamåsen, Stamåsen, Ång</t>
+          <t>Lill-Åsberget, Lill-Åsberget, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>541858</v>
+        <v>542249</v>
       </c>
       <c r="R20" t="n">
-        <v>7063338</v>
+        <v>7063942</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2675,6 +2680,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-02-24</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Bohål i torrgran, 2m ovan mark. 5 cm ø. Gott om stående död ved i området.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2701,10 +2711,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122741861</v>
+        <v>122733126</v>
       </c>
       <c r="B21" t="n">
-        <v>79843</v>
+        <v>78762</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2717,34 +2727,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Lill-Åsberget, Lill-Åsberget, Ång</t>
+          <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>542085</v>
+        <v>541858</v>
       </c>
       <c r="R21" t="n">
-        <v>7063858</v>
+        <v>7063338</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2803,10 +2813,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122729831</v>
+        <v>122730759</v>
       </c>
       <c r="B22" t="n">
-        <v>57478</v>
+        <v>91300</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2815,43 +2825,38 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>1506</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Lill-Åsberget, Lill-Åsberget, Ång</t>
+          <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>542249</v>
+        <v>542045</v>
       </c>
       <c r="R22" t="n">
-        <v>7063942</v>
+        <v>7063823</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2884,11 +2889,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-02-24</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Bohål i torrgran, 2m ovan mark. 5 cm ø. Gott om stående död ved i området.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2915,10 +2915,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122730759</v>
+        <v>122741861</v>
       </c>
       <c r="B23" t="n">
-        <v>91300</v>
+        <v>79843</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2927,38 +2927,38 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1506</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Stamåsen, Stamåsen, Ång</t>
+          <t>Lill-Åsberget, Lill-Åsberget, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>542045</v>
+        <v>542085</v>
       </c>
       <c r="R23" t="n">
-        <v>7063823</v>
+        <v>7063858</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -4353,10 +4353,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122741488</v>
+        <v>122730004</v>
       </c>
       <c r="B37" t="n">
-        <v>57494</v>
+        <v>90954</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4369,39 +4369,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100049</v>
+        <v>1204</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Stamåsen, Stamåsen, Ång</t>
+          <t>Lill-Åsberget, Lill-Åsberget, Ång</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>542034</v>
+        <v>542251</v>
       </c>
       <c r="R37" t="n">
-        <v>7063681</v>
+        <v>7063915</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4460,10 +4455,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122730004</v>
+        <v>122741488</v>
       </c>
       <c r="B38" t="n">
-        <v>90954</v>
+        <v>57494</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4476,34 +4471,39 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1204</v>
+        <v>100049</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Lill-Åsberget, Lill-Åsberget, Ång</t>
+          <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>542251</v>
+        <v>542034</v>
       </c>
       <c r="R38" t="n">
-        <v>7063915</v>
+        <v>7063681</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>

--- a/artfynd/A 3110-2025 artfynd.xlsx
+++ b/artfynd/A 3110-2025 artfynd.xlsx
@@ -1350,10 +1350,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122731904</v>
+        <v>122733041</v>
       </c>
       <c r="B8" t="n">
-        <v>78762</v>
+        <v>90962</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1366,21 +1366,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1390,10 +1390,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>541908</v>
+        <v>541873</v>
       </c>
       <c r="R8" t="n">
-        <v>7063682</v>
+        <v>7063379</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1426,11 +1426,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-02-24</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Garnlavsrika partier över hela sluttningen</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1457,10 +1452,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122731014</v>
+        <v>122731166</v>
       </c>
       <c r="B9" t="n">
-        <v>79843</v>
+        <v>90962</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1473,21 +1468,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1497,10 +1492,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>541940</v>
+        <v>541922</v>
       </c>
       <c r="R9" t="n">
-        <v>7063713</v>
+        <v>7063717</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1559,10 +1554,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122732657</v>
+        <v>122732558</v>
       </c>
       <c r="B10" t="n">
-        <v>90905</v>
+        <v>97315</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1575,21 +1570,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5447</v>
+        <v>221941</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1599,10 +1594,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>541761</v>
+        <v>541824</v>
       </c>
       <c r="R10" t="n">
-        <v>7063583</v>
+        <v>7063603</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1661,10 +1656,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122741781</v>
+        <v>122741376</v>
       </c>
       <c r="B11" t="n">
-        <v>91289</v>
+        <v>91235</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1673,25 +1668,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2062</v>
+        <v>658</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1701,10 +1696,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>542068</v>
+        <v>541997</v>
       </c>
       <c r="R11" t="n">
-        <v>7063778</v>
+        <v>7063580</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1763,10 +1758,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122732264</v>
+        <v>122730004</v>
       </c>
       <c r="B12" t="n">
-        <v>82549</v>
+        <v>90958</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1779,34 +1774,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1312</v>
+        <v>1204</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Stamåsen, Stamåsen, Ång</t>
+          <t>Lill-Åsberget, Lill-Åsberget, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>541883</v>
+        <v>542251</v>
       </c>
       <c r="R12" t="n">
-        <v>7063653</v>
+        <v>7063915</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1865,10 +1860,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122741643</v>
+        <v>122741488</v>
       </c>
       <c r="B13" t="n">
-        <v>56680</v>
+        <v>57494</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1881,16 +1876,16 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>102612</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1901,7 +1896,7 @@
       <c r="I13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1910,10 +1905,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>542064</v>
+        <v>542034</v>
       </c>
       <c r="R13" t="n">
-        <v>7063749</v>
+        <v>7063681</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1972,10 +1967,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122730595</v>
+        <v>122729831</v>
       </c>
       <c r="B14" t="n">
-        <v>90940</v>
+        <v>57478</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1988,34 +1983,39 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Stamåsen, Stamåsen, Ång</t>
+          <t>Lill-Åsberget, Lill-Åsberget, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>542097</v>
+        <v>542249</v>
       </c>
       <c r="R14" t="n">
-        <v>7063815</v>
+        <v>7063942</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2048,6 +2048,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-02-24</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Bohål i torrgran, 2m ovan mark. 5 cm ø. Gott om stående död ved i området.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2074,10 +2079,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122731193</v>
+        <v>122732631</v>
       </c>
       <c r="B15" t="n">
-        <v>91338</v>
+        <v>88303</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2090,16 +2095,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6040186</v>
+        <v>510</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Doftskinn</t>
+        </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2109,10 +2119,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>541919</v>
+        <v>541768</v>
       </c>
       <c r="R15" t="n">
-        <v>7063716</v>
+        <v>7063586</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2171,10 +2181,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122730177</v>
+        <v>122741513</v>
       </c>
       <c r="B16" t="n">
-        <v>56688</v>
+        <v>90944</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2183,43 +2193,38 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100138</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Lill-Åsberget, Lill-Åsberget, Ång</t>
+          <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>542198</v>
+        <v>542030</v>
       </c>
       <c r="R16" t="n">
-        <v>7063872</v>
+        <v>7063685</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2278,10 +2283,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122730426</v>
+        <v>122732958</v>
       </c>
       <c r="B17" t="n">
-        <v>56680</v>
+        <v>57478</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2294,16 +2299,16 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>102612</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -2314,19 +2319,19 @@
       <c r="I17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Lill-Åsberget, Lill-Åsberget, Ång</t>
+          <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>542150</v>
+        <v>541820</v>
       </c>
       <c r="R17" t="n">
-        <v>7063805</v>
+        <v>7063439</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2359,6 +2364,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-02-24</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Äldre ringhack, &gt;200-årig tall</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2385,10 +2395,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122742207</v>
+        <v>122741781</v>
       </c>
       <c r="B18" t="n">
-        <v>90958</v>
+        <v>91293</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2397,38 +2407,38 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5432</v>
+        <v>2062</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Lill-Åsberget, Lill-Åsberget, Ång</t>
+          <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>542238</v>
+        <v>542068</v>
       </c>
       <c r="R18" t="n">
-        <v>7063973</v>
+        <v>7063778</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2487,10 +2497,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122732958</v>
+        <v>122730829</v>
       </c>
       <c r="B19" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2503,39 +2513,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>541820</v>
+        <v>542035</v>
       </c>
       <c r="R19" t="n">
-        <v>7063439</v>
+        <v>7063816</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2568,11 +2573,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-02-24</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Äldre ringhack, &gt;200-årig tall</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2599,10 +2599,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122729831</v>
+        <v>122733126</v>
       </c>
       <c r="B20" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2615,39 +2615,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Lill-Åsberget, Lill-Åsberget, Ång</t>
+          <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>542249</v>
+        <v>541858</v>
       </c>
       <c r="R20" t="n">
-        <v>7063942</v>
+        <v>7063338</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2680,11 +2675,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-02-24</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Bohål i torrgran, 2m ovan mark. 5 cm ø. Gott om stående död ved i området.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2711,10 +2701,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122733126</v>
+        <v>122730042</v>
       </c>
       <c r="B21" t="n">
-        <v>78762</v>
+        <v>91235</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2727,34 +2717,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Stamåsen, Stamåsen, Ång</t>
+          <t>Lill-Åsberget, Lill-Åsberget, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>541858</v>
+        <v>542248</v>
       </c>
       <c r="R21" t="n">
-        <v>7063338</v>
+        <v>7063927</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2816,7 +2806,7 @@
         <v>122730759</v>
       </c>
       <c r="B22" t="n">
-        <v>91300</v>
+        <v>91304</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2915,10 +2905,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122741861</v>
+        <v>122731109</v>
       </c>
       <c r="B23" t="n">
-        <v>79843</v>
+        <v>57478</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2931,34 +2921,39 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Lill-Åsberget, Lill-Åsberget, Ång</t>
+          <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>542085</v>
+        <v>541940</v>
       </c>
       <c r="R23" t="n">
-        <v>7063858</v>
+        <v>7063712</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -2991,6 +2986,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-02-24</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Äldre ringhack, gammal tall</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3017,10 +3017,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122732817</v>
+        <v>122741861</v>
       </c>
       <c r="B24" t="n">
-        <v>56680</v>
+        <v>79847</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3033,39 +3033,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>102612</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Stamåsen, Stamåsen, Ång</t>
+          <t>Lill-Åsberget, Lill-Åsberget, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>541803</v>
+        <v>542085</v>
       </c>
       <c r="R24" t="n">
-        <v>7063479</v>
+        <v>7063858</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3124,10 +3119,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122730246</v>
+        <v>122730086</v>
       </c>
       <c r="B25" t="n">
-        <v>78762</v>
+        <v>90944</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3140,21 +3135,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3164,10 +3159,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>542168</v>
+        <v>542258</v>
       </c>
       <c r="R25" t="n">
-        <v>7063849</v>
+        <v>7063917</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3226,10 +3221,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122730086</v>
+        <v>122732653</v>
       </c>
       <c r="B26" t="n">
-        <v>90940</v>
+        <v>90958</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3242,34 +3237,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1202</v>
+        <v>1204</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Lill-Åsberget, Lill-Åsberget, Ång</t>
+          <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>542258</v>
+        <v>541760</v>
       </c>
       <c r="R26" t="n">
-        <v>7063917</v>
+        <v>7063584</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3328,10 +3323,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122732330</v>
+        <v>122731904</v>
       </c>
       <c r="B27" t="n">
-        <v>90905</v>
+        <v>78766</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3340,25 +3335,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3368,10 +3363,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>541875</v>
+        <v>541908</v>
       </c>
       <c r="R27" t="n">
-        <v>7063622</v>
+        <v>7063682</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3404,6 +3399,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-02-24</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Garnlavsrika partier över hela sluttningen</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3430,10 +3430,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122731166</v>
+        <v>122741643</v>
       </c>
       <c r="B28" t="n">
-        <v>90958</v>
+        <v>56680</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3446,34 +3446,39 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5432</v>
+        <v>102612</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>541922</v>
+        <v>542064</v>
       </c>
       <c r="R28" t="n">
-        <v>7063717</v>
+        <v>7063749</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3532,10 +3537,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122732558</v>
+        <v>122730426</v>
       </c>
       <c r="B29" t="n">
-        <v>97307</v>
+        <v>56680</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3544,38 +3549,43 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>221941</v>
+        <v>102612</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Stamåsen, Stamåsen, Ång</t>
+          <t>Lill-Åsberget, Lill-Åsberget, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>541824</v>
+        <v>542150</v>
       </c>
       <c r="R29" t="n">
-        <v>7063603</v>
+        <v>7063805</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3634,10 +3644,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122732584</v>
+        <v>122730595</v>
       </c>
       <c r="B30" t="n">
-        <v>97301</v>
+        <v>90944</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3646,25 +3656,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>221945</v>
+        <v>1202</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3674,10 +3684,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>541821</v>
+        <v>542097</v>
       </c>
       <c r="R30" t="n">
-        <v>7063616</v>
+        <v>7063815</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3736,10 +3746,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122732487</v>
+        <v>122732584</v>
       </c>
       <c r="B31" t="n">
-        <v>90940</v>
+        <v>97309</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3748,25 +3758,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1202</v>
+        <v>221945</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3776,10 +3786,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>541847</v>
+        <v>541821</v>
       </c>
       <c r="R31" t="n">
-        <v>7063615</v>
+        <v>7063616</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3838,10 +3848,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122730499</v>
+        <v>122732657</v>
       </c>
       <c r="B32" t="n">
-        <v>78762</v>
+        <v>90909</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3850,38 +3860,38 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Lill-Åsberget, Lill-Åsberget, Ång</t>
+          <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>542132</v>
+        <v>541761</v>
       </c>
       <c r="R32" t="n">
-        <v>7063797</v>
+        <v>7063583</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3940,10 +3950,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122741513</v>
+        <v>122730499</v>
       </c>
       <c r="B33" t="n">
-        <v>90940</v>
+        <v>78766</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3956,34 +3966,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Stamåsen, Stamåsen, Ång</t>
+          <t>Lill-Åsberget, Lill-Åsberget, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>542030</v>
+        <v>542132</v>
       </c>
       <c r="R33" t="n">
-        <v>7063685</v>
+        <v>7063797</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -4042,10 +4052,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122741763</v>
+        <v>122731014</v>
       </c>
       <c r="B34" t="n">
-        <v>90940</v>
+        <v>79847</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4058,21 +4068,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4082,10 +4092,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>542067</v>
+        <v>541940</v>
       </c>
       <c r="R34" t="n">
-        <v>7063777</v>
+        <v>7063713</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4144,10 +4154,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122730234</v>
+        <v>122731193</v>
       </c>
       <c r="B35" t="n">
-        <v>79843</v>
+        <v>91342</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4160,34 +4170,29 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6458</v>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>Lunglav</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Lill-Åsberget, Lill-Åsberget, Ång</t>
+          <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>542187</v>
+        <v>541919</v>
       </c>
       <c r="R35" t="n">
-        <v>7063885</v>
+        <v>7063716</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4246,10 +4251,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122741691</v>
+        <v>122742207</v>
       </c>
       <c r="B36" t="n">
-        <v>56680</v>
+        <v>90962</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4262,39 +4267,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>102612</v>
+        <v>5432</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Stamåsen, Stamåsen, Ång</t>
+          <t>Lill-Åsberget, Lill-Åsberget, Ång</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>542063</v>
+        <v>542238</v>
       </c>
       <c r="R36" t="n">
-        <v>7063786</v>
+        <v>7063973</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4353,10 +4353,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122730004</v>
+        <v>122732487</v>
       </c>
       <c r="B37" t="n">
-        <v>90954</v>
+        <v>90944</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4369,34 +4369,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1204</v>
+        <v>1202</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Lill-Åsberget, Lill-Åsberget, Ång</t>
+          <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>542251</v>
+        <v>541847</v>
       </c>
       <c r="R37" t="n">
-        <v>7063915</v>
+        <v>7063615</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4455,10 +4455,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122741488</v>
+        <v>122732817</v>
       </c>
       <c r="B38" t="n">
-        <v>57494</v>
+        <v>56680</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4471,16 +4471,16 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100049</v>
+        <v>102612</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -4491,7 +4491,7 @@
       <c r="I38" t="inlineStr"/>
       <c r="M38" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
@@ -4500,10 +4500,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>542034</v>
+        <v>541803</v>
       </c>
       <c r="R38" t="n">
-        <v>7063681</v>
+        <v>7063479</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4562,10 +4562,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122730829</v>
+        <v>122730177</v>
       </c>
       <c r="B39" t="n">
-        <v>78762</v>
+        <v>56688</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4574,38 +4574,43 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Stamåsen, Stamåsen, Ång</t>
+          <t>Lill-Åsberget, Lill-Åsberget, Ång</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>542035</v>
+        <v>542198</v>
       </c>
       <c r="R39" t="n">
-        <v>7063816</v>
+        <v>7063872</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -4664,10 +4669,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122733041</v>
+        <v>122732330</v>
       </c>
       <c r="B40" t="n">
-        <v>90958</v>
+        <v>90909</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4676,25 +4681,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5432</v>
+        <v>5447</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4704,10 +4709,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>541873</v>
+        <v>541875</v>
       </c>
       <c r="R40" t="n">
-        <v>7063379</v>
+        <v>7063622</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -4766,10 +4771,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122741741</v>
+        <v>122732264</v>
       </c>
       <c r="B41" t="n">
-        <v>90905</v>
+        <v>82553</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4778,25 +4783,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>5447</v>
+        <v>1312</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4806,10 +4811,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>542064</v>
+        <v>541883</v>
       </c>
       <c r="R41" t="n">
-        <v>7063777</v>
+        <v>7063653</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -4868,10 +4873,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122730042</v>
+        <v>122741691</v>
       </c>
       <c r="B42" t="n">
-        <v>91231</v>
+        <v>56680</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4884,34 +4889,39 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>658</v>
+        <v>102612</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Lill-Åsberget, Lill-Åsberget, Ång</t>
+          <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>542248</v>
+        <v>542063</v>
       </c>
       <c r="R42" t="n">
-        <v>7063927</v>
+        <v>7063786</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -4970,10 +4980,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122732653</v>
+        <v>122741763</v>
       </c>
       <c r="B43" t="n">
-        <v>90954</v>
+        <v>90944</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4986,21 +4996,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1204</v>
+        <v>1202</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5010,10 +5020,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>541760</v>
+        <v>542067</v>
       </c>
       <c r="R43" t="n">
-        <v>7063584</v>
+        <v>7063777</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -5072,10 +5082,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122731109</v>
+        <v>122730234</v>
       </c>
       <c r="B44" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5088,39 +5098,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Stamåsen, Stamåsen, Ång</t>
+          <t>Lill-Åsberget, Lill-Åsberget, Ång</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>541940</v>
+        <v>542187</v>
       </c>
       <c r="R44" t="n">
-        <v>7063712</v>
+        <v>7063885</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>
@@ -5153,11 +5158,6 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-02-24</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Äldre ringhack, gammal tall</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5184,10 +5184,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122732631</v>
+        <v>122730246</v>
       </c>
       <c r="B45" t="n">
-        <v>88299</v>
+        <v>78766</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5200,34 +5200,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>510</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Stamåsen, Stamåsen, Ång</t>
+          <t>Lill-Åsberget, Lill-Åsberget, Ång</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>541768</v>
+        <v>542168</v>
       </c>
       <c r="R45" t="n">
-        <v>7063586</v>
+        <v>7063849</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -5286,10 +5286,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122741376</v>
+        <v>122741741</v>
       </c>
       <c r="B46" t="n">
-        <v>91231</v>
+        <v>90909</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5298,25 +5298,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>658</v>
+        <v>5447</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5326,10 +5326,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>541997</v>
+        <v>542064</v>
       </c>
       <c r="R46" t="n">
-        <v>7063580</v>
+        <v>7063777</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>

--- a/artfynd/A 3110-2025 artfynd.xlsx
+++ b/artfynd/A 3110-2025 artfynd.xlsx
@@ -3221,10 +3221,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122732653</v>
+        <v>122741643</v>
       </c>
       <c r="B26" t="n">
-        <v>90958</v>
+        <v>56680</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3237,34 +3237,39 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1204</v>
+        <v>102612</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>541760</v>
+        <v>542064</v>
       </c>
       <c r="R26" t="n">
-        <v>7063584</v>
+        <v>7063749</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3430,10 +3435,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122741643</v>
+        <v>122732653</v>
       </c>
       <c r="B28" t="n">
-        <v>56680</v>
+        <v>90958</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3446,39 +3451,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>102612</v>
+        <v>1204</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>542064</v>
+        <v>541760</v>
       </c>
       <c r="R28" t="n">
-        <v>7063749</v>
+        <v>7063584</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3746,10 +3746,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122732584</v>
+        <v>122730499</v>
       </c>
       <c r="B31" t="n">
-        <v>97309</v>
+        <v>78766</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3758,38 +3758,38 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Stamåsen, Stamåsen, Ång</t>
+          <t>Lill-Åsberget, Lill-Åsberget, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>541821</v>
+        <v>542132</v>
       </c>
       <c r="R31" t="n">
-        <v>7063616</v>
+        <v>7063797</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3848,10 +3848,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122732657</v>
+        <v>122732584</v>
       </c>
       <c r="B32" t="n">
-        <v>90909</v>
+        <v>97309</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3864,21 +3864,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5447</v>
+        <v>221945</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3888,10 +3888,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>541761</v>
+        <v>541821</v>
       </c>
       <c r="R32" t="n">
-        <v>7063583</v>
+        <v>7063616</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3950,10 +3950,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122730499</v>
+        <v>122732657</v>
       </c>
       <c r="B33" t="n">
-        <v>78766</v>
+        <v>90909</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3962,38 +3962,38 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Lill-Åsberget, Lill-Åsberget, Ång</t>
+          <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>542132</v>
+        <v>541761</v>
       </c>
       <c r="R33" t="n">
-        <v>7063797</v>
+        <v>7063583</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>

--- a/artfynd/A 3110-2025 artfynd.xlsx
+++ b/artfynd/A 3110-2025 artfynd.xlsx
@@ -1350,10 +1350,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122733041</v>
+        <v>122731193</v>
       </c>
       <c r="B8" t="n">
-        <v>90962</v>
+        <v>91342</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1366,21 +1366,16 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Granticka</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1390,10 +1385,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>541873</v>
+        <v>541919</v>
       </c>
       <c r="R8" t="n">
-        <v>7063379</v>
+        <v>7063716</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1452,10 +1447,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122731166</v>
+        <v>122732558</v>
       </c>
       <c r="B9" t="n">
-        <v>90962</v>
+        <v>97315</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1464,25 +1459,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>221941</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1492,10 +1487,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>541922</v>
+        <v>541824</v>
       </c>
       <c r="R9" t="n">
-        <v>7063717</v>
+        <v>7063603</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1554,10 +1549,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122732558</v>
+        <v>122732264</v>
       </c>
       <c r="B10" t="n">
-        <v>97315</v>
+        <v>82553</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1566,25 +1561,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221941</v>
+        <v>1312</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1594,10 +1589,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>541824</v>
+        <v>541883</v>
       </c>
       <c r="R10" t="n">
-        <v>7063603</v>
+        <v>7063653</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1656,10 +1651,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122741376</v>
+        <v>122732817</v>
       </c>
       <c r="B11" t="n">
-        <v>91235</v>
+        <v>56680</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1672,34 +1667,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>658</v>
+        <v>102612</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>541997</v>
+        <v>541803</v>
       </c>
       <c r="R11" t="n">
-        <v>7063580</v>
+        <v>7063479</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1758,10 +1758,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122730004</v>
+        <v>122730759</v>
       </c>
       <c r="B12" t="n">
-        <v>90958</v>
+        <v>91304</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1770,38 +1770,38 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1204</v>
+        <v>1506</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Lill-Åsberget, Lill-Åsberget, Ång</t>
+          <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>542251</v>
+        <v>542045</v>
       </c>
       <c r="R12" t="n">
-        <v>7063915</v>
+        <v>7063823</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1860,10 +1860,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122741488</v>
+        <v>122741691</v>
       </c>
       <c r="B13" t="n">
-        <v>57494</v>
+        <v>56680</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1876,16 +1876,16 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>102612</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1896,7 +1896,7 @@
       <c r="I13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1905,10 +1905,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>542034</v>
+        <v>542063</v>
       </c>
       <c r="R13" t="n">
-        <v>7063681</v>
+        <v>7063786</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1967,10 +1967,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122729831</v>
+        <v>122732330</v>
       </c>
       <c r="B14" t="n">
-        <v>57478</v>
+        <v>90909</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1979,43 +1979,38 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Lill-Åsberget, Lill-Åsberget, Ång</t>
+          <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>542249</v>
+        <v>541875</v>
       </c>
       <c r="R14" t="n">
-        <v>7063942</v>
+        <v>7063622</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2048,11 +2043,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-02-24</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Bohål i torrgran, 2m ovan mark. 5 cm ø. Gott om stående död ved i området.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2079,10 +2069,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122732631</v>
+        <v>122730004</v>
       </c>
       <c r="B15" t="n">
-        <v>88303</v>
+        <v>90958</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2095,34 +2085,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>510</v>
+        <v>1204</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Stamåsen, Stamåsen, Ång</t>
+          <t>Lill-Åsberget, Lill-Åsberget, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>541768</v>
+        <v>542251</v>
       </c>
       <c r="R15" t="n">
-        <v>7063586</v>
+        <v>7063915</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2181,7 +2171,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122741513</v>
+        <v>122730086</v>
       </c>
       <c r="B16" t="n">
         <v>90944</v>
@@ -2217,14 +2207,14 @@
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Stamåsen, Stamåsen, Ång</t>
+          <t>Lill-Åsberget, Lill-Åsberget, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>542030</v>
+        <v>542258</v>
       </c>
       <c r="R16" t="n">
-        <v>7063685</v>
+        <v>7063917</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2283,10 +2273,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122732958</v>
+        <v>122741376</v>
       </c>
       <c r="B17" t="n">
-        <v>57478</v>
+        <v>91235</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2299,39 +2289,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>541820</v>
+        <v>541997</v>
       </c>
       <c r="R17" t="n">
-        <v>7063439</v>
+        <v>7063580</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2364,11 +2349,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-02-24</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Äldre ringhack, &gt;200-årig tall</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2395,10 +2375,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122741781</v>
+        <v>122731166</v>
       </c>
       <c r="B18" t="n">
-        <v>91293</v>
+        <v>90962</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2407,25 +2387,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2062</v>
+        <v>5432</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2435,10 +2415,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>542068</v>
+        <v>541922</v>
       </c>
       <c r="R18" t="n">
-        <v>7063778</v>
+        <v>7063717</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2497,10 +2477,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122730829</v>
+        <v>122733041</v>
       </c>
       <c r="B19" t="n">
-        <v>78766</v>
+        <v>90962</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2513,21 +2493,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2537,10 +2517,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>542035</v>
+        <v>541873</v>
       </c>
       <c r="R19" t="n">
-        <v>7063816</v>
+        <v>7063379</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2599,10 +2579,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122733126</v>
+        <v>122732657</v>
       </c>
       <c r="B20" t="n">
-        <v>78766</v>
+        <v>90909</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2611,25 +2591,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2639,10 +2619,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>541858</v>
+        <v>541761</v>
       </c>
       <c r="R20" t="n">
-        <v>7063338</v>
+        <v>7063583</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2701,10 +2681,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122730042</v>
+        <v>122732487</v>
       </c>
       <c r="B21" t="n">
-        <v>91235</v>
+        <v>90944</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2717,34 +2697,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Lill-Åsberget, Lill-Åsberget, Ång</t>
+          <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>542248</v>
+        <v>541847</v>
       </c>
       <c r="R21" t="n">
-        <v>7063927</v>
+        <v>7063615</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2803,10 +2783,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122730759</v>
+        <v>122730595</v>
       </c>
       <c r="B22" t="n">
-        <v>91304</v>
+        <v>90944</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2815,25 +2795,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1506</v>
+        <v>1202</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2843,10 +2823,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>542045</v>
+        <v>542097</v>
       </c>
       <c r="R22" t="n">
-        <v>7063823</v>
+        <v>7063815</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2905,10 +2885,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122731109</v>
+        <v>122732631</v>
       </c>
       <c r="B23" t="n">
-        <v>57478</v>
+        <v>88303</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2921,39 +2901,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>510</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>541940</v>
+        <v>541768</v>
       </c>
       <c r="R23" t="n">
-        <v>7063712</v>
+        <v>7063586</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -2986,11 +2961,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-02-24</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Äldre ringhack, gammal tall</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3017,10 +2987,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122741861</v>
+        <v>122741763</v>
       </c>
       <c r="B24" t="n">
-        <v>79847</v>
+        <v>90944</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3033,34 +3003,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Lill-Åsberget, Lill-Åsberget, Ång</t>
+          <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>542085</v>
+        <v>542067</v>
       </c>
       <c r="R24" t="n">
-        <v>7063858</v>
+        <v>7063777</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3119,10 +3089,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122730086</v>
+        <v>122730234</v>
       </c>
       <c r="B25" t="n">
-        <v>90944</v>
+        <v>79847</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3135,21 +3105,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3159,10 +3129,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>542258</v>
+        <v>542187</v>
       </c>
       <c r="R25" t="n">
-        <v>7063917</v>
+        <v>7063885</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3221,10 +3191,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122741643</v>
+        <v>122731014</v>
       </c>
       <c r="B26" t="n">
-        <v>56680</v>
+        <v>79847</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3237,39 +3207,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>102612</v>
+        <v>6458</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>542064</v>
+        <v>541940</v>
       </c>
       <c r="R26" t="n">
-        <v>7063749</v>
+        <v>7063713</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3328,7 +3293,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122731904</v>
+        <v>122733126</v>
       </c>
       <c r="B27" t="n">
         <v>78766</v>
@@ -3368,10 +3333,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>541908</v>
+        <v>541858</v>
       </c>
       <c r="R27" t="n">
-        <v>7063682</v>
+        <v>7063338</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3404,11 +3369,6 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2025-02-24</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Garnlavsrika partier över hela sluttningen</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3435,10 +3395,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122732653</v>
+        <v>122731904</v>
       </c>
       <c r="B28" t="n">
-        <v>90958</v>
+        <v>78766</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3451,21 +3411,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3475,10 +3435,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>541760</v>
+        <v>541908</v>
       </c>
       <c r="R28" t="n">
-        <v>7063584</v>
+        <v>7063682</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3511,6 +3471,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-02-24</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Garnlavsrika partier över hela sluttningen</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3537,10 +3502,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122730426</v>
+        <v>122741861</v>
       </c>
       <c r="B29" t="n">
-        <v>56680</v>
+        <v>79847</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3553,39 +3518,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>102612</v>
+        <v>6458</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Lill-Åsberget, Lill-Åsberget, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>542150</v>
+        <v>542085</v>
       </c>
       <c r="R29" t="n">
-        <v>7063805</v>
+        <v>7063858</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3644,10 +3604,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122730595</v>
+        <v>122729831</v>
       </c>
       <c r="B30" t="n">
-        <v>90944</v>
+        <v>57478</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3660,34 +3620,39 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Stamåsen, Stamåsen, Ång</t>
+          <t>Lill-Åsberget, Lill-Åsberget, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>542097</v>
+        <v>542249</v>
       </c>
       <c r="R30" t="n">
-        <v>7063815</v>
+        <v>7063942</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3720,6 +3685,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-02-24</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Bohål i torrgran, 2m ovan mark. 5 cm ø. Gott om stående död ved i området.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3746,10 +3716,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122730499</v>
+        <v>122741488</v>
       </c>
       <c r="B31" t="n">
-        <v>78766</v>
+        <v>57494</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3762,34 +3732,39 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Lill-Åsberget, Lill-Åsberget, Ång</t>
+          <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>542132</v>
+        <v>542034</v>
       </c>
       <c r="R31" t="n">
-        <v>7063797</v>
+        <v>7063681</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3848,10 +3823,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122732584</v>
+        <v>122741513</v>
       </c>
       <c r="B32" t="n">
-        <v>97309</v>
+        <v>90944</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3860,25 +3835,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>221945</v>
+        <v>1202</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3888,10 +3863,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>541821</v>
+        <v>542030</v>
       </c>
       <c r="R32" t="n">
-        <v>7063616</v>
+        <v>7063685</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3950,10 +3925,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122732657</v>
+        <v>122730042</v>
       </c>
       <c r="B33" t="n">
-        <v>90909</v>
+        <v>91235</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3962,38 +3937,38 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5447</v>
+        <v>658</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Stamåsen, Stamåsen, Ång</t>
+          <t>Lill-Åsberget, Lill-Åsberget, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>541761</v>
+        <v>542248</v>
       </c>
       <c r="R33" t="n">
-        <v>7063583</v>
+        <v>7063927</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -4052,10 +4027,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122731014</v>
+        <v>122732584</v>
       </c>
       <c r="B34" t="n">
-        <v>79847</v>
+        <v>97309</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4064,25 +4039,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6458</v>
+        <v>221945</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4092,10 +4067,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>541940</v>
+        <v>541821</v>
       </c>
       <c r="R34" t="n">
-        <v>7063713</v>
+        <v>7063616</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4154,10 +4129,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122731193</v>
+        <v>122730829</v>
       </c>
       <c r="B35" t="n">
-        <v>91342</v>
+        <v>78766</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4170,16 +4145,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6040186</v>
+        <v>6425</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4189,10 +4169,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>541919</v>
+        <v>542035</v>
       </c>
       <c r="R35" t="n">
-        <v>7063716</v>
+        <v>7063816</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4251,10 +4231,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122742207</v>
+        <v>122732958</v>
       </c>
       <c r="B36" t="n">
-        <v>90962</v>
+        <v>57478</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4267,34 +4247,39 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Lill-Åsberget, Lill-Åsberget, Ång</t>
+          <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>542238</v>
+        <v>541820</v>
       </c>
       <c r="R36" t="n">
-        <v>7063973</v>
+        <v>7063439</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4327,6 +4312,11 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-02-24</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Äldre ringhack, &gt;200-årig tall</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4353,10 +4343,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122732487</v>
+        <v>122742207</v>
       </c>
       <c r="B37" t="n">
-        <v>90944</v>
+        <v>90962</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4369,34 +4359,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Stamåsen, Stamåsen, Ång</t>
+          <t>Lill-Åsberget, Lill-Åsberget, Ång</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>541847</v>
+        <v>542238</v>
       </c>
       <c r="R37" t="n">
-        <v>7063615</v>
+        <v>7063973</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4455,10 +4445,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122732817</v>
+        <v>122741781</v>
       </c>
       <c r="B38" t="n">
-        <v>56680</v>
+        <v>91293</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4467,43 +4457,38 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>102612</v>
+        <v>2062</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>541803</v>
+        <v>542068</v>
       </c>
       <c r="R38" t="n">
-        <v>7063479</v>
+        <v>7063778</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4562,10 +4547,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122730177</v>
+        <v>122741741</v>
       </c>
       <c r="B39" t="n">
-        <v>56688</v>
+        <v>90909</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4578,39 +4563,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100138</v>
+        <v>5447</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Lill-Åsberget, Lill-Åsberget, Ång</t>
+          <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>542198</v>
+        <v>542064</v>
       </c>
       <c r="R39" t="n">
-        <v>7063872</v>
+        <v>7063777</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -4669,10 +4649,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122732330</v>
+        <v>122730246</v>
       </c>
       <c r="B40" t="n">
-        <v>90909</v>
+        <v>78766</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4681,38 +4661,38 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Stamåsen, Stamåsen, Ång</t>
+          <t>Lill-Åsberget, Lill-Åsberget, Ång</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>541875</v>
+        <v>542168</v>
       </c>
       <c r="R40" t="n">
-        <v>7063622</v>
+        <v>7063849</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -4771,10 +4751,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122732264</v>
+        <v>122741643</v>
       </c>
       <c r="B41" t="n">
-        <v>82553</v>
+        <v>56680</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4787,34 +4767,39 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1312</v>
+        <v>102612</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>541883</v>
+        <v>542064</v>
       </c>
       <c r="R41" t="n">
-        <v>7063653</v>
+        <v>7063749</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -4873,7 +4858,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122741691</v>
+        <v>122730426</v>
       </c>
       <c r="B42" t="n">
         <v>56680</v>
@@ -4914,14 +4899,14 @@
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Stamåsen, Stamåsen, Ång</t>
+          <t>Lill-Åsberget, Lill-Åsberget, Ång</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>542063</v>
+        <v>542150</v>
       </c>
       <c r="R42" t="n">
-        <v>7063786</v>
+        <v>7063805</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -4980,10 +4965,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122741763</v>
+        <v>122730177</v>
       </c>
       <c r="B43" t="n">
-        <v>90944</v>
+        <v>56688</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4992,38 +4977,43 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1202</v>
+        <v>100138</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Stamåsen, Stamåsen, Ång</t>
+          <t>Lill-Åsberget, Lill-Åsberget, Ång</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>542067</v>
+        <v>542198</v>
       </c>
       <c r="R43" t="n">
-        <v>7063777</v>
+        <v>7063872</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -5082,10 +5072,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122730234</v>
+        <v>122732653</v>
       </c>
       <c r="B44" t="n">
-        <v>79847</v>
+        <v>90958</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5098,34 +5088,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6458</v>
+        <v>1204</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Lill-Åsberget, Lill-Åsberget, Ång</t>
+          <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>542187</v>
+        <v>541760</v>
       </c>
       <c r="R44" t="n">
-        <v>7063885</v>
+        <v>7063584</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>
@@ -5184,10 +5174,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122730246</v>
+        <v>122731109</v>
       </c>
       <c r="B45" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5200,34 +5190,39 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Lill-Åsberget, Lill-Åsberget, Ång</t>
+          <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>542168</v>
+        <v>541940</v>
       </c>
       <c r="R45" t="n">
-        <v>7063849</v>
+        <v>7063712</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -5260,6 +5255,11 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-02-24</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Äldre ringhack, gammal tall</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5286,10 +5286,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122741741</v>
+        <v>122730499</v>
       </c>
       <c r="B46" t="n">
-        <v>90909</v>
+        <v>78766</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5298,38 +5298,38 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Stamåsen, Stamåsen, Ång</t>
+          <t>Lill-Åsberget, Lill-Åsberget, Ång</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>542064</v>
+        <v>542132</v>
       </c>
       <c r="R46" t="n">
-        <v>7063777</v>
+        <v>7063797</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>

--- a/artfynd/A 3110-2025 artfynd.xlsx
+++ b/artfynd/A 3110-2025 artfynd.xlsx
@@ -1350,10 +1350,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122731193</v>
+        <v>122732487</v>
       </c>
       <c r="B8" t="n">
-        <v>91342</v>
+        <v>90944</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1366,16 +1366,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6040186</v>
+        <v>1202</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1385,10 +1390,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>541919</v>
+        <v>541847</v>
       </c>
       <c r="R8" t="n">
-        <v>7063716</v>
+        <v>7063615</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1447,10 +1452,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122732558</v>
+        <v>122732330</v>
       </c>
       <c r="B9" t="n">
-        <v>97315</v>
+        <v>90909</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1463,21 +1468,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221941</v>
+        <v>5447</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1487,10 +1492,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>541824</v>
+        <v>541875</v>
       </c>
       <c r="R9" t="n">
-        <v>7063603</v>
+        <v>7063622</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1549,10 +1554,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122732264</v>
+        <v>122731904</v>
       </c>
       <c r="B10" t="n">
-        <v>82553</v>
+        <v>78766</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1565,21 +1570,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1589,10 +1594,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>541883</v>
+        <v>541908</v>
       </c>
       <c r="R10" t="n">
-        <v>7063653</v>
+        <v>7063682</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1625,6 +1630,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-02-24</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Garnlavsrika partier över hela sluttningen</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1651,10 +1661,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122732817</v>
+        <v>122732631</v>
       </c>
       <c r="B11" t="n">
-        <v>56680</v>
+        <v>88303</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1667,39 +1677,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>102612</v>
+        <v>510</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>541803</v>
+        <v>541768</v>
       </c>
       <c r="R11" t="n">
-        <v>7063479</v>
+        <v>7063586</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1758,10 +1763,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122730759</v>
+        <v>122731193</v>
       </c>
       <c r="B12" t="n">
-        <v>91304</v>
+        <v>91342</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1770,25 +1775,20 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1506</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Ostticka</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1798,10 +1798,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>542045</v>
+        <v>541919</v>
       </c>
       <c r="R12" t="n">
-        <v>7063823</v>
+        <v>7063716</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1860,7 +1860,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122741691</v>
+        <v>122741643</v>
       </c>
       <c r="B13" t="n">
         <v>56680</v>
@@ -1905,10 +1905,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>542063</v>
+        <v>542064</v>
       </c>
       <c r="R13" t="n">
-        <v>7063786</v>
+        <v>7063749</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1967,10 +1967,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122732330</v>
+        <v>122732817</v>
       </c>
       <c r="B14" t="n">
-        <v>90909</v>
+        <v>56680</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1979,38 +1979,43 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5447</v>
+        <v>102612</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>541875</v>
+        <v>541803</v>
       </c>
       <c r="R14" t="n">
-        <v>7063622</v>
+        <v>7063479</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2069,10 +2074,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122730004</v>
+        <v>122730086</v>
       </c>
       <c r="B15" t="n">
-        <v>90958</v>
+        <v>90944</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2085,21 +2090,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1204</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2109,10 +2114,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>542251</v>
+        <v>542258</v>
       </c>
       <c r="R15" t="n">
-        <v>7063915</v>
+        <v>7063917</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2171,10 +2176,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122730086</v>
+        <v>122731166</v>
       </c>
       <c r="B16" t="n">
-        <v>90944</v>
+        <v>90962</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2187,34 +2192,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Lill-Åsberget, Lill-Åsberget, Ång</t>
+          <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>542258</v>
+        <v>541922</v>
       </c>
       <c r="R16" t="n">
-        <v>7063917</v>
+        <v>7063717</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2273,10 +2278,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122741376</v>
+        <v>122732958</v>
       </c>
       <c r="B17" t="n">
-        <v>91235</v>
+        <v>57478</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2289,34 +2294,39 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>541997</v>
+        <v>541820</v>
       </c>
       <c r="R17" t="n">
-        <v>7063580</v>
+        <v>7063439</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2349,6 +2359,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-02-24</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Äldre ringhack, &gt;200-årig tall</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2375,10 +2390,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122731166</v>
+        <v>122730004</v>
       </c>
       <c r="B18" t="n">
-        <v>90962</v>
+        <v>90958</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2391,34 +2406,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5432</v>
+        <v>1204</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Stamåsen, Stamåsen, Ång</t>
+          <t>Lill-Åsberget, Lill-Åsberget, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>541922</v>
+        <v>542251</v>
       </c>
       <c r="R18" t="n">
-        <v>7063717</v>
+        <v>7063915</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2477,10 +2492,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122733041</v>
+        <v>122730499</v>
       </c>
       <c r="B19" t="n">
-        <v>90962</v>
+        <v>78766</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2493,34 +2508,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Stamåsen, Stamåsen, Ång</t>
+          <t>Lill-Åsberget, Lill-Åsberget, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>541873</v>
+        <v>542132</v>
       </c>
       <c r="R19" t="n">
-        <v>7063379</v>
+        <v>7063797</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2579,10 +2594,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122732657</v>
+        <v>122741763</v>
       </c>
       <c r="B20" t="n">
-        <v>90909</v>
+        <v>90944</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2591,25 +2606,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2619,10 +2634,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>541761</v>
+        <v>542067</v>
       </c>
       <c r="R20" t="n">
-        <v>7063583</v>
+        <v>7063777</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2681,10 +2696,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122732487</v>
+        <v>122733041</v>
       </c>
       <c r="B21" t="n">
-        <v>90944</v>
+        <v>90962</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2697,21 +2712,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2721,10 +2736,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>541847</v>
+        <v>541873</v>
       </c>
       <c r="R21" t="n">
-        <v>7063615</v>
+        <v>7063379</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2783,10 +2798,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122730595</v>
+        <v>122741781</v>
       </c>
       <c r="B22" t="n">
-        <v>90944</v>
+        <v>91293</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2795,25 +2810,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1202</v>
+        <v>2062</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2823,10 +2838,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>542097</v>
+        <v>542068</v>
       </c>
       <c r="R22" t="n">
-        <v>7063815</v>
+        <v>7063778</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2885,10 +2900,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122732631</v>
+        <v>122730234</v>
       </c>
       <c r="B23" t="n">
-        <v>88303</v>
+        <v>79847</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2901,34 +2916,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>510</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Stamåsen, Stamåsen, Ång</t>
+          <t>Lill-Åsberget, Lill-Åsberget, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>541768</v>
+        <v>542187</v>
       </c>
       <c r="R23" t="n">
-        <v>7063586</v>
+        <v>7063885</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -2987,10 +3002,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122741763</v>
+        <v>122732264</v>
       </c>
       <c r="B24" t="n">
-        <v>90944</v>
+        <v>82553</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3003,21 +3018,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1202</v>
+        <v>1312</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3027,10 +3042,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>542067</v>
+        <v>541883</v>
       </c>
       <c r="R24" t="n">
-        <v>7063777</v>
+        <v>7063653</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3089,10 +3104,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122730234</v>
+        <v>122730426</v>
       </c>
       <c r="B25" t="n">
-        <v>79847</v>
+        <v>56680</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3105,34 +3120,39 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6458</v>
+        <v>102612</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Lill-Åsberget, Lill-Åsberget, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>542187</v>
+        <v>542150</v>
       </c>
       <c r="R25" t="n">
-        <v>7063885</v>
+        <v>7063805</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3191,10 +3211,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122731014</v>
+        <v>122741691</v>
       </c>
       <c r="B26" t="n">
-        <v>79847</v>
+        <v>56680</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3207,34 +3227,39 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6458</v>
+        <v>102612</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>541940</v>
+        <v>542063</v>
       </c>
       <c r="R26" t="n">
-        <v>7063713</v>
+        <v>7063786</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3293,10 +3318,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122733126</v>
+        <v>122732584</v>
       </c>
       <c r="B27" t="n">
-        <v>78766</v>
+        <v>97311</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3305,25 +3330,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3333,10 +3358,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>541858</v>
+        <v>541821</v>
       </c>
       <c r="R27" t="n">
-        <v>7063338</v>
+        <v>7063616</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3395,7 +3420,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122731904</v>
+        <v>122730829</v>
       </c>
       <c r="B28" t="n">
         <v>78766</v>
@@ -3435,10 +3460,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>541908</v>
+        <v>542035</v>
       </c>
       <c r="R28" t="n">
-        <v>7063682</v>
+        <v>7063816</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3471,11 +3496,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-02-24</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Garnlavsrika partier över hela sluttningen</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3604,10 +3624,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122729831</v>
+        <v>122741513</v>
       </c>
       <c r="B30" t="n">
-        <v>57478</v>
+        <v>90944</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3620,39 +3640,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Lill-Åsberget, Lill-Åsberget, Ång</t>
+          <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>542249</v>
+        <v>542030</v>
       </c>
       <c r="R30" t="n">
-        <v>7063942</v>
+        <v>7063685</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3685,11 +3700,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-02-24</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Bohål i torrgran, 2m ovan mark. 5 cm ø. Gott om stående död ved i området.</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3716,10 +3726,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122741488</v>
+        <v>122732653</v>
       </c>
       <c r="B31" t="n">
-        <v>57494</v>
+        <v>90958</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3732,39 +3742,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100049</v>
+        <v>1204</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>542034</v>
+        <v>541760</v>
       </c>
       <c r="R31" t="n">
-        <v>7063681</v>
+        <v>7063584</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3823,10 +3828,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122741513</v>
+        <v>122730246</v>
       </c>
       <c r="B32" t="n">
-        <v>90944</v>
+        <v>78766</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3839,34 +3844,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Stamåsen, Stamåsen, Ång</t>
+          <t>Lill-Åsberget, Lill-Åsberget, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>542030</v>
+        <v>542168</v>
       </c>
       <c r="R32" t="n">
-        <v>7063685</v>
+        <v>7063849</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3925,10 +3930,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122730042</v>
+        <v>122730177</v>
       </c>
       <c r="B33" t="n">
-        <v>91235</v>
+        <v>56688</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3937,38 +3942,43 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>658</v>
+        <v>100138</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Lill-Åsberget, Lill-Åsberget, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>542248</v>
+        <v>542198</v>
       </c>
       <c r="R33" t="n">
-        <v>7063927</v>
+        <v>7063872</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -4027,10 +4037,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122732584</v>
+        <v>122732558</v>
       </c>
       <c r="B34" t="n">
-        <v>97309</v>
+        <v>97317</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4043,16 +4053,16 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>221945</v>
+        <v>221941</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -4067,10 +4077,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>541821</v>
+        <v>541824</v>
       </c>
       <c r="R34" t="n">
-        <v>7063616</v>
+        <v>7063603</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4129,10 +4139,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122730829</v>
+        <v>122731109</v>
       </c>
       <c r="B35" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4145,34 +4155,39 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>542035</v>
+        <v>541940</v>
       </c>
       <c r="R35" t="n">
-        <v>7063816</v>
+        <v>7063712</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4205,6 +4220,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-02-24</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Äldre ringhack, gammal tall</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4231,10 +4251,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122732958</v>
+        <v>122741488</v>
       </c>
       <c r="B36" t="n">
-        <v>57478</v>
+        <v>57494</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4247,16 +4267,16 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -4267,7 +4287,7 @@
       <c r="I36" t="inlineStr"/>
       <c r="M36" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
@@ -4276,10 +4296,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>541820</v>
+        <v>542034</v>
       </c>
       <c r="R36" t="n">
-        <v>7063439</v>
+        <v>7063681</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4312,11 +4332,6 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-02-24</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Äldre ringhack, &gt;200-årig tall</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4343,10 +4358,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122742207</v>
+        <v>122729831</v>
       </c>
       <c r="B37" t="n">
-        <v>90962</v>
+        <v>57478</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4359,34 +4374,39 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Lill-Åsberget, Lill-Åsberget, Ång</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>542238</v>
+        <v>542249</v>
       </c>
       <c r="R37" t="n">
-        <v>7063973</v>
+        <v>7063942</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4419,6 +4439,11 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-02-24</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Bohål i torrgran, 2m ovan mark. 5 cm ø. Gott om stående död ved i området.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4445,10 +4470,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122741781</v>
+        <v>122730042</v>
       </c>
       <c r="B38" t="n">
-        <v>91293</v>
+        <v>91235</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4457,38 +4482,38 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>2062</v>
+        <v>658</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Stamåsen, Stamåsen, Ång</t>
+          <t>Lill-Åsberget, Lill-Åsberget, Ång</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>542068</v>
+        <v>542248</v>
       </c>
       <c r="R38" t="n">
-        <v>7063778</v>
+        <v>7063927</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4547,10 +4572,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122741741</v>
+        <v>122730595</v>
       </c>
       <c r="B39" t="n">
-        <v>90909</v>
+        <v>90944</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4559,25 +4584,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4587,10 +4612,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>542064</v>
+        <v>542097</v>
       </c>
       <c r="R39" t="n">
-        <v>7063777</v>
+        <v>7063815</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -4649,7 +4674,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122730246</v>
+        <v>122733126</v>
       </c>
       <c r="B40" t="n">
         <v>78766</v>
@@ -4685,14 +4710,14 @@
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Lill-Åsberget, Lill-Åsberget, Ång</t>
+          <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>542168</v>
+        <v>541858</v>
       </c>
       <c r="R40" t="n">
-        <v>7063849</v>
+        <v>7063338</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -4751,10 +4776,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122741643</v>
+        <v>122731014</v>
       </c>
       <c r="B41" t="n">
-        <v>56680</v>
+        <v>79847</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4767,39 +4792,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>102612</v>
+        <v>6458</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>542064</v>
+        <v>541940</v>
       </c>
       <c r="R41" t="n">
-        <v>7063749</v>
+        <v>7063713</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -4858,10 +4878,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122730426</v>
+        <v>122742207</v>
       </c>
       <c r="B42" t="n">
-        <v>56680</v>
+        <v>90962</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4874,39 +4894,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>102612</v>
+        <v>5432</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Lill-Åsberget, Lill-Åsberget, Ång</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>542150</v>
+        <v>542238</v>
       </c>
       <c r="R42" t="n">
-        <v>7063805</v>
+        <v>7063973</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -4965,10 +4980,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122730177</v>
+        <v>122730759</v>
       </c>
       <c r="B43" t="n">
-        <v>56688</v>
+        <v>91304</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4977,43 +4992,38 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100138</v>
+        <v>1506</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Lill-Åsberget, Lill-Åsberget, Ång</t>
+          <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>542198</v>
+        <v>542045</v>
       </c>
       <c r="R43" t="n">
-        <v>7063872</v>
+        <v>7063823</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -5072,10 +5082,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122732653</v>
+        <v>122732657</v>
       </c>
       <c r="B44" t="n">
-        <v>90958</v>
+        <v>90909</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5084,25 +5094,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1204</v>
+        <v>5447</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5112,10 +5122,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>541760</v>
+        <v>541761</v>
       </c>
       <c r="R44" t="n">
-        <v>7063584</v>
+        <v>7063583</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>
@@ -5174,10 +5184,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122731109</v>
+        <v>122741376</v>
       </c>
       <c r="B45" t="n">
-        <v>57478</v>
+        <v>91235</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5190,39 +5200,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>541940</v>
+        <v>541997</v>
       </c>
       <c r="R45" t="n">
-        <v>7063712</v>
+        <v>7063580</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -5255,11 +5260,6 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-02-24</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Äldre ringhack, gammal tall</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5286,10 +5286,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122730499</v>
+        <v>122741741</v>
       </c>
       <c r="B46" t="n">
-        <v>78766</v>
+        <v>90909</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5298,38 +5298,38 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Lill-Åsberget, Lill-Åsberget, Ång</t>
+          <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>542132</v>
+        <v>542064</v>
       </c>
       <c r="R46" t="n">
-        <v>7063797</v>
+        <v>7063777</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>

--- a/artfynd/A 3110-2025 artfynd.xlsx
+++ b/artfynd/A 3110-2025 artfynd.xlsx
@@ -1661,10 +1661,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122732631</v>
+        <v>122731193</v>
       </c>
       <c r="B11" t="n">
-        <v>88303</v>
+        <v>91342</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1677,21 +1677,16 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>510</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Doftskinn</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1701,10 +1696,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>541768</v>
+        <v>541919</v>
       </c>
       <c r="R11" t="n">
-        <v>7063586</v>
+        <v>7063716</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1763,10 +1758,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122731193</v>
+        <v>122741643</v>
       </c>
       <c r="B12" t="n">
-        <v>91342</v>
+        <v>56680</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1779,29 +1774,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6040186</v>
+        <v>102612</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Järpe</t>
+        </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>541919</v>
+        <v>542064</v>
       </c>
       <c r="R12" t="n">
-        <v>7063716</v>
+        <v>7063749</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1860,10 +1865,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122741643</v>
+        <v>122732631</v>
       </c>
       <c r="B13" t="n">
-        <v>56680</v>
+        <v>88303</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1876,39 +1881,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>102612</v>
+        <v>510</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>542064</v>
+        <v>541768</v>
       </c>
       <c r="R13" t="n">
-        <v>7063749</v>
+        <v>7063586</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1967,10 +1967,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122732817</v>
+        <v>122731166</v>
       </c>
       <c r="B14" t="n">
-        <v>56680</v>
+        <v>90962</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1983,39 +1983,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>102612</v>
+        <v>5432</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>541803</v>
+        <v>541922</v>
       </c>
       <c r="R14" t="n">
-        <v>7063479</v>
+        <v>7063717</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2074,10 +2069,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122730086</v>
+        <v>122732817</v>
       </c>
       <c r="B15" t="n">
-        <v>90944</v>
+        <v>56680</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2090,34 +2085,39 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>102612</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Lill-Åsberget, Lill-Åsberget, Ång</t>
+          <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>542258</v>
+        <v>541803</v>
       </c>
       <c r="R15" t="n">
-        <v>7063917</v>
+        <v>7063479</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2176,10 +2176,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122731166</v>
+        <v>122730086</v>
       </c>
       <c r="B16" t="n">
-        <v>90962</v>
+        <v>90944</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2192,34 +2192,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Stamåsen, Stamåsen, Ång</t>
+          <t>Lill-Åsberget, Lill-Åsberget, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>541922</v>
+        <v>542258</v>
       </c>
       <c r="R16" t="n">
-        <v>7063717</v>
+        <v>7063917</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2278,10 +2278,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122732958</v>
+        <v>122730004</v>
       </c>
       <c r="B17" t="n">
-        <v>57478</v>
+        <v>90958</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2294,39 +2294,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>1204</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Stamåsen, Stamåsen, Ång</t>
+          <t>Lill-Åsberget, Lill-Åsberget, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>541820</v>
+        <v>542251</v>
       </c>
       <c r="R17" t="n">
-        <v>7063439</v>
+        <v>7063915</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2359,11 +2354,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-02-24</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Äldre ringhack, &gt;200-årig tall</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2390,10 +2380,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122730004</v>
+        <v>122730499</v>
       </c>
       <c r="B18" t="n">
-        <v>90958</v>
+        <v>78766</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2406,21 +2396,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2430,10 +2420,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>542251</v>
+        <v>542132</v>
       </c>
       <c r="R18" t="n">
-        <v>7063915</v>
+        <v>7063797</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2492,10 +2482,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122730499</v>
+        <v>122732958</v>
       </c>
       <c r="B19" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2508,34 +2498,39 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Lill-Åsberget, Lill-Åsberget, Ång</t>
+          <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>542132</v>
+        <v>541820</v>
       </c>
       <c r="R19" t="n">
-        <v>7063797</v>
+        <v>7063439</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2568,6 +2563,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-02-24</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Äldre ringhack, &gt;200-årig tall</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -4470,10 +4470,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122730042</v>
+        <v>122730595</v>
       </c>
       <c r="B38" t="n">
-        <v>91235</v>
+        <v>90944</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4486,34 +4486,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Lill-Åsberget, Lill-Åsberget, Ång</t>
+          <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>542248</v>
+        <v>542097</v>
       </c>
       <c r="R38" t="n">
-        <v>7063927</v>
+        <v>7063815</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4572,10 +4572,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122730595</v>
+        <v>122730042</v>
       </c>
       <c r="B39" t="n">
-        <v>90944</v>
+        <v>91235</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4588,34 +4588,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Stamåsen, Stamåsen, Ång</t>
+          <t>Lill-Åsberget, Lill-Åsberget, Ång</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>542097</v>
+        <v>542248</v>
       </c>
       <c r="R39" t="n">
-        <v>7063815</v>
+        <v>7063927</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>

--- a/artfynd/A 3110-2025 artfynd.xlsx
+++ b/artfynd/A 3110-2025 artfynd.xlsx
@@ -3726,10 +3726,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122732653</v>
+        <v>122730246</v>
       </c>
       <c r="B31" t="n">
-        <v>90958</v>
+        <v>78766</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3742,34 +3742,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Stamåsen, Stamåsen, Ång</t>
+          <t>Lill-Åsberget, Lill-Åsberget, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>541760</v>
+        <v>542168</v>
       </c>
       <c r="R31" t="n">
-        <v>7063584</v>
+        <v>7063849</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3828,10 +3828,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122730246</v>
+        <v>122730177</v>
       </c>
       <c r="B32" t="n">
-        <v>78766</v>
+        <v>56688</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3840,38 +3840,43 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Lill-Åsberget, Lill-Åsberget, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>542168</v>
+        <v>542198</v>
       </c>
       <c r="R32" t="n">
-        <v>7063849</v>
+        <v>7063872</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3930,10 +3935,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122730177</v>
+        <v>122732653</v>
       </c>
       <c r="B33" t="n">
-        <v>56688</v>
+        <v>90958</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3942,43 +3947,38 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100138</v>
+        <v>1204</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Lill-Åsberget, Lill-Åsberget, Ång</t>
+          <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>542198</v>
+        <v>541760</v>
       </c>
       <c r="R33" t="n">
-        <v>7063872</v>
+        <v>7063584</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -4251,10 +4251,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122741488</v>
+        <v>122729831</v>
       </c>
       <c r="B36" t="n">
-        <v>57494</v>
+        <v>57478</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4267,16 +4267,16 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -4287,19 +4287,19 @@
       <c r="I36" t="inlineStr"/>
       <c r="M36" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Stamåsen, Stamåsen, Ång</t>
+          <t>Lill-Åsberget, Lill-Åsberget, Ång</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>542034</v>
+        <v>542249</v>
       </c>
       <c r="R36" t="n">
-        <v>7063681</v>
+        <v>7063942</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4332,6 +4332,11 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-02-24</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Bohål i torrgran, 2m ovan mark. 5 cm ø. Gott om stående död ved i området.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4358,10 +4363,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122729831</v>
+        <v>122741488</v>
       </c>
       <c r="B37" t="n">
-        <v>57478</v>
+        <v>57494</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4374,16 +4379,16 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -4394,19 +4399,19 @@
       <c r="I37" t="inlineStr"/>
       <c r="M37" t="inlineStr">
         <is>
-          <t>gammalt bo</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Lill-Åsberget, Lill-Åsberget, Ång</t>
+          <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>542249</v>
+        <v>542034</v>
       </c>
       <c r="R37" t="n">
-        <v>7063942</v>
+        <v>7063681</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4439,11 +4444,6 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-02-24</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Bohål i torrgran, 2m ovan mark. 5 cm ø. Gott om stående död ved i området.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4470,10 +4470,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122730595</v>
+        <v>122730042</v>
       </c>
       <c r="B38" t="n">
-        <v>90944</v>
+        <v>91235</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4486,34 +4486,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Stamåsen, Stamåsen, Ång</t>
+          <t>Lill-Åsberget, Lill-Åsberget, Ång</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>542097</v>
+        <v>542248</v>
       </c>
       <c r="R38" t="n">
-        <v>7063815</v>
+        <v>7063927</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4572,10 +4572,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122730042</v>
+        <v>122730595</v>
       </c>
       <c r="B39" t="n">
-        <v>91235</v>
+        <v>90944</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4588,34 +4588,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Lill-Åsberget, Lill-Åsberget, Ång</t>
+          <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>542248</v>
+        <v>542097</v>
       </c>
       <c r="R39" t="n">
-        <v>7063927</v>
+        <v>7063815</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>

--- a/artfynd/A 3110-2025 artfynd.xlsx
+++ b/artfynd/A 3110-2025 artfynd.xlsx
@@ -1661,10 +1661,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122731193</v>
+        <v>122732631</v>
       </c>
       <c r="B11" t="n">
-        <v>91342</v>
+        <v>88303</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1677,16 +1677,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6040186</v>
+        <v>510</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Doftskinn</t>
+        </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1696,10 +1701,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>541919</v>
+        <v>541768</v>
       </c>
       <c r="R11" t="n">
-        <v>7063716</v>
+        <v>7063586</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1758,10 +1763,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122741643</v>
+        <v>122731193</v>
       </c>
       <c r="B12" t="n">
-        <v>56680</v>
+        <v>91342</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1774,39 +1779,29 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>102612</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Järpe</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>542064</v>
+        <v>541919</v>
       </c>
       <c r="R12" t="n">
-        <v>7063749</v>
+        <v>7063716</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1865,10 +1860,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122732631</v>
+        <v>122741643</v>
       </c>
       <c r="B13" t="n">
-        <v>88303</v>
+        <v>56680</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1881,34 +1876,39 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>510</v>
+        <v>102612</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>541768</v>
+        <v>542064</v>
       </c>
       <c r="R13" t="n">
-        <v>7063586</v>
+        <v>7063749</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -2278,10 +2278,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122730004</v>
+        <v>122732958</v>
       </c>
       <c r="B17" t="n">
-        <v>90958</v>
+        <v>57478</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2294,34 +2294,39 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1204</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Lill-Åsberget, Lill-Åsberget, Ång</t>
+          <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>542251</v>
+        <v>541820</v>
       </c>
       <c r="R17" t="n">
-        <v>7063915</v>
+        <v>7063439</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2354,6 +2359,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-02-24</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Äldre ringhack, &gt;200-årig tall</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2380,10 +2390,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122730499</v>
+        <v>122730004</v>
       </c>
       <c r="B18" t="n">
-        <v>78766</v>
+        <v>90958</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2396,21 +2406,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2420,10 +2430,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>542132</v>
+        <v>542251</v>
       </c>
       <c r="R18" t="n">
-        <v>7063797</v>
+        <v>7063915</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2482,10 +2492,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122732958</v>
+        <v>122730499</v>
       </c>
       <c r="B19" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2498,39 +2508,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Stamåsen, Stamåsen, Ång</t>
+          <t>Lill-Åsberget, Lill-Åsberget, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>541820</v>
+        <v>542132</v>
       </c>
       <c r="R19" t="n">
-        <v>7063439</v>
+        <v>7063797</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2563,11 +2568,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-02-24</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Äldre ringhack, &gt;200-årig tall</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3002,10 +3002,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122732264</v>
+        <v>122730426</v>
       </c>
       <c r="B24" t="n">
-        <v>82553</v>
+        <v>56680</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3018,34 +3018,39 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1312</v>
+        <v>102612</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Stamåsen, Stamåsen, Ång</t>
+          <t>Lill-Åsberget, Lill-Åsberget, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>541883</v>
+        <v>542150</v>
       </c>
       <c r="R24" t="n">
-        <v>7063653</v>
+        <v>7063805</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3104,7 +3109,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122730426</v>
+        <v>122741691</v>
       </c>
       <c r="B25" t="n">
         <v>56680</v>
@@ -3145,14 +3150,14 @@
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Lill-Åsberget, Lill-Åsberget, Ång</t>
+          <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>542150</v>
+        <v>542063</v>
       </c>
       <c r="R25" t="n">
-        <v>7063805</v>
+        <v>7063786</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3211,10 +3216,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122741691</v>
+        <v>122732584</v>
       </c>
       <c r="B26" t="n">
-        <v>56680</v>
+        <v>97311</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3223,43 +3228,38 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>102612</v>
+        <v>221945</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>542063</v>
+        <v>541821</v>
       </c>
       <c r="R26" t="n">
-        <v>7063786</v>
+        <v>7063616</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3318,10 +3318,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122732584</v>
+        <v>122732264</v>
       </c>
       <c r="B27" t="n">
-        <v>97311</v>
+        <v>82553</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3330,25 +3330,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>221945</v>
+        <v>1312</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3358,10 +3358,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>541821</v>
+        <v>541883</v>
       </c>
       <c r="R27" t="n">
-        <v>7063616</v>
+        <v>7063653</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3726,10 +3726,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122730246</v>
+        <v>122732653</v>
       </c>
       <c r="B31" t="n">
-        <v>78766</v>
+        <v>90958</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3742,34 +3742,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Lill-Åsberget, Lill-Åsberget, Ång</t>
+          <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>542168</v>
+        <v>541760</v>
       </c>
       <c r="R31" t="n">
-        <v>7063849</v>
+        <v>7063584</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3828,10 +3828,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122730177</v>
+        <v>122730246</v>
       </c>
       <c r="B32" t="n">
-        <v>56688</v>
+        <v>78766</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3840,43 +3840,38 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Lill-Åsberget, Lill-Åsberget, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>542198</v>
+        <v>542168</v>
       </c>
       <c r="R32" t="n">
-        <v>7063872</v>
+        <v>7063849</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3935,10 +3930,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122732653</v>
+        <v>122730177</v>
       </c>
       <c r="B33" t="n">
-        <v>90958</v>
+        <v>56688</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3947,38 +3942,43 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1204</v>
+        <v>100138</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Stamåsen, Stamåsen, Ång</t>
+          <t>Lill-Åsberget, Lill-Åsberget, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>541760</v>
+        <v>542198</v>
       </c>
       <c r="R33" t="n">
-        <v>7063584</v>
+        <v>7063872</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>

--- a/artfynd/A 3110-2025 artfynd.xlsx
+++ b/artfynd/A 3110-2025 artfynd.xlsx
@@ -1350,10 +1350,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122732487</v>
+        <v>122732653</v>
       </c>
       <c r="B8" t="n">
-        <v>90944</v>
+        <v>90958</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1366,21 +1366,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>1204</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1390,10 +1390,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>541847</v>
+        <v>541760</v>
       </c>
       <c r="R8" t="n">
-        <v>7063615</v>
+        <v>7063584</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1452,10 +1452,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122732330</v>
+        <v>122731109</v>
       </c>
       <c r="B9" t="n">
-        <v>90909</v>
+        <v>57478</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1464,38 +1464,43 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>541875</v>
+        <v>541940</v>
       </c>
       <c r="R9" t="n">
-        <v>7063622</v>
+        <v>7063712</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1528,6 +1533,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-02-24</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Äldre ringhack, gammal tall</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1554,10 +1564,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122731904</v>
+        <v>122730177</v>
       </c>
       <c r="B10" t="n">
-        <v>78766</v>
+        <v>56688</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1566,38 +1576,43 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Stamåsen, Stamåsen, Ång</t>
+          <t>Lill-Åsberget, Lill-Åsberget, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>541908</v>
+        <v>542198</v>
       </c>
       <c r="R10" t="n">
-        <v>7063682</v>
+        <v>7063872</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1630,11 +1645,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-02-24</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Garnlavsrika partier över hela sluttningen</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1661,10 +1671,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122732631</v>
+        <v>122732487</v>
       </c>
       <c r="B11" t="n">
-        <v>88303</v>
+        <v>90944</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1677,21 +1687,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>510</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1701,10 +1711,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>541768</v>
+        <v>541847</v>
       </c>
       <c r="R11" t="n">
-        <v>7063586</v>
+        <v>7063615</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1763,10 +1773,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122731193</v>
+        <v>122730759</v>
       </c>
       <c r="B12" t="n">
-        <v>91342</v>
+        <v>91304</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1775,20 +1785,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6040186</v>
+        <v>1506</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Ostticka</t>
+        </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1798,10 +1813,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>541919</v>
+        <v>542045</v>
       </c>
       <c r="R12" t="n">
-        <v>7063716</v>
+        <v>7063823</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1860,10 +1875,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122741643</v>
+        <v>122741513</v>
       </c>
       <c r="B13" t="n">
-        <v>56680</v>
+        <v>90944</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1876,39 +1891,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>102612</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>542064</v>
+        <v>542030</v>
       </c>
       <c r="R13" t="n">
-        <v>7063749</v>
+        <v>7063685</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -2069,10 +2079,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122732817</v>
+        <v>122732558</v>
       </c>
       <c r="B15" t="n">
-        <v>56680</v>
+        <v>97317</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2081,43 +2091,38 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>102612</v>
+        <v>221941</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>541803</v>
+        <v>541824</v>
       </c>
       <c r="R15" t="n">
-        <v>7063479</v>
+        <v>7063603</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2176,10 +2181,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122730086</v>
+        <v>122730042</v>
       </c>
       <c r="B16" t="n">
-        <v>90944</v>
+        <v>91235</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2192,21 +2197,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2216,10 +2221,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>542258</v>
+        <v>542248</v>
       </c>
       <c r="R16" t="n">
-        <v>7063917</v>
+        <v>7063927</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2278,10 +2283,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122732958</v>
+        <v>122732657</v>
       </c>
       <c r="B17" t="n">
-        <v>57478</v>
+        <v>90909</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2290,43 +2295,38 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>541820</v>
+        <v>541761</v>
       </c>
       <c r="R17" t="n">
-        <v>7063439</v>
+        <v>7063583</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2359,11 +2359,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-02-24</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Äldre ringhack, &gt;200-årig tall</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2390,10 +2385,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122730004</v>
+        <v>122741643</v>
       </c>
       <c r="B18" t="n">
-        <v>90958</v>
+        <v>56680</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2406,34 +2401,39 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1204</v>
+        <v>102612</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Lill-Åsberget, Lill-Åsberget, Ång</t>
+          <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>542251</v>
+        <v>542064</v>
       </c>
       <c r="R18" t="n">
-        <v>7063915</v>
+        <v>7063749</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2492,10 +2492,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122730499</v>
+        <v>122730595</v>
       </c>
       <c r="B19" t="n">
-        <v>78766</v>
+        <v>90944</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2508,34 +2508,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Lill-Åsberget, Lill-Åsberget, Ång</t>
+          <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>542132</v>
+        <v>542097</v>
       </c>
       <c r="R19" t="n">
-        <v>7063797</v>
+        <v>7063815</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2594,10 +2594,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122741763</v>
+        <v>122733126</v>
       </c>
       <c r="B20" t="n">
-        <v>90944</v>
+        <v>78766</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2610,21 +2610,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2634,10 +2634,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>542067</v>
+        <v>541858</v>
       </c>
       <c r="R20" t="n">
-        <v>7063777</v>
+        <v>7063338</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2696,10 +2696,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122733041</v>
+        <v>122730426</v>
       </c>
       <c r="B21" t="n">
-        <v>90962</v>
+        <v>56680</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2712,34 +2712,39 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5432</v>
+        <v>102612</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Stamåsen, Stamåsen, Ång</t>
+          <t>Lill-Åsberget, Lill-Åsberget, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>541873</v>
+        <v>542150</v>
       </c>
       <c r="R21" t="n">
-        <v>7063379</v>
+        <v>7063805</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2798,10 +2803,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122741781</v>
+        <v>122741691</v>
       </c>
       <c r="B22" t="n">
-        <v>91293</v>
+        <v>56680</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2810,38 +2815,43 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2062</v>
+        <v>102612</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>542068</v>
+        <v>542063</v>
       </c>
       <c r="R22" t="n">
-        <v>7063778</v>
+        <v>7063786</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2900,10 +2910,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122730234</v>
+        <v>122732584</v>
       </c>
       <c r="B23" t="n">
-        <v>79847</v>
+        <v>97311</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2912,38 +2922,38 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6458</v>
+        <v>221945</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Lill-Åsberget, Lill-Åsberget, Ång</t>
+          <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>542187</v>
+        <v>541821</v>
       </c>
       <c r="R23" t="n">
-        <v>7063885</v>
+        <v>7063616</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -3002,10 +3012,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122730426</v>
+        <v>122730499</v>
       </c>
       <c r="B24" t="n">
-        <v>56680</v>
+        <v>78766</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3018,39 +3028,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>102612</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Lill-Åsberget, Lill-Åsberget, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>542150</v>
+        <v>542132</v>
       </c>
       <c r="R24" t="n">
-        <v>7063805</v>
+        <v>7063797</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3109,10 +3114,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122741691</v>
+        <v>122732958</v>
       </c>
       <c r="B25" t="n">
-        <v>56680</v>
+        <v>57478</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3125,16 +3130,16 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>102612</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -3145,7 +3150,7 @@
       <c r="I25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3154,10 +3159,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>542063</v>
+        <v>541820</v>
       </c>
       <c r="R25" t="n">
-        <v>7063786</v>
+        <v>7063439</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3190,6 +3195,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-02-24</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Äldre ringhack, &gt;200-årig tall</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3216,10 +3226,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122732584</v>
+        <v>122732817</v>
       </c>
       <c r="B26" t="n">
-        <v>97311</v>
+        <v>56680</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3228,38 +3238,43 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>221945</v>
+        <v>102612</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>541821</v>
+        <v>541803</v>
       </c>
       <c r="R26" t="n">
-        <v>7063616</v>
+        <v>7063479</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3318,10 +3333,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122732264</v>
+        <v>122730234</v>
       </c>
       <c r="B27" t="n">
-        <v>82553</v>
+        <v>79847</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3334,34 +3349,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1312</v>
+        <v>6458</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Stamåsen, Stamåsen, Ång</t>
+          <t>Lill-Åsberget, Lill-Åsberget, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>541883</v>
+        <v>542187</v>
       </c>
       <c r="R27" t="n">
-        <v>7063653</v>
+        <v>7063885</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3420,10 +3435,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122730829</v>
+        <v>122731193</v>
       </c>
       <c r="B28" t="n">
-        <v>78766</v>
+        <v>91342</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3436,21 +3451,16 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3460,10 +3470,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>542035</v>
+        <v>541919</v>
       </c>
       <c r="R28" t="n">
-        <v>7063816</v>
+        <v>7063716</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3522,10 +3532,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122741861</v>
+        <v>122733041</v>
       </c>
       <c r="B29" t="n">
-        <v>79847</v>
+        <v>90962</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3538,34 +3548,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Lill-Åsberget, Lill-Åsberget, Ång</t>
+          <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>542085</v>
+        <v>541873</v>
       </c>
       <c r="R29" t="n">
-        <v>7063858</v>
+        <v>7063379</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3624,10 +3634,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122741513</v>
+        <v>122730004</v>
       </c>
       <c r="B30" t="n">
-        <v>90944</v>
+        <v>90958</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3640,34 +3650,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1202</v>
+        <v>1204</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Stamåsen, Stamåsen, Ång</t>
+          <t>Lill-Åsberget, Lill-Åsberget, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>542030</v>
+        <v>542251</v>
       </c>
       <c r="R30" t="n">
-        <v>7063685</v>
+        <v>7063915</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3726,10 +3736,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122732653</v>
+        <v>122742207</v>
       </c>
       <c r="B31" t="n">
-        <v>90958</v>
+        <v>90962</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3742,34 +3752,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1204</v>
+        <v>5432</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Stamåsen, Stamåsen, Ång</t>
+          <t>Lill-Åsberget, Lill-Åsberget, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>541760</v>
+        <v>542238</v>
       </c>
       <c r="R31" t="n">
-        <v>7063584</v>
+        <v>7063973</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3828,10 +3838,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122730246</v>
+        <v>122741741</v>
       </c>
       <c r="B32" t="n">
-        <v>78766</v>
+        <v>90909</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3840,38 +3850,38 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Lill-Åsberget, Lill-Åsberget, Ång</t>
+          <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>542168</v>
+        <v>542064</v>
       </c>
       <c r="R32" t="n">
-        <v>7063849</v>
+        <v>7063777</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3930,10 +3940,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122730177</v>
+        <v>122729831</v>
       </c>
       <c r="B33" t="n">
-        <v>56688</v>
+        <v>57478</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3942,31 +3952,31 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="M33" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -3975,10 +3985,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>542198</v>
+        <v>542249</v>
       </c>
       <c r="R33" t="n">
-        <v>7063872</v>
+        <v>7063942</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -4011,6 +4021,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-02-24</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Bohål i torrgran, 2m ovan mark. 5 cm ø. Gott om stående död ved i området.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4037,10 +4052,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122732558</v>
+        <v>122741781</v>
       </c>
       <c r="B34" t="n">
-        <v>97317</v>
+        <v>91293</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4049,25 +4064,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>221941</v>
+        <v>2062</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4077,10 +4092,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>541824</v>
+        <v>542068</v>
       </c>
       <c r="R34" t="n">
-        <v>7063603</v>
+        <v>7063778</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4139,10 +4154,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122731109</v>
+        <v>122730246</v>
       </c>
       <c r="B35" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4155,39 +4170,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Stamåsen, Stamåsen, Ång</t>
+          <t>Lill-Åsberget, Lill-Åsberget, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>541940</v>
+        <v>542168</v>
       </c>
       <c r="R35" t="n">
-        <v>7063712</v>
+        <v>7063849</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4220,11 +4230,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-02-24</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Äldre ringhack, gammal tall</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4251,10 +4256,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122729831</v>
+        <v>122741861</v>
       </c>
       <c r="B36" t="n">
-        <v>57478</v>
+        <v>79847</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4267,39 +4272,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Lill-Åsberget, Lill-Åsberget, Ång</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>542249</v>
+        <v>542085</v>
       </c>
       <c r="R36" t="n">
-        <v>7063942</v>
+        <v>7063858</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4332,11 +4332,6 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-02-24</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Bohål i torrgran, 2m ovan mark. 5 cm ø. Gott om stående död ved i området.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4363,10 +4358,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122741488</v>
+        <v>122731014</v>
       </c>
       <c r="B37" t="n">
-        <v>57494</v>
+        <v>79847</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4379,39 +4374,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>542034</v>
+        <v>541940</v>
       </c>
       <c r="R37" t="n">
-        <v>7063681</v>
+        <v>7063713</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4470,10 +4460,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122730042</v>
+        <v>122732631</v>
       </c>
       <c r="B38" t="n">
-        <v>91235</v>
+        <v>88303</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4486,34 +4476,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>658</v>
+        <v>510</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Lill-Åsberget, Lill-Åsberget, Ång</t>
+          <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>542248</v>
+        <v>541768</v>
       </c>
       <c r="R38" t="n">
-        <v>7063927</v>
+        <v>7063586</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4572,10 +4562,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122730595</v>
+        <v>122730829</v>
       </c>
       <c r="B39" t="n">
-        <v>90944</v>
+        <v>78766</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4588,21 +4578,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4612,10 +4602,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>542097</v>
+        <v>542035</v>
       </c>
       <c r="R39" t="n">
-        <v>7063815</v>
+        <v>7063816</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -4674,10 +4664,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122733126</v>
+        <v>122741488</v>
       </c>
       <c r="B40" t="n">
-        <v>78766</v>
+        <v>57494</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4690,34 +4680,39 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>541858</v>
+        <v>542034</v>
       </c>
       <c r="R40" t="n">
-        <v>7063338</v>
+        <v>7063681</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -4776,10 +4771,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122731014</v>
+        <v>122731904</v>
       </c>
       <c r="B41" t="n">
-        <v>79847</v>
+        <v>78766</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4792,21 +4787,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4816,10 +4811,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>541940</v>
+        <v>541908</v>
       </c>
       <c r="R41" t="n">
-        <v>7063713</v>
+        <v>7063682</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -4852,6 +4847,11 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-02-24</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Garnlavsrika partier över hela sluttningen</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4878,10 +4878,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122742207</v>
+        <v>122741763</v>
       </c>
       <c r="B42" t="n">
-        <v>90962</v>
+        <v>90944</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4894,34 +4894,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Lill-Åsberget, Lill-Åsberget, Ång</t>
+          <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>542238</v>
+        <v>542067</v>
       </c>
       <c r="R42" t="n">
-        <v>7063973</v>
+        <v>7063777</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -4980,10 +4980,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122730759</v>
+        <v>122730086</v>
       </c>
       <c r="B43" t="n">
-        <v>91304</v>
+        <v>90944</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4992,38 +4992,38 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1506</v>
+        <v>1202</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Stamåsen, Stamåsen, Ång</t>
+          <t>Lill-Åsberget, Lill-Åsberget, Ång</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>542045</v>
+        <v>542258</v>
       </c>
       <c r="R43" t="n">
-        <v>7063823</v>
+        <v>7063917</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -5082,10 +5082,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122732657</v>
+        <v>122741376</v>
       </c>
       <c r="B44" t="n">
-        <v>90909</v>
+        <v>91235</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5094,25 +5094,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>5447</v>
+        <v>658</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5122,10 +5122,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>541761</v>
+        <v>541997</v>
       </c>
       <c r="R44" t="n">
-        <v>7063583</v>
+        <v>7063580</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>
@@ -5184,10 +5184,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122741376</v>
+        <v>122732264</v>
       </c>
       <c r="B45" t="n">
-        <v>91235</v>
+        <v>82553</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5200,21 +5200,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>658</v>
+        <v>1312</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5224,10 +5224,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>541997</v>
+        <v>541883</v>
       </c>
       <c r="R45" t="n">
-        <v>7063580</v>
+        <v>7063653</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -5286,7 +5286,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122741741</v>
+        <v>122732330</v>
       </c>
       <c r="B46" t="n">
         <v>90909</v>
@@ -5326,10 +5326,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>542064</v>
+        <v>541875</v>
       </c>
       <c r="R46" t="n">
-        <v>7063777</v>
+        <v>7063622</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>

--- a/artfynd/A 3110-2025 artfynd.xlsx
+++ b/artfynd/A 3110-2025 artfynd.xlsx
@@ -3435,10 +3435,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122731193</v>
+        <v>122733041</v>
       </c>
       <c r="B28" t="n">
-        <v>91342</v>
+        <v>90962</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3451,16 +3451,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6040186</v>
+        <v>5432</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3470,10 +3475,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>541919</v>
+        <v>541873</v>
       </c>
       <c r="R28" t="n">
-        <v>7063716</v>
+        <v>7063379</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3532,10 +3537,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122733041</v>
+        <v>122731193</v>
       </c>
       <c r="B29" t="n">
-        <v>90962</v>
+        <v>91342</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3548,21 +3553,16 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5432</v>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>Granticka</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3572,10 +3572,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>541873</v>
+        <v>541919</v>
       </c>
       <c r="R29" t="n">
-        <v>7063379</v>
+        <v>7063716</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3838,10 +3838,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122741741</v>
+        <v>122729831</v>
       </c>
       <c r="B32" t="n">
-        <v>90909</v>
+        <v>57478</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3850,38 +3850,43 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Stamåsen, Stamåsen, Ång</t>
+          <t>Lill-Åsberget, Lill-Åsberget, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>542064</v>
+        <v>542249</v>
       </c>
       <c r="R32" t="n">
-        <v>7063777</v>
+        <v>7063942</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3914,6 +3919,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-02-24</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Bohål i torrgran, 2m ovan mark. 5 cm ø. Gott om stående död ved i området.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3940,10 +3950,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122729831</v>
+        <v>122741781</v>
       </c>
       <c r="B33" t="n">
-        <v>57478</v>
+        <v>91293</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3952,43 +3962,38 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>2062</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Lill-Åsberget, Lill-Åsberget, Ång</t>
+          <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>542249</v>
+        <v>542068</v>
       </c>
       <c r="R33" t="n">
-        <v>7063942</v>
+        <v>7063778</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -4021,11 +4026,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-02-24</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Bohål i torrgran, 2m ovan mark. 5 cm ø. Gott om stående död ved i området.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4052,10 +4052,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122741781</v>
+        <v>122741741</v>
       </c>
       <c r="B34" t="n">
-        <v>91293</v>
+        <v>90909</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4064,25 +4064,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>2062</v>
+        <v>5447</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4092,10 +4092,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>542068</v>
+        <v>542064</v>
       </c>
       <c r="R34" t="n">
-        <v>7063778</v>
+        <v>7063777</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4154,10 +4154,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122730246</v>
+        <v>122741861</v>
       </c>
       <c r="B35" t="n">
-        <v>78766</v>
+        <v>79847</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4170,21 +4170,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4194,10 +4194,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>542168</v>
+        <v>542085</v>
       </c>
       <c r="R35" t="n">
-        <v>7063849</v>
+        <v>7063858</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4256,10 +4256,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122741861</v>
+        <v>122730246</v>
       </c>
       <c r="B36" t="n">
-        <v>79847</v>
+        <v>78766</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4272,21 +4272,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4296,10 +4296,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>542085</v>
+        <v>542168</v>
       </c>
       <c r="R36" t="n">
-        <v>7063858</v>
+        <v>7063849</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>

--- a/artfynd/A 3110-2025 artfynd.xlsx
+++ b/artfynd/A 3110-2025 artfynd.xlsx
@@ -1671,10 +1671,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122732487</v>
+        <v>122730759</v>
       </c>
       <c r="B11" t="n">
-        <v>90944</v>
+        <v>91304</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1683,25 +1683,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>1506</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1711,10 +1711,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>541847</v>
+        <v>542045</v>
       </c>
       <c r="R11" t="n">
-        <v>7063615</v>
+        <v>7063823</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1773,10 +1773,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122730759</v>
+        <v>122732487</v>
       </c>
       <c r="B12" t="n">
-        <v>91304</v>
+        <v>90944</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1785,25 +1785,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1506</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1813,10 +1813,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>542045</v>
+        <v>541847</v>
       </c>
       <c r="R12" t="n">
-        <v>7063823</v>
+        <v>7063615</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -4771,10 +4771,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122731904</v>
+        <v>122741763</v>
       </c>
       <c r="B41" t="n">
-        <v>78766</v>
+        <v>90944</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4787,21 +4787,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4811,10 +4811,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>541908</v>
+        <v>542067</v>
       </c>
       <c r="R41" t="n">
-        <v>7063682</v>
+        <v>7063777</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -4847,11 +4847,6 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-02-24</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Garnlavsrika partier över hela sluttningen</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4878,7 +4873,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122741763</v>
+        <v>122730086</v>
       </c>
       <c r="B42" t="n">
         <v>90944</v>
@@ -4914,14 +4909,14 @@
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Stamåsen, Stamåsen, Ång</t>
+          <t>Lill-Åsberget, Lill-Åsberget, Ång</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>542067</v>
+        <v>542258</v>
       </c>
       <c r="R42" t="n">
-        <v>7063777</v>
+        <v>7063917</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -4980,10 +4975,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122730086</v>
+        <v>122741376</v>
       </c>
       <c r="B43" t="n">
-        <v>90944</v>
+        <v>91235</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4996,34 +4991,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Lill-Åsberget, Lill-Åsberget, Ång</t>
+          <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>542258</v>
+        <v>541997</v>
       </c>
       <c r="R43" t="n">
-        <v>7063917</v>
+        <v>7063580</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -5082,10 +5077,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122741376</v>
+        <v>122732264</v>
       </c>
       <c r="B44" t="n">
-        <v>91235</v>
+        <v>82553</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5098,21 +5093,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>658</v>
+        <v>1312</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5122,10 +5117,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>541997</v>
+        <v>541883</v>
       </c>
       <c r="R44" t="n">
-        <v>7063580</v>
+        <v>7063653</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>
@@ -5184,10 +5179,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122732264</v>
+        <v>122731904</v>
       </c>
       <c r="B45" t="n">
-        <v>82553</v>
+        <v>78766</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5200,21 +5195,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5224,10 +5219,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>541883</v>
+        <v>541908</v>
       </c>
       <c r="R45" t="n">
-        <v>7063653</v>
+        <v>7063682</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -5260,6 +5255,11 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-02-24</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Garnlavsrika partier över hela sluttningen</t>
         </is>
       </c>
       <c r="AD45" t="b">

--- a/artfynd/A 3110-2025 artfynd.xlsx
+++ b/artfynd/A 3110-2025 artfynd.xlsx
@@ -1350,10 +1350,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122732653</v>
+        <v>122741741</v>
       </c>
       <c r="B8" t="n">
-        <v>90958</v>
+        <v>90917</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1362,25 +1362,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1204</v>
+        <v>5447</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1390,10 +1390,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>541760</v>
+        <v>542064</v>
       </c>
       <c r="R8" t="n">
-        <v>7063584</v>
+        <v>7063777</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1452,10 +1452,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122731109</v>
+        <v>122730086</v>
       </c>
       <c r="B9" t="n">
-        <v>57478</v>
+        <v>90952</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1468,39 +1468,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Stamåsen, Stamåsen, Ång</t>
+          <t>Lill-Åsberget, Lill-Åsberget, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>541940</v>
+        <v>542258</v>
       </c>
       <c r="R9" t="n">
-        <v>7063712</v>
+        <v>7063917</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1533,11 +1528,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-02-24</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Äldre ringhack, gammal tall</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1564,10 +1554,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122730177</v>
+        <v>122730426</v>
       </c>
       <c r="B10" t="n">
-        <v>56688</v>
+        <v>56680</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1576,25 +1566,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100138</v>
+        <v>102612</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1609,10 +1599,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>542198</v>
+        <v>542150</v>
       </c>
       <c r="R10" t="n">
-        <v>7063872</v>
+        <v>7063805</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1671,10 +1661,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122730759</v>
+        <v>122732958</v>
       </c>
       <c r="B11" t="n">
-        <v>91304</v>
+        <v>57478</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1683,38 +1673,43 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1506</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>542045</v>
+        <v>541820</v>
       </c>
       <c r="R11" t="n">
-        <v>7063823</v>
+        <v>7063439</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1747,6 +1742,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-02-24</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Äldre ringhack, &gt;200-årig tall</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1773,10 +1773,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122732487</v>
+        <v>122732330</v>
       </c>
       <c r="B12" t="n">
-        <v>90944</v>
+        <v>90917</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1785,25 +1785,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1813,10 +1813,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>541847</v>
+        <v>541875</v>
       </c>
       <c r="R12" t="n">
-        <v>7063615</v>
+        <v>7063622</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1875,10 +1875,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122741513</v>
+        <v>122731014</v>
       </c>
       <c r="B13" t="n">
-        <v>90944</v>
+        <v>79847</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1891,21 +1891,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1915,10 +1915,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>542030</v>
+        <v>541940</v>
       </c>
       <c r="R13" t="n">
-        <v>7063685</v>
+        <v>7063713</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1980,7 +1980,7 @@
         <v>122731166</v>
       </c>
       <c r="B14" t="n">
-        <v>90962</v>
+        <v>90970</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2079,10 +2079,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122732558</v>
+        <v>122730829</v>
       </c>
       <c r="B15" t="n">
-        <v>97317</v>
+        <v>78766</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2091,25 +2091,25 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>221941</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2119,10 +2119,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>541824</v>
+        <v>542035</v>
       </c>
       <c r="R15" t="n">
-        <v>7063603</v>
+        <v>7063816</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2184,7 +2184,7 @@
         <v>122730042</v>
       </c>
       <c r="B16" t="n">
-        <v>91235</v>
+        <v>91243</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2283,10 +2283,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122732657</v>
+        <v>122732558</v>
       </c>
       <c r="B17" t="n">
-        <v>90909</v>
+        <v>97325</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2299,21 +2299,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5447</v>
+        <v>221941</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2323,10 +2323,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>541761</v>
+        <v>541824</v>
       </c>
       <c r="R17" t="n">
-        <v>7063583</v>
+        <v>7063603</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2385,10 +2385,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122741643</v>
+        <v>122730004</v>
       </c>
       <c r="B18" t="n">
-        <v>56680</v>
+        <v>90966</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2401,39 +2401,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>102612</v>
+        <v>1204</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Stamåsen, Stamåsen, Ång</t>
+          <t>Lill-Åsberget, Lill-Åsberget, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>542064</v>
+        <v>542251</v>
       </c>
       <c r="R18" t="n">
-        <v>7063749</v>
+        <v>7063915</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2492,10 +2487,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122730595</v>
+        <v>122733041</v>
       </c>
       <c r="B19" t="n">
-        <v>90944</v>
+        <v>90970</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2508,21 +2503,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2532,10 +2527,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>542097</v>
+        <v>541873</v>
       </c>
       <c r="R19" t="n">
-        <v>7063815</v>
+        <v>7063379</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2594,10 +2589,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122733126</v>
+        <v>122742207</v>
       </c>
       <c r="B20" t="n">
-        <v>78766</v>
+        <v>90970</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2610,34 +2605,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Stamåsen, Stamåsen, Ång</t>
+          <t>Lill-Åsberget, Lill-Åsberget, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>541858</v>
+        <v>542238</v>
       </c>
       <c r="R20" t="n">
-        <v>7063338</v>
+        <v>7063973</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2696,10 +2691,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122730426</v>
+        <v>122730246</v>
       </c>
       <c r="B21" t="n">
-        <v>56680</v>
+        <v>78766</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2712,39 +2707,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>102612</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Lill-Åsberget, Lill-Åsberget, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>542150</v>
+        <v>542168</v>
       </c>
       <c r="R21" t="n">
-        <v>7063805</v>
+        <v>7063849</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2803,10 +2793,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122741691</v>
+        <v>122730177</v>
       </c>
       <c r="B22" t="n">
-        <v>56680</v>
+        <v>56688</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2815,25 +2805,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>102612</v>
+        <v>100138</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2844,14 +2834,14 @@
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Stamåsen, Stamåsen, Ång</t>
+          <t>Lill-Åsberget, Lill-Åsberget, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>542063</v>
+        <v>542198</v>
       </c>
       <c r="R22" t="n">
-        <v>7063786</v>
+        <v>7063872</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2910,10 +2900,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122732584</v>
+        <v>122732817</v>
       </c>
       <c r="B23" t="n">
-        <v>97311</v>
+        <v>56680</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2922,38 +2912,43 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>221945</v>
+        <v>102612</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>541821</v>
+        <v>541803</v>
       </c>
       <c r="R23" t="n">
-        <v>7063616</v>
+        <v>7063479</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -3012,10 +3007,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122730499</v>
+        <v>122731109</v>
       </c>
       <c r="B24" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3028,34 +3023,39 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Lill-Åsberget, Lill-Åsberget, Ång</t>
+          <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>542132</v>
+        <v>541940</v>
       </c>
       <c r="R24" t="n">
-        <v>7063797</v>
+        <v>7063712</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3088,6 +3088,11 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-02-24</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Äldre ringhack, gammal tall</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3114,7 +3119,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122732958</v>
+        <v>122729831</v>
       </c>
       <c r="B25" t="n">
         <v>57478</v>
@@ -3150,19 +3155,19 @@
       <c r="I25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Stamåsen, Stamåsen, Ång</t>
+          <t>Lill-Åsberget, Lill-Åsberget, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>541820</v>
+        <v>542249</v>
       </c>
       <c r="R25" t="n">
-        <v>7063439</v>
+        <v>7063942</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3199,7 +3204,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Äldre ringhack, &gt;200-årig tall</t>
+          <t>Bohål i torrgran, 2m ovan mark. 5 cm ø. Gott om stående död ved i området.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3226,10 +3231,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122732817</v>
+        <v>122732584</v>
       </c>
       <c r="B26" t="n">
-        <v>56680</v>
+        <v>97319</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3238,43 +3243,38 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>102612</v>
+        <v>221945</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>541803</v>
+        <v>541821</v>
       </c>
       <c r="R26" t="n">
-        <v>7063479</v>
+        <v>7063616</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3333,10 +3333,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122730234</v>
+        <v>122741691</v>
       </c>
       <c r="B27" t="n">
-        <v>79847</v>
+        <v>56680</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3349,34 +3349,39 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6458</v>
+        <v>102612</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Lill-Åsberget, Lill-Åsberget, Ång</t>
+          <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>542187</v>
+        <v>542063</v>
       </c>
       <c r="R27" t="n">
-        <v>7063885</v>
+        <v>7063786</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3435,10 +3440,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122733041</v>
+        <v>122741513</v>
       </c>
       <c r="B28" t="n">
-        <v>90962</v>
+        <v>90952</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3451,21 +3456,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3475,10 +3480,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>541873</v>
+        <v>542030</v>
       </c>
       <c r="R28" t="n">
-        <v>7063379</v>
+        <v>7063685</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3537,10 +3542,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122731193</v>
+        <v>122732264</v>
       </c>
       <c r="B29" t="n">
-        <v>91342</v>
+        <v>82553</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3553,16 +3558,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6040186</v>
+        <v>1312</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3572,10 +3582,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>541919</v>
+        <v>541883</v>
       </c>
       <c r="R29" t="n">
-        <v>7063716</v>
+        <v>7063653</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3634,10 +3644,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122730004</v>
+        <v>122741643</v>
       </c>
       <c r="B30" t="n">
-        <v>90958</v>
+        <v>56680</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3650,34 +3660,39 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1204</v>
+        <v>102612</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Lill-Åsberget, Lill-Åsberget, Ång</t>
+          <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>542251</v>
+        <v>542064</v>
       </c>
       <c r="R30" t="n">
-        <v>7063915</v>
+        <v>7063749</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3736,10 +3751,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122742207</v>
+        <v>122732487</v>
       </c>
       <c r="B31" t="n">
-        <v>90962</v>
+        <v>90952</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3752,34 +3767,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Lill-Åsberget, Lill-Åsberget, Ång</t>
+          <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>542238</v>
+        <v>541847</v>
       </c>
       <c r="R31" t="n">
-        <v>7063973</v>
+        <v>7063615</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3838,10 +3853,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122729831</v>
+        <v>122732657</v>
       </c>
       <c r="B32" t="n">
-        <v>57478</v>
+        <v>90917</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3850,43 +3865,38 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Lill-Åsberget, Lill-Åsberget, Ång</t>
+          <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>542249</v>
+        <v>541761</v>
       </c>
       <c r="R32" t="n">
-        <v>7063942</v>
+        <v>7063583</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3919,11 +3929,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-02-24</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Bohål i torrgran, 2m ovan mark. 5 cm ø. Gott om stående död ved i området.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3953,7 +3958,7 @@
         <v>122741781</v>
       </c>
       <c r="B33" t="n">
-        <v>91293</v>
+        <v>91301</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4052,10 +4057,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122741741</v>
+        <v>122741861</v>
       </c>
       <c r="B34" t="n">
-        <v>90909</v>
+        <v>79847</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4064,38 +4069,38 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5447</v>
+        <v>6458</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Stamåsen, Stamåsen, Ång</t>
+          <t>Lill-Åsberget, Lill-Åsberget, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>542064</v>
+        <v>542085</v>
       </c>
       <c r="R34" t="n">
-        <v>7063777</v>
+        <v>7063858</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4154,7 +4159,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122741861</v>
+        <v>122730234</v>
       </c>
       <c r="B35" t="n">
         <v>79847</v>
@@ -4194,10 +4199,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>542085</v>
+        <v>542187</v>
       </c>
       <c r="R35" t="n">
-        <v>7063858</v>
+        <v>7063885</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4256,10 +4261,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122730246</v>
+        <v>122732653</v>
       </c>
       <c r="B36" t="n">
-        <v>78766</v>
+        <v>90966</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4272,34 +4277,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Lill-Åsberget, Lill-Åsberget, Ång</t>
+          <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>542168</v>
+        <v>541760</v>
       </c>
       <c r="R36" t="n">
-        <v>7063849</v>
+        <v>7063584</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4358,10 +4363,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122731014</v>
+        <v>122741376</v>
       </c>
       <c r="B37" t="n">
-        <v>79847</v>
+        <v>91243</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4374,21 +4379,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4398,10 +4403,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>541940</v>
+        <v>541997</v>
       </c>
       <c r="R37" t="n">
-        <v>7063713</v>
+        <v>7063580</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4460,10 +4465,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122732631</v>
+        <v>122733126</v>
       </c>
       <c r="B38" t="n">
-        <v>88303</v>
+        <v>78766</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4476,21 +4481,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>510</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4500,10 +4505,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>541768</v>
+        <v>541858</v>
       </c>
       <c r="R38" t="n">
-        <v>7063586</v>
+        <v>7063338</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4562,7 +4567,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122730829</v>
+        <v>122730499</v>
       </c>
       <c r="B39" t="n">
         <v>78766</v>
@@ -4598,14 +4603,14 @@
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Stamåsen, Stamåsen, Ång</t>
+          <t>Lill-Åsberget, Lill-Åsberget, Ång</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>542035</v>
+        <v>542132</v>
       </c>
       <c r="R39" t="n">
-        <v>7063816</v>
+        <v>7063797</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -4664,10 +4669,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122741488</v>
+        <v>122730759</v>
       </c>
       <c r="B40" t="n">
-        <v>57494</v>
+        <v>91312</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4676,43 +4681,38 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100049</v>
+        <v>1506</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P40" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>542034</v>
+        <v>542045</v>
       </c>
       <c r="R40" t="n">
-        <v>7063681</v>
+        <v>7063823</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -4771,10 +4771,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122741763</v>
+        <v>122730595</v>
       </c>
       <c r="B41" t="n">
-        <v>90944</v>
+        <v>90952</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4811,10 +4811,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>542067</v>
+        <v>542097</v>
       </c>
       <c r="R41" t="n">
-        <v>7063777</v>
+        <v>7063815</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -4873,10 +4873,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122730086</v>
+        <v>122732631</v>
       </c>
       <c r="B42" t="n">
-        <v>90944</v>
+        <v>88303</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4889,34 +4889,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1202</v>
+        <v>510</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Lill-Åsberget, Lill-Åsberget, Ång</t>
+          <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>542258</v>
+        <v>541768</v>
       </c>
       <c r="R42" t="n">
-        <v>7063917</v>
+        <v>7063586</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -4975,10 +4975,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122741376</v>
+        <v>122731193</v>
       </c>
       <c r="B43" t="n">
-        <v>91235</v>
+        <v>91350</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4991,21 +4991,16 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>658</v>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>Rosenticka</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5015,10 +5010,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>541997</v>
+        <v>541919</v>
       </c>
       <c r="R43" t="n">
-        <v>7063580</v>
+        <v>7063716</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -5077,10 +5072,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122732264</v>
+        <v>122731904</v>
       </c>
       <c r="B44" t="n">
-        <v>82553</v>
+        <v>78766</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5093,21 +5088,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5117,10 +5112,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>541883</v>
+        <v>541908</v>
       </c>
       <c r="R44" t="n">
-        <v>7063653</v>
+        <v>7063682</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>
@@ -5153,6 +5148,11 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-02-24</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Garnlavsrika partier över hela sluttningen</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5179,10 +5179,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122731904</v>
+        <v>122741763</v>
       </c>
       <c r="B45" t="n">
-        <v>78766</v>
+        <v>90952</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5195,21 +5195,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5219,10 +5219,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>541908</v>
+        <v>542067</v>
       </c>
       <c r="R45" t="n">
-        <v>7063682</v>
+        <v>7063777</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -5255,11 +5255,6 @@
       <c r="AA45" t="inlineStr">
         <is>
           <t>2025-02-24</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Garnlavsrika partier över hela sluttningen</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5286,10 +5281,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122732330</v>
+        <v>122741488</v>
       </c>
       <c r="B46" t="n">
-        <v>90909</v>
+        <v>57494</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5298,38 +5293,43 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>541875</v>
+        <v>542034</v>
       </c>
       <c r="R46" t="n">
-        <v>7063622</v>
+        <v>7063681</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>

--- a/artfynd/A 3110-2025 artfynd.xlsx
+++ b/artfynd/A 3110-2025 artfynd.xlsx
@@ -2283,10 +2283,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122732558</v>
+        <v>122733041</v>
       </c>
       <c r="B17" t="n">
-        <v>97325</v>
+        <v>90970</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2295,25 +2295,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221941</v>
+        <v>5432</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2323,10 +2323,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>541824</v>
+        <v>541873</v>
       </c>
       <c r="R17" t="n">
-        <v>7063603</v>
+        <v>7063379</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2385,10 +2385,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122730004</v>
+        <v>122732558</v>
       </c>
       <c r="B18" t="n">
-        <v>90966</v>
+        <v>97325</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2397,38 +2397,38 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1204</v>
+        <v>221941</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Lill-Åsberget, Lill-Åsberget, Ång</t>
+          <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>542251</v>
+        <v>541824</v>
       </c>
       <c r="R18" t="n">
-        <v>7063915</v>
+        <v>7063603</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2487,10 +2487,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122733041</v>
+        <v>122730004</v>
       </c>
       <c r="B19" t="n">
-        <v>90970</v>
+        <v>90966</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2503,34 +2503,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5432</v>
+        <v>1204</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Stamåsen, Stamåsen, Ång</t>
+          <t>Lill-Åsberget, Lill-Åsberget, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>541873</v>
+        <v>542251</v>
       </c>
       <c r="R19" t="n">
-        <v>7063379</v>
+        <v>7063915</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -4057,10 +4057,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122741861</v>
+        <v>122732653</v>
       </c>
       <c r="B34" t="n">
-        <v>79847</v>
+        <v>90966</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4073,34 +4073,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6458</v>
+        <v>1204</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Lill-Åsberget, Lill-Åsberget, Ång</t>
+          <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>542085</v>
+        <v>541760</v>
       </c>
       <c r="R34" t="n">
-        <v>7063858</v>
+        <v>7063584</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4159,7 +4159,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122730234</v>
+        <v>122741861</v>
       </c>
       <c r="B35" t="n">
         <v>79847</v>
@@ -4199,10 +4199,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>542187</v>
+        <v>542085</v>
       </c>
       <c r="R35" t="n">
-        <v>7063885</v>
+        <v>7063858</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4261,10 +4261,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122732653</v>
+        <v>122730234</v>
       </c>
       <c r="B36" t="n">
-        <v>90966</v>
+        <v>79847</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4277,34 +4277,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1204</v>
+        <v>6458</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Stamåsen, Stamåsen, Ång</t>
+          <t>Lill-Åsberget, Lill-Åsberget, Ång</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>541760</v>
+        <v>542187</v>
       </c>
       <c r="R36" t="n">
-        <v>7063584</v>
+        <v>7063885</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>

--- a/artfynd/A 3110-2025 artfynd.xlsx
+++ b/artfynd/A 3110-2025 artfynd.xlsx
@@ -1350,10 +1350,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122741741</v>
+        <v>122731166</v>
       </c>
       <c r="B8" t="n">
-        <v>90917</v>
+        <v>90970</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1362,25 +1362,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5447</v>
+        <v>5432</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1390,10 +1390,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>542064</v>
+        <v>541922</v>
       </c>
       <c r="R8" t="n">
-        <v>7063777</v>
+        <v>7063717</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1452,10 +1452,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122730086</v>
+        <v>122731109</v>
       </c>
       <c r="B9" t="n">
-        <v>90952</v>
+        <v>57478</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1468,34 +1468,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Lill-Åsberget, Lill-Åsberget, Ång</t>
+          <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>542258</v>
+        <v>541940</v>
       </c>
       <c r="R9" t="n">
-        <v>7063917</v>
+        <v>7063712</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1528,6 +1533,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-02-24</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Äldre ringhack, gammal tall</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1554,7 +1564,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122730426</v>
+        <v>122732817</v>
       </c>
       <c r="B10" t="n">
         <v>56680</v>
@@ -1595,14 +1605,14 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Lill-Åsberget, Lill-Åsberget, Ång</t>
+          <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>542150</v>
+        <v>541803</v>
       </c>
       <c r="R10" t="n">
-        <v>7063805</v>
+        <v>7063479</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1661,10 +1671,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122732958</v>
+        <v>122741376</v>
       </c>
       <c r="B11" t="n">
-        <v>57478</v>
+        <v>91243</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1677,39 +1687,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>541820</v>
+        <v>541997</v>
       </c>
       <c r="R11" t="n">
-        <v>7063439</v>
+        <v>7063580</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1742,11 +1747,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-02-24</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Äldre ringhack, &gt;200-årig tall</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1773,10 +1773,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122732330</v>
+        <v>122730759</v>
       </c>
       <c r="B12" t="n">
-        <v>90917</v>
+        <v>91312</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1785,25 +1785,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5447</v>
+        <v>1506</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1813,10 +1813,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>541875</v>
+        <v>542045</v>
       </c>
       <c r="R12" t="n">
-        <v>7063622</v>
+        <v>7063823</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1875,10 +1875,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122731014</v>
+        <v>122741781</v>
       </c>
       <c r="B13" t="n">
-        <v>79847</v>
+        <v>91301</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1887,25 +1887,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>2062</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1915,10 +1915,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>541940</v>
+        <v>542068</v>
       </c>
       <c r="R13" t="n">
-        <v>7063713</v>
+        <v>7063778</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1977,10 +1977,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122731166</v>
+        <v>122730829</v>
       </c>
       <c r="B14" t="n">
-        <v>90970</v>
+        <v>78766</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1993,21 +1993,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2017,10 +2017,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>541922</v>
+        <v>542035</v>
       </c>
       <c r="R14" t="n">
-        <v>7063717</v>
+        <v>7063816</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2079,10 +2079,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122730829</v>
+        <v>122742207</v>
       </c>
       <c r="B15" t="n">
-        <v>78766</v>
+        <v>90970</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2095,34 +2095,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Stamåsen, Stamåsen, Ång</t>
+          <t>Lill-Åsberget, Lill-Åsberget, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>542035</v>
+        <v>542238</v>
       </c>
       <c r="R15" t="n">
-        <v>7063816</v>
+        <v>7063973</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2181,10 +2181,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122730042</v>
+        <v>122733041</v>
       </c>
       <c r="B16" t="n">
-        <v>91243</v>
+        <v>90970</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2197,34 +2197,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>658</v>
+        <v>5432</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Lill-Åsberget, Lill-Åsberget, Ång</t>
+          <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>542248</v>
+        <v>541873</v>
       </c>
       <c r="R16" t="n">
-        <v>7063927</v>
+        <v>7063379</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2283,10 +2283,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122733041</v>
+        <v>122732330</v>
       </c>
       <c r="B17" t="n">
-        <v>90970</v>
+        <v>90917</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2295,25 +2295,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5432</v>
+        <v>5447</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2323,10 +2323,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>541873</v>
+        <v>541875</v>
       </c>
       <c r="R17" t="n">
-        <v>7063379</v>
+        <v>7063622</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2385,10 +2385,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122732558</v>
+        <v>122731904</v>
       </c>
       <c r="B18" t="n">
-        <v>97325</v>
+        <v>78766</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2397,25 +2397,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>221941</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2425,10 +2425,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>541824</v>
+        <v>541908</v>
       </c>
       <c r="R18" t="n">
-        <v>7063603</v>
+        <v>7063682</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2461,6 +2461,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-02-24</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Garnlavsrika partier över hela sluttningen</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2487,10 +2492,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122730004</v>
+        <v>122730234</v>
       </c>
       <c r="B19" t="n">
-        <v>90966</v>
+        <v>79847</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2503,21 +2508,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1204</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2527,10 +2532,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>542251</v>
+        <v>542187</v>
       </c>
       <c r="R19" t="n">
-        <v>7063915</v>
+        <v>7063885</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2589,10 +2594,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122742207</v>
+        <v>122741763</v>
       </c>
       <c r="B20" t="n">
-        <v>90970</v>
+        <v>90952</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2605,34 +2610,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Lill-Åsberget, Lill-Åsberget, Ång</t>
+          <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>542238</v>
+        <v>542067</v>
       </c>
       <c r="R20" t="n">
-        <v>7063973</v>
+        <v>7063777</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2691,10 +2696,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122730246</v>
+        <v>122731193</v>
       </c>
       <c r="B21" t="n">
-        <v>78766</v>
+        <v>91350</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2707,34 +2712,29 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Lill-Åsberget, Lill-Åsberget, Ång</t>
+          <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>542168</v>
+        <v>541919</v>
       </c>
       <c r="R21" t="n">
-        <v>7063849</v>
+        <v>7063716</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2793,10 +2793,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122730177</v>
+        <v>122741488</v>
       </c>
       <c r="B22" t="n">
-        <v>56688</v>
+        <v>57494</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2805,43 +2805,43 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Lill-Åsberget, Lill-Åsberget, Ång</t>
+          <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>542198</v>
+        <v>542034</v>
       </c>
       <c r="R22" t="n">
-        <v>7063872</v>
+        <v>7063681</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2900,10 +2900,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122732817</v>
+        <v>122741513</v>
       </c>
       <c r="B23" t="n">
-        <v>56680</v>
+        <v>90952</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2916,39 +2916,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>102612</v>
+        <v>1202</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>541803</v>
+        <v>542030</v>
       </c>
       <c r="R23" t="n">
-        <v>7063479</v>
+        <v>7063685</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -3007,10 +3002,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122731109</v>
+        <v>122730004</v>
       </c>
       <c r="B24" t="n">
-        <v>57478</v>
+        <v>90966</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3023,39 +3018,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>1204</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Stamåsen, Stamåsen, Ång</t>
+          <t>Lill-Åsberget, Lill-Åsberget, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>541940</v>
+        <v>542251</v>
       </c>
       <c r="R24" t="n">
-        <v>7063712</v>
+        <v>7063915</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3088,11 +3078,6 @@
       <c r="AA24" t="inlineStr">
         <is>
           <t>2025-02-24</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Äldre ringhack, gammal tall</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3119,10 +3104,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122729831</v>
+        <v>122733126</v>
       </c>
       <c r="B25" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3135,39 +3120,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Lill-Åsberget, Lill-Åsberget, Ång</t>
+          <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>542249</v>
+        <v>541858</v>
       </c>
       <c r="R25" t="n">
-        <v>7063942</v>
+        <v>7063338</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3200,11 +3180,6 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2025-02-24</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Bohål i torrgran, 2m ovan mark. 5 cm ø. Gott om stående död ved i området.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3231,10 +3206,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122732584</v>
+        <v>122730499</v>
       </c>
       <c r="B26" t="n">
-        <v>97319</v>
+        <v>78766</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3243,38 +3218,38 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Stamåsen, Stamåsen, Ång</t>
+          <t>Lill-Åsberget, Lill-Åsberget, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>541821</v>
+        <v>542132</v>
       </c>
       <c r="R26" t="n">
-        <v>7063616</v>
+        <v>7063797</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3333,10 +3308,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122741691</v>
+        <v>122730246</v>
       </c>
       <c r="B27" t="n">
-        <v>56680</v>
+        <v>78766</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3349,39 +3324,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>102612</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Stamåsen, Stamåsen, Ång</t>
+          <t>Lill-Åsberget, Lill-Åsberget, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>542063</v>
+        <v>542168</v>
       </c>
       <c r="R27" t="n">
-        <v>7063786</v>
+        <v>7063849</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3440,7 +3410,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122741513</v>
+        <v>122730086</v>
       </c>
       <c r="B28" t="n">
         <v>90952</v>
@@ -3476,14 +3446,14 @@
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Stamåsen, Stamåsen, Ång</t>
+          <t>Lill-Åsberget, Lill-Åsberget, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>542030</v>
+        <v>542258</v>
       </c>
       <c r="R28" t="n">
-        <v>7063685</v>
+        <v>7063917</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3542,10 +3512,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122732264</v>
+        <v>122732653</v>
       </c>
       <c r="B29" t="n">
-        <v>82553</v>
+        <v>90966</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3558,21 +3528,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1312</v>
+        <v>1204</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3582,10 +3552,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>541883</v>
+        <v>541760</v>
       </c>
       <c r="R29" t="n">
-        <v>7063653</v>
+        <v>7063584</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3644,10 +3614,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122741643</v>
+        <v>122741861</v>
       </c>
       <c r="B30" t="n">
-        <v>56680</v>
+        <v>79847</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3660,39 +3630,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>102612</v>
+        <v>6458</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Stamåsen, Stamåsen, Ång</t>
+          <t>Lill-Åsberget, Lill-Åsberget, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>542064</v>
+        <v>542085</v>
       </c>
       <c r="R30" t="n">
-        <v>7063749</v>
+        <v>7063858</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3751,10 +3716,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122732487</v>
+        <v>122731014</v>
       </c>
       <c r="B31" t="n">
-        <v>90952</v>
+        <v>79847</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3767,21 +3732,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3791,10 +3756,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>541847</v>
+        <v>541940</v>
       </c>
       <c r="R31" t="n">
-        <v>7063615</v>
+        <v>7063713</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3853,10 +3818,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122732657</v>
+        <v>122732487</v>
       </c>
       <c r="B32" t="n">
-        <v>90917</v>
+        <v>90952</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3865,25 +3830,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3893,10 +3858,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>541761</v>
+        <v>541847</v>
       </c>
       <c r="R32" t="n">
-        <v>7063583</v>
+        <v>7063615</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3955,10 +3920,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122741781</v>
+        <v>122741741</v>
       </c>
       <c r="B33" t="n">
-        <v>91301</v>
+        <v>90917</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3967,25 +3932,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>2062</v>
+        <v>5447</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3995,10 +3960,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>542068</v>
+        <v>542064</v>
       </c>
       <c r="R33" t="n">
-        <v>7063778</v>
+        <v>7063777</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -4057,10 +4022,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122732653</v>
+        <v>122730177</v>
       </c>
       <c r="B34" t="n">
-        <v>90966</v>
+        <v>56688</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4069,38 +4034,43 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1204</v>
+        <v>100138</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Stamåsen, Stamåsen, Ång</t>
+          <t>Lill-Åsberget, Lill-Åsberget, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>541760</v>
+        <v>542198</v>
       </c>
       <c r="R34" t="n">
-        <v>7063584</v>
+        <v>7063872</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4159,10 +4129,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122741861</v>
+        <v>122741643</v>
       </c>
       <c r="B35" t="n">
-        <v>79847</v>
+        <v>56680</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4175,34 +4145,39 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6458</v>
+        <v>102612</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Lill-Åsberget, Lill-Åsberget, Ång</t>
+          <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>542085</v>
+        <v>542064</v>
       </c>
       <c r="R35" t="n">
-        <v>7063858</v>
+        <v>7063749</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4261,10 +4236,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122730234</v>
+        <v>122730426</v>
       </c>
       <c r="B36" t="n">
-        <v>79847</v>
+        <v>56680</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4277,34 +4252,39 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6458</v>
+        <v>102612</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Lill-Åsberget, Lill-Åsberget, Ång</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>542187</v>
+        <v>542150</v>
       </c>
       <c r="R36" t="n">
-        <v>7063885</v>
+        <v>7063805</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4363,10 +4343,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122741376</v>
+        <v>122732657</v>
       </c>
       <c r="B37" t="n">
-        <v>91243</v>
+        <v>90917</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4375,25 +4355,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>658</v>
+        <v>5447</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4403,10 +4383,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>541997</v>
+        <v>541761</v>
       </c>
       <c r="R37" t="n">
-        <v>7063580</v>
+        <v>7063583</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4465,10 +4445,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122733126</v>
+        <v>122729831</v>
       </c>
       <c r="B38" t="n">
-        <v>78766</v>
+        <v>57478</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4481,34 +4461,39 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Stamåsen, Stamåsen, Ång</t>
+          <t>Lill-Åsberget, Lill-Åsberget, Ång</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>541858</v>
+        <v>542249</v>
       </c>
       <c r="R38" t="n">
-        <v>7063338</v>
+        <v>7063942</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4541,6 +4526,11 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-02-24</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Bohål i torrgran, 2m ovan mark. 5 cm ø. Gott om stående död ved i området.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4567,10 +4557,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122730499</v>
+        <v>122741691</v>
       </c>
       <c r="B39" t="n">
-        <v>78766</v>
+        <v>56680</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4583,34 +4573,39 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>102612</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Lill-Åsberget, Lill-Åsberget, Ång</t>
+          <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>542132</v>
+        <v>542063</v>
       </c>
       <c r="R39" t="n">
-        <v>7063797</v>
+        <v>7063786</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -4669,10 +4664,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122730759</v>
+        <v>122732264</v>
       </c>
       <c r="B40" t="n">
-        <v>91312</v>
+        <v>82553</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4681,25 +4676,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1506</v>
+        <v>1312</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4709,10 +4704,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>542045</v>
+        <v>541883</v>
       </c>
       <c r="R40" t="n">
-        <v>7063823</v>
+        <v>7063653</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -4771,10 +4766,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122730595</v>
+        <v>122732584</v>
       </c>
       <c r="B41" t="n">
-        <v>90952</v>
+        <v>97319</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4783,25 +4778,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1202</v>
+        <v>221945</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4811,10 +4806,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>542097</v>
+        <v>541821</v>
       </c>
       <c r="R41" t="n">
-        <v>7063815</v>
+        <v>7063616</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -4873,10 +4868,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122732631</v>
+        <v>122730042</v>
       </c>
       <c r="B42" t="n">
-        <v>88303</v>
+        <v>91243</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4889,34 +4884,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>510</v>
+        <v>658</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Stamåsen, Stamåsen, Ång</t>
+          <t>Lill-Åsberget, Lill-Åsberget, Ång</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>541768</v>
+        <v>542248</v>
       </c>
       <c r="R42" t="n">
-        <v>7063586</v>
+        <v>7063927</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -4975,10 +4970,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122731193</v>
+        <v>122730595</v>
       </c>
       <c r="B43" t="n">
-        <v>91350</v>
+        <v>90952</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4991,16 +4986,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6040186</v>
+        <v>1202</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5010,10 +5010,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>541919</v>
+        <v>542097</v>
       </c>
       <c r="R43" t="n">
-        <v>7063716</v>
+        <v>7063815</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -5072,10 +5072,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122731904</v>
+        <v>122732631</v>
       </c>
       <c r="B44" t="n">
-        <v>78766</v>
+        <v>88303</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5088,21 +5088,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>510</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5112,10 +5112,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>541908</v>
+        <v>541768</v>
       </c>
       <c r="R44" t="n">
-        <v>7063682</v>
+        <v>7063586</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>
@@ -5148,11 +5148,6 @@
       <c r="AA44" t="inlineStr">
         <is>
           <t>2025-02-24</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Garnlavsrika partier över hela sluttningen</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5179,10 +5174,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122741763</v>
+        <v>122732558</v>
       </c>
       <c r="B45" t="n">
-        <v>90952</v>
+        <v>97325</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5191,25 +5186,25 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1202</v>
+        <v>221941</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5219,10 +5214,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>542067</v>
+        <v>541824</v>
       </c>
       <c r="R45" t="n">
-        <v>7063777</v>
+        <v>7063603</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -5281,10 +5276,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122741488</v>
+        <v>122732958</v>
       </c>
       <c r="B46" t="n">
-        <v>57494</v>
+        <v>57478</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5297,16 +5292,16 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -5317,7 +5312,7 @@
       <c r="I46" t="inlineStr"/>
       <c r="M46" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
@@ -5326,10 +5321,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>542034</v>
+        <v>541820</v>
       </c>
       <c r="R46" t="n">
-        <v>7063681</v>
+        <v>7063439</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>
@@ -5362,6 +5357,11 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-02-24</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Äldre ringhack, &gt;200-årig tall</t>
         </is>
       </c>
       <c r="AD46" t="b">

--- a/artfynd/A 3110-2025 artfynd.xlsx
+++ b/artfynd/A 3110-2025 artfynd.xlsx
@@ -3818,10 +3818,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122732487</v>
+        <v>122741741</v>
       </c>
       <c r="B32" t="n">
-        <v>90952</v>
+        <v>90917</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3830,25 +3830,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3858,10 +3858,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>541847</v>
+        <v>542064</v>
       </c>
       <c r="R32" t="n">
-        <v>7063615</v>
+        <v>7063777</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3920,10 +3920,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122741741</v>
+        <v>122730177</v>
       </c>
       <c r="B33" t="n">
-        <v>90917</v>
+        <v>56688</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3936,34 +3936,39 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>5447</v>
+        <v>100138</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Stamåsen, Stamåsen, Ång</t>
+          <t>Lill-Åsberget, Lill-Åsberget, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>542064</v>
+        <v>542198</v>
       </c>
       <c r="R33" t="n">
-        <v>7063777</v>
+        <v>7063872</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -4022,10 +4027,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122730177</v>
+        <v>122741643</v>
       </c>
       <c r="B34" t="n">
-        <v>56688</v>
+        <v>56680</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4034,25 +4039,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100138</v>
+        <v>102612</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4063,14 +4068,14 @@
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Lill-Åsberget, Lill-Åsberget, Ång</t>
+          <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>542198</v>
+        <v>542064</v>
       </c>
       <c r="R34" t="n">
-        <v>7063872</v>
+        <v>7063749</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4129,10 +4134,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122741643</v>
+        <v>122732487</v>
       </c>
       <c r="B35" t="n">
-        <v>56680</v>
+        <v>90952</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4145,39 +4150,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>102612</v>
+        <v>1202</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>542064</v>
+        <v>541847</v>
       </c>
       <c r="R35" t="n">
-        <v>7063749</v>
+        <v>7063615</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>

--- a/artfynd/A 3110-2025 artfynd.xlsx
+++ b/artfynd/A 3110-2025 artfynd.xlsx
@@ -2594,10 +2594,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122741763</v>
+        <v>122731193</v>
       </c>
       <c r="B20" t="n">
-        <v>90952</v>
+        <v>91350</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2610,21 +2610,16 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1202</v>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>Ullticka</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2634,10 +2629,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>542067</v>
+        <v>541919</v>
       </c>
       <c r="R20" t="n">
-        <v>7063777</v>
+        <v>7063716</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2696,10 +2691,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122731193</v>
+        <v>122741763</v>
       </c>
       <c r="B21" t="n">
-        <v>91350</v>
+        <v>90952</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2712,16 +2707,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6040186</v>
+        <v>1202</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2731,10 +2731,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>541919</v>
+        <v>542067</v>
       </c>
       <c r="R21" t="n">
-        <v>7063716</v>
+        <v>7063777</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>

--- a/artfynd/A 3110-2025 artfynd.xlsx
+++ b/artfynd/A 3110-2025 artfynd.xlsx
@@ -1350,10 +1350,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122731166</v>
+        <v>122741861</v>
       </c>
       <c r="B8" t="n">
-        <v>90970</v>
+        <v>79847</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1366,34 +1366,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Stamåsen, Stamåsen, Ång</t>
+          <t>Lill-Åsberget, Lill-Åsberget, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>541922</v>
+        <v>542085</v>
       </c>
       <c r="R8" t="n">
-        <v>7063717</v>
+        <v>7063858</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1452,10 +1452,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122731109</v>
+        <v>122730829</v>
       </c>
       <c r="B9" t="n">
-        <v>57478</v>
+        <v>78766</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1468,39 +1468,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>541940</v>
+        <v>542035</v>
       </c>
       <c r="R9" t="n">
-        <v>7063712</v>
+        <v>7063816</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1533,11 +1528,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-02-24</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Äldre ringhack, gammal tall</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1564,10 +1554,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122732817</v>
+        <v>122732330</v>
       </c>
       <c r="B10" t="n">
-        <v>56680</v>
+        <v>90917</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1576,43 +1566,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>102612</v>
+        <v>5447</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>541803</v>
+        <v>541875</v>
       </c>
       <c r="R10" t="n">
-        <v>7063479</v>
+        <v>7063622</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1671,10 +1656,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122741376</v>
+        <v>122732817</v>
       </c>
       <c r="B11" t="n">
-        <v>91243</v>
+        <v>56680</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1687,34 +1672,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>658</v>
+        <v>102612</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>541997</v>
+        <v>541803</v>
       </c>
       <c r="R11" t="n">
-        <v>7063580</v>
+        <v>7063479</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1773,10 +1763,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122730759</v>
+        <v>122731193</v>
       </c>
       <c r="B12" t="n">
-        <v>91312</v>
+        <v>91350</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1785,25 +1775,20 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1506</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Ostticka</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1813,10 +1798,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>542045</v>
+        <v>541919</v>
       </c>
       <c r="R12" t="n">
-        <v>7063823</v>
+        <v>7063716</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1875,10 +1860,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122741781</v>
+        <v>122730759</v>
       </c>
       <c r="B13" t="n">
-        <v>91301</v>
+        <v>91312</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1891,21 +1876,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2062</v>
+        <v>1506</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1915,10 +1900,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>542068</v>
+        <v>542045</v>
       </c>
       <c r="R13" t="n">
-        <v>7063778</v>
+        <v>7063823</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1977,10 +1962,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122730829</v>
+        <v>122732653</v>
       </c>
       <c r="B14" t="n">
-        <v>78766</v>
+        <v>90966</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1993,21 +1978,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2017,10 +2002,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>542035</v>
+        <v>541760</v>
       </c>
       <c r="R14" t="n">
-        <v>7063816</v>
+        <v>7063584</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2079,10 +2064,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122742207</v>
+        <v>122730595</v>
       </c>
       <c r="B15" t="n">
-        <v>90970</v>
+        <v>90952</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2095,34 +2080,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Lill-Åsberget, Lill-Åsberget, Ång</t>
+          <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>542238</v>
+        <v>542097</v>
       </c>
       <c r="R15" t="n">
-        <v>7063973</v>
+        <v>7063815</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2181,10 +2166,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122733041</v>
+        <v>122741763</v>
       </c>
       <c r="B16" t="n">
-        <v>90970</v>
+        <v>90952</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2197,21 +2182,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2221,10 +2206,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>541873</v>
+        <v>542067</v>
       </c>
       <c r="R16" t="n">
-        <v>7063379</v>
+        <v>7063777</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2283,10 +2268,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122732330</v>
+        <v>122730086</v>
       </c>
       <c r="B17" t="n">
-        <v>90917</v>
+        <v>90952</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2295,38 +2280,38 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Stamåsen, Stamåsen, Ång</t>
+          <t>Lill-Åsberget, Lill-Åsberget, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>541875</v>
+        <v>542258</v>
       </c>
       <c r="R17" t="n">
-        <v>7063622</v>
+        <v>7063917</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2385,10 +2370,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122731904</v>
+        <v>122741376</v>
       </c>
       <c r="B18" t="n">
-        <v>78766</v>
+        <v>91243</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2401,21 +2386,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2425,10 +2410,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>541908</v>
+        <v>541997</v>
       </c>
       <c r="R18" t="n">
-        <v>7063682</v>
+        <v>7063580</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2461,11 +2446,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-02-24</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Garnlavsrika partier över hela sluttningen</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2492,10 +2472,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122730234</v>
+        <v>122730426</v>
       </c>
       <c r="B19" t="n">
-        <v>79847</v>
+        <v>56680</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2508,34 +2488,39 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>102612</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Lill-Åsberget, Lill-Åsberget, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>542187</v>
+        <v>542150</v>
       </c>
       <c r="R19" t="n">
-        <v>7063885</v>
+        <v>7063805</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2594,10 +2579,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122731193</v>
+        <v>122733126</v>
       </c>
       <c r="B20" t="n">
-        <v>91350</v>
+        <v>78766</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2610,16 +2595,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6040186</v>
+        <v>6425</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2629,10 +2619,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>541919</v>
+        <v>541858</v>
       </c>
       <c r="R20" t="n">
-        <v>7063716</v>
+        <v>7063338</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2691,10 +2681,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122741763</v>
+        <v>122741691</v>
       </c>
       <c r="B21" t="n">
-        <v>90952</v>
+        <v>56680</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2707,34 +2697,39 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>102612</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>542067</v>
+        <v>542063</v>
       </c>
       <c r="R21" t="n">
-        <v>7063777</v>
+        <v>7063786</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2793,10 +2788,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122741488</v>
+        <v>122741781</v>
       </c>
       <c r="B22" t="n">
-        <v>57494</v>
+        <v>91301</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2805,43 +2800,38 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>2062</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>542034</v>
+        <v>542068</v>
       </c>
       <c r="R22" t="n">
-        <v>7063681</v>
+        <v>7063778</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2900,10 +2890,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122741513</v>
+        <v>122732657</v>
       </c>
       <c r="B23" t="n">
-        <v>90952</v>
+        <v>90917</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2912,25 +2902,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2940,10 +2930,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>542030</v>
+        <v>541761</v>
       </c>
       <c r="R23" t="n">
-        <v>7063685</v>
+        <v>7063583</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -3104,10 +3094,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122733126</v>
+        <v>122730234</v>
       </c>
       <c r="B25" t="n">
-        <v>78766</v>
+        <v>79847</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3120,34 +3110,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Stamåsen, Stamåsen, Ång</t>
+          <t>Lill-Åsberget, Lill-Åsberget, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>541858</v>
+        <v>542187</v>
       </c>
       <c r="R25" t="n">
-        <v>7063338</v>
+        <v>7063885</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3206,10 +3196,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122730499</v>
+        <v>122741741</v>
       </c>
       <c r="B26" t="n">
-        <v>78766</v>
+        <v>90917</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3218,38 +3208,38 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Lill-Åsberget, Lill-Åsberget, Ång</t>
+          <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>542132</v>
+        <v>542064</v>
       </c>
       <c r="R26" t="n">
-        <v>7063797</v>
+        <v>7063777</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3308,10 +3298,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122730246</v>
+        <v>122741488</v>
       </c>
       <c r="B27" t="n">
-        <v>78766</v>
+        <v>57494</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3324,34 +3314,39 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Lill-Åsberget, Lill-Åsberget, Ång</t>
+          <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>542168</v>
+        <v>542034</v>
       </c>
       <c r="R27" t="n">
-        <v>7063849</v>
+        <v>7063681</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3410,10 +3405,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122730086</v>
+        <v>122731014</v>
       </c>
       <c r="B28" t="n">
-        <v>90952</v>
+        <v>79847</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3426,34 +3421,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Lill-Åsberget, Lill-Åsberget, Ång</t>
+          <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>542258</v>
+        <v>541940</v>
       </c>
       <c r="R28" t="n">
-        <v>7063917</v>
+        <v>7063713</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3512,10 +3507,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122732653</v>
+        <v>122730246</v>
       </c>
       <c r="B29" t="n">
-        <v>90966</v>
+        <v>78766</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3528,34 +3523,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1204</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Stamåsen, Stamåsen, Ång</t>
+          <t>Lill-Åsberget, Lill-Åsberget, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>541760</v>
+        <v>542168</v>
       </c>
       <c r="R29" t="n">
-        <v>7063584</v>
+        <v>7063849</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3614,10 +3609,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122741861</v>
+        <v>122730499</v>
       </c>
       <c r="B30" t="n">
-        <v>79847</v>
+        <v>78766</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3630,21 +3625,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3654,10 +3649,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>542085</v>
+        <v>542132</v>
       </c>
       <c r="R30" t="n">
-        <v>7063858</v>
+        <v>7063797</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3716,10 +3711,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122731014</v>
+        <v>122732958</v>
       </c>
       <c r="B31" t="n">
-        <v>79847</v>
+        <v>57478</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3732,34 +3727,39 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>541940</v>
+        <v>541820</v>
       </c>
       <c r="R31" t="n">
-        <v>7063713</v>
+        <v>7063439</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3792,6 +3792,11 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-02-24</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Äldre ringhack, &gt;200-årig tall</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3818,10 +3823,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122741741</v>
+        <v>122731904</v>
       </c>
       <c r="B32" t="n">
-        <v>90917</v>
+        <v>78766</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3830,25 +3835,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3858,10 +3863,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>542064</v>
+        <v>541908</v>
       </c>
       <c r="R32" t="n">
-        <v>7063777</v>
+        <v>7063682</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3894,6 +3899,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-02-24</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Garnlavsrika partier över hela sluttningen</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3920,10 +3930,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122730177</v>
+        <v>122741643</v>
       </c>
       <c r="B33" t="n">
-        <v>56688</v>
+        <v>56680</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3932,25 +3942,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100138</v>
+        <v>102612</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3961,14 +3971,14 @@
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Lill-Åsberget, Lill-Åsberget, Ång</t>
+          <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>542198</v>
+        <v>542064</v>
       </c>
       <c r="R33" t="n">
-        <v>7063872</v>
+        <v>7063749</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -4027,10 +4037,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122741643</v>
+        <v>122732487</v>
       </c>
       <c r="B34" t="n">
-        <v>56680</v>
+        <v>90952</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4043,39 +4053,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>102612</v>
+        <v>1202</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P34" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>542064</v>
+        <v>541847</v>
       </c>
       <c r="R34" t="n">
-        <v>7063749</v>
+        <v>7063615</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4134,10 +4139,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122732487</v>
+        <v>122742207</v>
       </c>
       <c r="B35" t="n">
-        <v>90952</v>
+        <v>90970</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4150,34 +4155,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1202</v>
+        <v>5432</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Stamåsen, Stamåsen, Ång</t>
+          <t>Lill-Åsberget, Lill-Åsberget, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>541847</v>
+        <v>542238</v>
       </c>
       <c r="R35" t="n">
-        <v>7063615</v>
+        <v>7063973</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4236,10 +4241,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122730426</v>
+        <v>122731109</v>
       </c>
       <c r="B36" t="n">
-        <v>56680</v>
+        <v>57478</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4252,16 +4257,16 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>102612</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -4272,19 +4277,19 @@
       <c r="I36" t="inlineStr"/>
       <c r="M36" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Lill-Åsberget, Lill-Åsberget, Ång</t>
+          <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>542150</v>
+        <v>541940</v>
       </c>
       <c r="R36" t="n">
-        <v>7063805</v>
+        <v>7063712</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4317,6 +4322,11 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-02-24</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Äldre ringhack, gammal tall</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4343,10 +4353,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122732657</v>
+        <v>122733041</v>
       </c>
       <c r="B37" t="n">
-        <v>90917</v>
+        <v>90970</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4355,25 +4365,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>5447</v>
+        <v>5432</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4383,10 +4393,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>541761</v>
+        <v>541873</v>
       </c>
       <c r="R37" t="n">
-        <v>7063583</v>
+        <v>7063379</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4445,10 +4455,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122729831</v>
+        <v>122732558</v>
       </c>
       <c r="B38" t="n">
-        <v>57478</v>
+        <v>97325</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4457,43 +4467,38 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>221941</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Lill-Åsberget, Lill-Åsberget, Ång</t>
+          <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>542249</v>
+        <v>541824</v>
       </c>
       <c r="R38" t="n">
-        <v>7063942</v>
+        <v>7063603</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4526,11 +4531,6 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-02-24</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Bohål i torrgran, 2m ovan mark. 5 cm ø. Gott om stående död ved i området.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4557,10 +4557,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122741691</v>
+        <v>122732584</v>
       </c>
       <c r="B39" t="n">
-        <v>56680</v>
+        <v>97319</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4569,43 +4569,38 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>102612</v>
+        <v>221945</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>542063</v>
+        <v>541821</v>
       </c>
       <c r="R39" t="n">
-        <v>7063786</v>
+        <v>7063616</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -4664,10 +4659,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122732264</v>
+        <v>122732631</v>
       </c>
       <c r="B40" t="n">
-        <v>82553</v>
+        <v>88303</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4680,21 +4675,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1312</v>
+        <v>510</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4704,10 +4699,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>541883</v>
+        <v>541768</v>
       </c>
       <c r="R40" t="n">
-        <v>7063653</v>
+        <v>7063586</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -4766,10 +4761,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122732584</v>
+        <v>122730177</v>
       </c>
       <c r="B41" t="n">
-        <v>97319</v>
+        <v>56688</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4782,34 +4777,39 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>221945</v>
+        <v>100138</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Stamåsen, Stamåsen, Ång</t>
+          <t>Lill-Åsberget, Lill-Åsberget, Ång</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>541821</v>
+        <v>542198</v>
       </c>
       <c r="R41" t="n">
-        <v>7063616</v>
+        <v>7063872</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -4970,7 +4970,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122730595</v>
+        <v>122741513</v>
       </c>
       <c r="B43" t="n">
         <v>90952</v>
@@ -5010,10 +5010,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>542097</v>
+        <v>542030</v>
       </c>
       <c r="R43" t="n">
-        <v>7063815</v>
+        <v>7063685</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -5072,10 +5072,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122732631</v>
+        <v>122731166</v>
       </c>
       <c r="B44" t="n">
-        <v>88303</v>
+        <v>90970</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5088,21 +5088,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>510</v>
+        <v>5432</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5112,10 +5112,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>541768</v>
+        <v>541922</v>
       </c>
       <c r="R44" t="n">
-        <v>7063586</v>
+        <v>7063717</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>
@@ -5174,10 +5174,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122732558</v>
+        <v>122732264</v>
       </c>
       <c r="B45" t="n">
-        <v>97325</v>
+        <v>82553</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5186,25 +5186,25 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>221941</v>
+        <v>1312</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5214,10 +5214,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>541824</v>
+        <v>541883</v>
       </c>
       <c r="R45" t="n">
-        <v>7063603</v>
+        <v>7063653</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -5276,7 +5276,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122732958</v>
+        <v>122729831</v>
       </c>
       <c r="B46" t="n">
         <v>57478</v>
@@ -5312,19 +5312,19 @@
       <c r="I46" t="inlineStr"/>
       <c r="M46" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Stamåsen, Stamåsen, Ång</t>
+          <t>Lill-Åsberget, Lill-Åsberget, Ång</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>541820</v>
+        <v>542249</v>
       </c>
       <c r="R46" t="n">
-        <v>7063439</v>
+        <v>7063942</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>
@@ -5361,7 +5361,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Äldre ringhack, &gt;200-årig tall</t>
+          <t>Bohål i torrgran, 2m ovan mark. 5 cm ø. Gott om stående död ved i området.</t>
         </is>
       </c>
       <c r="AD46" t="b">

--- a/artfynd/A 3110-2025 artfynd.xlsx
+++ b/artfynd/A 3110-2025 artfynd.xlsx
@@ -1350,10 +1350,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122741861</v>
+        <v>122741513</v>
       </c>
       <c r="B8" t="n">
-        <v>79847</v>
+        <v>90952</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1366,34 +1366,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Lill-Åsberget, Lill-Åsberget, Ång</t>
+          <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>542085</v>
+        <v>542030</v>
       </c>
       <c r="R8" t="n">
-        <v>7063858</v>
+        <v>7063685</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1452,10 +1452,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122730829</v>
+        <v>122731193</v>
       </c>
       <c r="B9" t="n">
-        <v>78766</v>
+        <v>91350</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1468,21 +1468,16 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Garnlav</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1492,10 +1487,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>542035</v>
+        <v>541919</v>
       </c>
       <c r="R9" t="n">
-        <v>7063816</v>
+        <v>7063716</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1554,10 +1549,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122732330</v>
+        <v>122731166</v>
       </c>
       <c r="B10" t="n">
-        <v>90917</v>
+        <v>90970</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1566,25 +1561,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5447</v>
+        <v>5432</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1594,10 +1589,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>541875</v>
+        <v>541922</v>
       </c>
       <c r="R10" t="n">
-        <v>7063622</v>
+        <v>7063717</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1656,7 +1651,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122732817</v>
+        <v>122741643</v>
       </c>
       <c r="B11" t="n">
         <v>56680</v>
@@ -1701,10 +1696,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>541803</v>
+        <v>542064</v>
       </c>
       <c r="R11" t="n">
-        <v>7063479</v>
+        <v>7063749</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1763,10 +1758,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122731193</v>
+        <v>122732657</v>
       </c>
       <c r="B12" t="n">
-        <v>91350</v>
+        <v>90917</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1775,20 +1770,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6040186</v>
+        <v>5447</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1798,10 +1798,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>541919</v>
+        <v>541761</v>
       </c>
       <c r="R12" t="n">
-        <v>7063716</v>
+        <v>7063583</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1860,10 +1860,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122730759</v>
+        <v>122732558</v>
       </c>
       <c r="B13" t="n">
-        <v>91312</v>
+        <v>97325</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1872,25 +1872,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1506</v>
+        <v>221941</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1900,10 +1900,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>542045</v>
+        <v>541824</v>
       </c>
       <c r="R13" t="n">
-        <v>7063823</v>
+        <v>7063603</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1962,10 +1962,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122732653</v>
+        <v>122731109</v>
       </c>
       <c r="B14" t="n">
-        <v>90966</v>
+        <v>57478</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1978,34 +1978,39 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1204</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>541760</v>
+        <v>541940</v>
       </c>
       <c r="R14" t="n">
-        <v>7063584</v>
+        <v>7063712</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2038,6 +2043,11 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-02-24</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Äldre ringhack, gammal tall</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2064,10 +2074,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122730595</v>
+        <v>122732958</v>
       </c>
       <c r="B15" t="n">
-        <v>90952</v>
+        <v>57478</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2080,34 +2090,39 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>542097</v>
+        <v>541820</v>
       </c>
       <c r="R15" t="n">
-        <v>7063815</v>
+        <v>7063439</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2140,6 +2155,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-02-24</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Äldre ringhack, &gt;200-årig tall</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2166,10 +2186,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122741763</v>
+        <v>122732264</v>
       </c>
       <c r="B16" t="n">
-        <v>90952</v>
+        <v>82553</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2182,21 +2202,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>1312</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2206,10 +2226,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>542067</v>
+        <v>541883</v>
       </c>
       <c r="R16" t="n">
-        <v>7063777</v>
+        <v>7063653</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2268,10 +2288,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122730086</v>
+        <v>122732330</v>
       </c>
       <c r="B17" t="n">
-        <v>90952</v>
+        <v>90917</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2280,38 +2300,38 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Lill-Åsberget, Lill-Åsberget, Ång</t>
+          <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>542258</v>
+        <v>541875</v>
       </c>
       <c r="R17" t="n">
-        <v>7063917</v>
+        <v>7063622</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2370,10 +2390,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122741376</v>
+        <v>122731014</v>
       </c>
       <c r="B18" t="n">
-        <v>91243</v>
+        <v>79847</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2386,21 +2406,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2410,10 +2430,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>541997</v>
+        <v>541940</v>
       </c>
       <c r="R18" t="n">
-        <v>7063580</v>
+        <v>7063713</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2472,10 +2492,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122730426</v>
+        <v>122730004</v>
       </c>
       <c r="B19" t="n">
-        <v>56680</v>
+        <v>90966</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2488,39 +2508,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>102612</v>
+        <v>1204</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Lill-Åsberget, Lill-Åsberget, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>542150</v>
+        <v>542251</v>
       </c>
       <c r="R19" t="n">
-        <v>7063805</v>
+        <v>7063915</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2579,10 +2594,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122733126</v>
+        <v>122741691</v>
       </c>
       <c r="B20" t="n">
-        <v>78766</v>
+        <v>56680</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2595,34 +2610,39 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>102612</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>541858</v>
+        <v>542063</v>
       </c>
       <c r="R20" t="n">
-        <v>7063338</v>
+        <v>7063786</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2681,10 +2701,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122741691</v>
+        <v>122730234</v>
       </c>
       <c r="B21" t="n">
-        <v>56680</v>
+        <v>79847</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2697,39 +2717,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>102612</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Stamåsen, Stamåsen, Ång</t>
+          <t>Lill-Åsberget, Lill-Åsberget, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>542063</v>
+        <v>542187</v>
       </c>
       <c r="R21" t="n">
-        <v>7063786</v>
+        <v>7063885</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2788,10 +2803,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122741781</v>
+        <v>122732631</v>
       </c>
       <c r="B22" t="n">
-        <v>91301</v>
+        <v>88303</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2800,25 +2815,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2062</v>
+        <v>510</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2828,10 +2843,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>542068</v>
+        <v>541768</v>
       </c>
       <c r="R22" t="n">
-        <v>7063778</v>
+        <v>7063586</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2890,10 +2905,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122732657</v>
+        <v>122741488</v>
       </c>
       <c r="B23" t="n">
-        <v>90917</v>
+        <v>57494</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2902,38 +2917,43 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>541761</v>
+        <v>542034</v>
       </c>
       <c r="R23" t="n">
-        <v>7063583</v>
+        <v>7063681</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -2992,10 +3012,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122730004</v>
+        <v>122730426</v>
       </c>
       <c r="B24" t="n">
-        <v>90966</v>
+        <v>56680</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3008,34 +3028,39 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1204</v>
+        <v>102612</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
           <t>Lill-Åsberget, Lill-Åsberget, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>542251</v>
+        <v>542150</v>
       </c>
       <c r="R24" t="n">
-        <v>7063915</v>
+        <v>7063805</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3094,10 +3119,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122730234</v>
+        <v>122741741</v>
       </c>
       <c r="B25" t="n">
-        <v>79847</v>
+        <v>90917</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3106,38 +3131,38 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6458</v>
+        <v>5447</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Lill-Åsberget, Lill-Åsberget, Ång</t>
+          <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>542187</v>
+        <v>542064</v>
       </c>
       <c r="R25" t="n">
-        <v>7063885</v>
+        <v>7063777</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3196,10 +3221,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122741741</v>
+        <v>122733126</v>
       </c>
       <c r="B26" t="n">
-        <v>90917</v>
+        <v>78766</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3208,25 +3233,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3236,10 +3261,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>542064</v>
+        <v>541858</v>
       </c>
       <c r="R26" t="n">
-        <v>7063777</v>
+        <v>7063338</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3298,10 +3323,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122741488</v>
+        <v>122730177</v>
       </c>
       <c r="B27" t="n">
-        <v>57494</v>
+        <v>56688</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3310,43 +3335,43 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Stamåsen, Stamåsen, Ång</t>
+          <t>Lill-Åsberget, Lill-Åsberget, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>542034</v>
+        <v>542198</v>
       </c>
       <c r="R27" t="n">
-        <v>7063681</v>
+        <v>7063872</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3405,10 +3430,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122731014</v>
+        <v>122730759</v>
       </c>
       <c r="B28" t="n">
-        <v>79847</v>
+        <v>91312</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3417,25 +3442,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6458</v>
+        <v>1506</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3445,10 +3470,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>541940</v>
+        <v>542045</v>
       </c>
       <c r="R28" t="n">
-        <v>7063713</v>
+        <v>7063823</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3507,10 +3532,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122730246</v>
+        <v>122742207</v>
       </c>
       <c r="B29" t="n">
-        <v>78766</v>
+        <v>90970</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3523,21 +3548,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3547,10 +3572,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>542168</v>
+        <v>542238</v>
       </c>
       <c r="R29" t="n">
-        <v>7063849</v>
+        <v>7063973</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3609,7 +3634,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122730499</v>
+        <v>122730829</v>
       </c>
       <c r="B30" t="n">
         <v>78766</v>
@@ -3645,14 +3670,14 @@
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Lill-Åsberget, Lill-Åsberget, Ång</t>
+          <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>542132</v>
+        <v>542035</v>
       </c>
       <c r="R30" t="n">
-        <v>7063797</v>
+        <v>7063816</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3711,10 +3736,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122732958</v>
+        <v>122741763</v>
       </c>
       <c r="B31" t="n">
-        <v>57478</v>
+        <v>90952</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3727,39 +3752,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>541820</v>
+        <v>542067</v>
       </c>
       <c r="R31" t="n">
-        <v>7063439</v>
+        <v>7063777</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3792,11 +3812,6 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-02-24</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Äldre ringhack, &gt;200-årig tall</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3823,10 +3838,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122731904</v>
+        <v>122741781</v>
       </c>
       <c r="B32" t="n">
-        <v>78766</v>
+        <v>91301</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3835,25 +3850,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>2062</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3863,10 +3878,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>541908</v>
+        <v>542068</v>
       </c>
       <c r="R32" t="n">
-        <v>7063682</v>
+        <v>7063778</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3899,11 +3914,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-02-24</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Garnlavsrika partier över hela sluttningen</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3930,10 +3940,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122741643</v>
+        <v>122732584</v>
       </c>
       <c r="B33" t="n">
-        <v>56680</v>
+        <v>97319</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3942,43 +3952,38 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>102612</v>
+        <v>221945</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>542064</v>
+        <v>541821</v>
       </c>
       <c r="R33" t="n">
-        <v>7063749</v>
+        <v>7063616</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -4037,10 +4042,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122732487</v>
+        <v>122730246</v>
       </c>
       <c r="B34" t="n">
-        <v>90952</v>
+        <v>78766</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4053,34 +4058,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Stamåsen, Stamåsen, Ång</t>
+          <t>Lill-Åsberget, Lill-Åsberget, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>541847</v>
+        <v>542168</v>
       </c>
       <c r="R34" t="n">
-        <v>7063615</v>
+        <v>7063849</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4139,10 +4144,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122742207</v>
+        <v>122730499</v>
       </c>
       <c r="B35" t="n">
-        <v>90970</v>
+        <v>78766</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4155,21 +4160,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4179,10 +4184,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>542238</v>
+        <v>542132</v>
       </c>
       <c r="R35" t="n">
-        <v>7063973</v>
+        <v>7063797</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4241,10 +4246,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122731109</v>
+        <v>122732653</v>
       </c>
       <c r="B36" t="n">
-        <v>57478</v>
+        <v>90966</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4257,39 +4262,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>1204</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>541940</v>
+        <v>541760</v>
       </c>
       <c r="R36" t="n">
-        <v>7063712</v>
+        <v>7063584</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4322,11 +4322,6 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-02-24</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Äldre ringhack, gammal tall</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4353,10 +4348,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122733041</v>
+        <v>122732817</v>
       </c>
       <c r="B37" t="n">
-        <v>90970</v>
+        <v>56680</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4369,34 +4364,39 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>5432</v>
+        <v>102612</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>541873</v>
+        <v>541803</v>
       </c>
       <c r="R37" t="n">
-        <v>7063379</v>
+        <v>7063479</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4455,10 +4455,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122732558</v>
+        <v>122741376</v>
       </c>
       <c r="B38" t="n">
-        <v>97325</v>
+        <v>91243</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4467,25 +4467,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>221941</v>
+        <v>658</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4495,10 +4495,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>541824</v>
+        <v>541997</v>
       </c>
       <c r="R38" t="n">
-        <v>7063603</v>
+        <v>7063580</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4557,10 +4557,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122732584</v>
+        <v>122732487</v>
       </c>
       <c r="B39" t="n">
-        <v>97319</v>
+        <v>90952</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4569,25 +4569,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>221945</v>
+        <v>1202</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4597,10 +4597,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>541821</v>
+        <v>541847</v>
       </c>
       <c r="R39" t="n">
-        <v>7063616</v>
+        <v>7063615</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -4659,10 +4659,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122732631</v>
+        <v>122730086</v>
       </c>
       <c r="B40" t="n">
-        <v>88303</v>
+        <v>90952</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4675,34 +4675,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>510</v>
+        <v>1202</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Stamåsen, Stamåsen, Ång</t>
+          <t>Lill-Åsberget, Lill-Åsberget, Ång</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>541768</v>
+        <v>542258</v>
       </c>
       <c r="R40" t="n">
-        <v>7063586</v>
+        <v>7063917</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -4761,10 +4761,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122730177</v>
+        <v>122729831</v>
       </c>
       <c r="B41" t="n">
-        <v>56688</v>
+        <v>57478</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4773,31 +4773,31 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="M41" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
@@ -4806,10 +4806,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>542198</v>
+        <v>542249</v>
       </c>
       <c r="R41" t="n">
-        <v>7063872</v>
+        <v>7063942</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -4842,6 +4842,11 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-02-24</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Bohål i torrgran, 2m ovan mark. 5 cm ø. Gott om stående död ved i området.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4868,10 +4873,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122730042</v>
+        <v>122741861</v>
       </c>
       <c r="B42" t="n">
-        <v>91243</v>
+        <v>79847</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4884,21 +4889,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4908,10 +4913,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>542248</v>
+        <v>542085</v>
       </c>
       <c r="R42" t="n">
-        <v>7063927</v>
+        <v>7063858</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -4970,10 +4975,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122741513</v>
+        <v>122731904</v>
       </c>
       <c r="B43" t="n">
-        <v>90952</v>
+        <v>78766</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4986,21 +4991,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5010,10 +5015,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>542030</v>
+        <v>541908</v>
       </c>
       <c r="R43" t="n">
-        <v>7063685</v>
+        <v>7063682</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -5046,6 +5051,11 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-02-24</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Garnlavsrika partier över hela sluttningen</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5072,10 +5082,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122731166</v>
+        <v>122730595</v>
       </c>
       <c r="B44" t="n">
-        <v>90970</v>
+        <v>90952</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5088,21 +5098,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5112,10 +5122,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>541922</v>
+        <v>542097</v>
       </c>
       <c r="R44" t="n">
-        <v>7063717</v>
+        <v>7063815</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>
@@ -5174,10 +5184,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122732264</v>
+        <v>122730042</v>
       </c>
       <c r="B45" t="n">
-        <v>82553</v>
+        <v>91243</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5190,34 +5200,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1312</v>
+        <v>658</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Stamåsen, Stamåsen, Ång</t>
+          <t>Lill-Åsberget, Lill-Åsberget, Ång</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>541883</v>
+        <v>542248</v>
       </c>
       <c r="R45" t="n">
-        <v>7063653</v>
+        <v>7063927</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -5276,10 +5286,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122729831</v>
+        <v>122733041</v>
       </c>
       <c r="B46" t="n">
-        <v>57478</v>
+        <v>90970</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5292,39 +5302,34 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Lill-Åsberget, Lill-Åsberget, Ång</t>
+          <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>542249</v>
+        <v>541873</v>
       </c>
       <c r="R46" t="n">
-        <v>7063942</v>
+        <v>7063379</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>
@@ -5357,11 +5362,6 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-02-24</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Bohål i torrgran, 2m ovan mark. 5 cm ø. Gott om stående död ved i området.</t>
         </is>
       </c>
       <c r="AD46" t="b">

--- a/artfynd/A 3110-2025 artfynd.xlsx
+++ b/artfynd/A 3110-2025 artfynd.xlsx
@@ -1452,10 +1452,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122731193</v>
+        <v>122731166</v>
       </c>
       <c r="B9" t="n">
-        <v>91350</v>
+        <v>90970</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1468,16 +1468,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6040186</v>
+        <v>5432</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1487,10 +1492,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>541919</v>
+        <v>541922</v>
       </c>
       <c r="R9" t="n">
-        <v>7063716</v>
+        <v>7063717</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1549,10 +1554,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122731166</v>
+        <v>122741643</v>
       </c>
       <c r="B10" t="n">
-        <v>90970</v>
+        <v>56680</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1565,34 +1570,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5432</v>
+        <v>102612</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>541922</v>
+        <v>542064</v>
       </c>
       <c r="R10" t="n">
-        <v>7063717</v>
+        <v>7063749</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1651,10 +1661,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122741643</v>
+        <v>122731193</v>
       </c>
       <c r="B11" t="n">
-        <v>56680</v>
+        <v>91350</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1667,39 +1677,29 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>102612</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Järpe</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>542064</v>
+        <v>541919</v>
       </c>
       <c r="R11" t="n">
-        <v>7063749</v>
+        <v>7063716</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1758,10 +1758,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122732657</v>
+        <v>122732558</v>
       </c>
       <c r="B12" t="n">
-        <v>90917</v>
+        <v>97325</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1774,21 +1774,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5447</v>
+        <v>221941</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1798,10 +1798,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>541761</v>
+        <v>541824</v>
       </c>
       <c r="R12" t="n">
-        <v>7063583</v>
+        <v>7063603</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1860,10 +1860,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122732558</v>
+        <v>122732657</v>
       </c>
       <c r="B13" t="n">
-        <v>97325</v>
+        <v>90917</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1876,21 +1876,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221941</v>
+        <v>5447</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1900,10 +1900,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>541824</v>
+        <v>541761</v>
       </c>
       <c r="R13" t="n">
-        <v>7063603</v>
+        <v>7063583</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -2390,10 +2390,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122731014</v>
+        <v>122730004</v>
       </c>
       <c r="B18" t="n">
-        <v>79847</v>
+        <v>90966</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2406,34 +2406,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>1204</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Stamåsen, Stamåsen, Ång</t>
+          <t>Lill-Åsberget, Lill-Åsberget, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>541940</v>
+        <v>542251</v>
       </c>
       <c r="R18" t="n">
-        <v>7063713</v>
+        <v>7063915</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2492,10 +2492,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122730004</v>
+        <v>122731014</v>
       </c>
       <c r="B19" t="n">
-        <v>90966</v>
+        <v>79847</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2508,34 +2508,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1204</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Lill-Åsberget, Lill-Åsberget, Ång</t>
+          <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>542251</v>
+        <v>541940</v>
       </c>
       <c r="R19" t="n">
-        <v>7063915</v>
+        <v>7063713</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2594,10 +2594,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122741691</v>
+        <v>122730234</v>
       </c>
       <c r="B20" t="n">
-        <v>56680</v>
+        <v>79847</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2610,39 +2610,34 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>102612</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Stamåsen, Stamåsen, Ång</t>
+          <t>Lill-Åsberget, Lill-Åsberget, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>542063</v>
+        <v>542187</v>
       </c>
       <c r="R20" t="n">
-        <v>7063786</v>
+        <v>7063885</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2701,10 +2696,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122730234</v>
+        <v>122741691</v>
       </c>
       <c r="B21" t="n">
-        <v>79847</v>
+        <v>56680</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2717,34 +2712,39 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>102612</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Lill-Åsberget, Lill-Åsberget, Ång</t>
+          <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>542187</v>
+        <v>542063</v>
       </c>
       <c r="R21" t="n">
-        <v>7063885</v>
+        <v>7063786</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -3221,10 +3221,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122733126</v>
+        <v>122730177</v>
       </c>
       <c r="B26" t="n">
-        <v>78766</v>
+        <v>56688</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3233,38 +3233,43 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Stamåsen, Stamåsen, Ång</t>
+          <t>Lill-Åsberget, Lill-Åsberget, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>541858</v>
+        <v>542198</v>
       </c>
       <c r="R26" t="n">
-        <v>7063338</v>
+        <v>7063872</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3323,10 +3328,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122730177</v>
+        <v>122733126</v>
       </c>
       <c r="B27" t="n">
-        <v>56688</v>
+        <v>78766</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3335,43 +3340,38 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Lill-Åsberget, Lill-Åsberget, Ång</t>
+          <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>542198</v>
+        <v>541858</v>
       </c>
       <c r="R27" t="n">
-        <v>7063872</v>
+        <v>7063338</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3430,10 +3430,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122730759</v>
+        <v>122742207</v>
       </c>
       <c r="B28" t="n">
-        <v>91312</v>
+        <v>90970</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3442,38 +3442,38 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1506</v>
+        <v>5432</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Stamåsen, Stamåsen, Ång</t>
+          <t>Lill-Åsberget, Lill-Åsberget, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>542045</v>
+        <v>542238</v>
       </c>
       <c r="R28" t="n">
-        <v>7063823</v>
+        <v>7063973</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3532,10 +3532,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122742207</v>
+        <v>122730759</v>
       </c>
       <c r="B29" t="n">
-        <v>90970</v>
+        <v>91312</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3544,38 +3544,38 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5432</v>
+        <v>1506</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Lill-Åsberget, Lill-Åsberget, Ång</t>
+          <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>542238</v>
+        <v>542045</v>
       </c>
       <c r="R29" t="n">
-        <v>7063973</v>
+        <v>7063823</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -4246,10 +4246,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122732653</v>
+        <v>122732817</v>
       </c>
       <c r="B36" t="n">
-        <v>90966</v>
+        <v>56680</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4262,34 +4262,39 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1204</v>
+        <v>102612</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>541760</v>
+        <v>541803</v>
       </c>
       <c r="R36" t="n">
-        <v>7063584</v>
+        <v>7063479</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4348,10 +4353,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122732817</v>
+        <v>122732653</v>
       </c>
       <c r="B37" t="n">
-        <v>56680</v>
+        <v>90966</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4364,39 +4369,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>102612</v>
+        <v>1204</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>541803</v>
+        <v>541760</v>
       </c>
       <c r="R37" t="n">
-        <v>7063479</v>
+        <v>7063584</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4873,10 +4873,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122741861</v>
+        <v>122731904</v>
       </c>
       <c r="B42" t="n">
-        <v>79847</v>
+        <v>78766</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4889,34 +4889,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Lill-Åsberget, Lill-Åsberget, Ång</t>
+          <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>542085</v>
+        <v>541908</v>
       </c>
       <c r="R42" t="n">
-        <v>7063858</v>
+        <v>7063682</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -4949,6 +4949,11 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-02-24</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Garnlavsrika partier över hela sluttningen</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4975,10 +4980,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122731904</v>
+        <v>122730595</v>
       </c>
       <c r="B43" t="n">
-        <v>78766</v>
+        <v>90952</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4991,21 +4996,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5015,10 +5020,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>541908</v>
+        <v>542097</v>
       </c>
       <c r="R43" t="n">
-        <v>7063682</v>
+        <v>7063815</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -5051,11 +5056,6 @@
       <c r="AA43" t="inlineStr">
         <is>
           <t>2025-02-24</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Garnlavsrika partier över hela sluttningen</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5082,10 +5082,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122730595</v>
+        <v>122741861</v>
       </c>
       <c r="B44" t="n">
-        <v>90952</v>
+        <v>79847</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5098,34 +5098,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Stamåsen, Stamåsen, Ång</t>
+          <t>Lill-Åsberget, Lill-Åsberget, Ång</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>542097</v>
+        <v>542085</v>
       </c>
       <c r="R44" t="n">
-        <v>7063815</v>
+        <v>7063858</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>
@@ -5184,10 +5184,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122730042</v>
+        <v>122733041</v>
       </c>
       <c r="B45" t="n">
-        <v>91243</v>
+        <v>90970</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5200,34 +5200,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>658</v>
+        <v>5432</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Lill-Åsberget, Lill-Åsberget, Ång</t>
+          <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>542248</v>
+        <v>541873</v>
       </c>
       <c r="R45" t="n">
-        <v>7063927</v>
+        <v>7063379</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -5286,10 +5286,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122733041</v>
+        <v>122730042</v>
       </c>
       <c r="B46" t="n">
-        <v>90970</v>
+        <v>91243</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5302,34 +5302,34 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>5432</v>
+        <v>658</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Stamåsen, Stamåsen, Ång</t>
+          <t>Lill-Åsberget, Lill-Åsberget, Ång</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>541873</v>
+        <v>542248</v>
       </c>
       <c r="R46" t="n">
-        <v>7063379</v>
+        <v>7063927</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>

--- a/artfynd/A 3110-2025 artfynd.xlsx
+++ b/artfynd/A 3110-2025 artfynd.xlsx
@@ -4246,10 +4246,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122732817</v>
+        <v>122732653</v>
       </c>
       <c r="B36" t="n">
-        <v>56680</v>
+        <v>90966</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4262,39 +4262,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>102612</v>
+        <v>1204</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>541803</v>
+        <v>541760</v>
       </c>
       <c r="R36" t="n">
-        <v>7063479</v>
+        <v>7063584</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4353,10 +4348,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122732653</v>
+        <v>122732817</v>
       </c>
       <c r="B37" t="n">
-        <v>90966</v>
+        <v>56680</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4369,34 +4364,39 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1204</v>
+        <v>102612</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>541760</v>
+        <v>541803</v>
       </c>
       <c r="R37" t="n">
-        <v>7063584</v>
+        <v>7063479</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>

--- a/artfynd/A 3110-2025 artfynd.xlsx
+++ b/artfynd/A 3110-2025 artfynd.xlsx
@@ -1350,10 +1350,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122741513</v>
+        <v>122730042</v>
       </c>
       <c r="B8" t="n">
-        <v>90952</v>
+        <v>91242</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1366,34 +1366,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Stamåsen, Stamåsen, Ång</t>
+          <t>Lill-Åsberget, Lill-Åsberget, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>542030</v>
+        <v>542248</v>
       </c>
       <c r="R8" t="n">
-        <v>7063685</v>
+        <v>7063927</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1452,10 +1452,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122731166</v>
+        <v>122732330</v>
       </c>
       <c r="B9" t="n">
-        <v>90970</v>
+        <v>90920</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1464,25 +1464,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>5447</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1492,10 +1492,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>541922</v>
+        <v>541875</v>
       </c>
       <c r="R9" t="n">
-        <v>7063717</v>
+        <v>7063622</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1554,10 +1554,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122741643</v>
+        <v>122731904</v>
       </c>
       <c r="B10" t="n">
-        <v>56680</v>
+        <v>78769</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1570,39 +1570,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>102612</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>542064</v>
+        <v>541908</v>
       </c>
       <c r="R10" t="n">
-        <v>7063749</v>
+        <v>7063682</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1635,6 +1630,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-02-24</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Garnlavsrika partier över hela sluttningen</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1661,10 +1661,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122731193</v>
+        <v>122730829</v>
       </c>
       <c r="B11" t="n">
-        <v>91350</v>
+        <v>78769</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1677,16 +1677,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6040186</v>
+        <v>6425</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1696,10 +1701,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>541919</v>
+        <v>542035</v>
       </c>
       <c r="R11" t="n">
-        <v>7063716</v>
+        <v>7063816</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1758,10 +1763,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122732558</v>
+        <v>122732631</v>
       </c>
       <c r="B12" t="n">
-        <v>97325</v>
+        <v>88306</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1770,25 +1775,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221941</v>
+        <v>510</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1798,10 +1803,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>541824</v>
+        <v>541768</v>
       </c>
       <c r="R12" t="n">
-        <v>7063603</v>
+        <v>7063586</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1860,10 +1865,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122732657</v>
+        <v>122741376</v>
       </c>
       <c r="B13" t="n">
-        <v>90917</v>
+        <v>91242</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1872,25 +1877,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5447</v>
+        <v>658</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1900,10 +1905,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>541761</v>
+        <v>541997</v>
       </c>
       <c r="R13" t="n">
-        <v>7063583</v>
+        <v>7063580</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1962,10 +1967,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122731109</v>
+        <v>122732817</v>
       </c>
       <c r="B14" t="n">
-        <v>57478</v>
+        <v>56683</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1978,16 +1983,16 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>102612</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1998,7 +2003,7 @@
       <c r="I14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2007,10 +2012,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>541940</v>
+        <v>541803</v>
       </c>
       <c r="R14" t="n">
-        <v>7063712</v>
+        <v>7063479</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2043,11 +2048,6 @@
       <c r="AA14" t="inlineStr">
         <is>
           <t>2025-02-24</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Äldre ringhack, gammal tall</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2074,10 +2074,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122732958</v>
+        <v>122741781</v>
       </c>
       <c r="B15" t="n">
-        <v>57478</v>
+        <v>91304</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2086,43 +2086,38 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>2062</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>541820</v>
+        <v>542068</v>
       </c>
       <c r="R15" t="n">
-        <v>7063439</v>
+        <v>7063778</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2155,11 +2150,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-02-24</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Äldre ringhack, &gt;200-årig tall</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2186,10 +2176,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122732264</v>
+        <v>122732653</v>
       </c>
       <c r="B16" t="n">
-        <v>82553</v>
+        <v>90969</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2202,21 +2192,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1312</v>
+        <v>1204</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2226,10 +2216,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>541883</v>
+        <v>541760</v>
       </c>
       <c r="R16" t="n">
-        <v>7063653</v>
+        <v>7063584</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2288,10 +2278,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122732330</v>
+        <v>122731014</v>
       </c>
       <c r="B17" t="n">
-        <v>90917</v>
+        <v>79850</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2300,25 +2290,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5447</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2328,10 +2318,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>541875</v>
+        <v>541940</v>
       </c>
       <c r="R17" t="n">
-        <v>7063622</v>
+        <v>7063713</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2390,10 +2380,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122730004</v>
+        <v>122731109</v>
       </c>
       <c r="B18" t="n">
-        <v>90966</v>
+        <v>57481</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2406,34 +2396,39 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1204</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Lill-Åsberget, Lill-Åsberget, Ång</t>
+          <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>542251</v>
+        <v>541940</v>
       </c>
       <c r="R18" t="n">
-        <v>7063915</v>
+        <v>7063712</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2466,6 +2461,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-02-24</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Äldre ringhack, gammal tall</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2492,10 +2492,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122731014</v>
+        <v>122730499</v>
       </c>
       <c r="B19" t="n">
-        <v>79847</v>
+        <v>78769</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2508,34 +2508,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Stamåsen, Stamåsen, Ång</t>
+          <t>Lill-Åsberget, Lill-Åsberget, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>541940</v>
+        <v>542132</v>
       </c>
       <c r="R19" t="n">
-        <v>7063713</v>
+        <v>7063797</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2594,10 +2594,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122730234</v>
+        <v>122741643</v>
       </c>
       <c r="B20" t="n">
-        <v>79847</v>
+        <v>56683</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2610,34 +2610,39 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>102612</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Lill-Åsberget, Lill-Åsberget, Ång</t>
+          <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>542187</v>
+        <v>542064</v>
       </c>
       <c r="R20" t="n">
-        <v>7063885</v>
+        <v>7063749</v>
       </c>
       <c r="S20" t="n">
         <v>15</v>
@@ -2696,10 +2701,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122741691</v>
+        <v>122730426</v>
       </c>
       <c r="B21" t="n">
-        <v>56680</v>
+        <v>56683</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2737,14 +2742,14 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Stamåsen, Stamåsen, Ång</t>
+          <t>Lill-Åsberget, Lill-Åsberget, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>542063</v>
+        <v>542150</v>
       </c>
       <c r="R21" t="n">
-        <v>7063786</v>
+        <v>7063805</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2803,10 +2808,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122732631</v>
+        <v>122730177</v>
       </c>
       <c r="B22" t="n">
-        <v>88303</v>
+        <v>56691</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2815,38 +2820,43 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>510</v>
+        <v>100138</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Stamåsen, Stamåsen, Ång</t>
+          <t>Lill-Åsberget, Lill-Åsberget, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>541768</v>
+        <v>542198</v>
       </c>
       <c r="R22" t="n">
-        <v>7063586</v>
+        <v>7063872</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2905,10 +2915,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122741488</v>
+        <v>122732958</v>
       </c>
       <c r="B23" t="n">
-        <v>57494</v>
+        <v>57481</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2921,16 +2931,16 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2941,7 +2951,7 @@
       <c r="I23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -2950,10 +2960,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>542034</v>
+        <v>541820</v>
       </c>
       <c r="R23" t="n">
-        <v>7063681</v>
+        <v>7063439</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -2986,6 +2996,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-02-24</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Äldre ringhack, &gt;200-årig tall</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3012,10 +3027,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122730426</v>
+        <v>122741513</v>
       </c>
       <c r="B24" t="n">
-        <v>56680</v>
+        <v>90955</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3028,39 +3043,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>102612</v>
+        <v>1202</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Lill-Åsberget, Lill-Åsberget, Ång</t>
+          <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>542150</v>
+        <v>542030</v>
       </c>
       <c r="R24" t="n">
-        <v>7063805</v>
+        <v>7063685</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3119,10 +3129,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122741741</v>
+        <v>122730246</v>
       </c>
       <c r="B25" t="n">
-        <v>90917</v>
+        <v>78769</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3131,38 +3141,38 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Stamåsen, Stamåsen, Ång</t>
+          <t>Lill-Åsberget, Lill-Åsberget, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>542064</v>
+        <v>542168</v>
       </c>
       <c r="R25" t="n">
-        <v>7063777</v>
+        <v>7063849</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3221,10 +3231,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122730177</v>
+        <v>122732558</v>
       </c>
       <c r="B26" t="n">
-        <v>56688</v>
+        <v>97328</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3237,39 +3247,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100138</v>
+        <v>221941</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Lill-Åsberget, Lill-Åsberget, Ång</t>
+          <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>542198</v>
+        <v>541824</v>
       </c>
       <c r="R26" t="n">
-        <v>7063872</v>
+        <v>7063603</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3328,10 +3333,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122733126</v>
+        <v>122732487</v>
       </c>
       <c r="B27" t="n">
-        <v>78766</v>
+        <v>90955</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3344,21 +3349,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3368,10 +3373,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>541858</v>
+        <v>541847</v>
       </c>
       <c r="R27" t="n">
-        <v>7063338</v>
+        <v>7063615</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3430,10 +3435,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122742207</v>
+        <v>122730234</v>
       </c>
       <c r="B28" t="n">
-        <v>90970</v>
+        <v>79850</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3446,21 +3451,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3470,10 +3475,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>542238</v>
+        <v>542187</v>
       </c>
       <c r="R28" t="n">
-        <v>7063973</v>
+        <v>7063885</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3532,10 +3537,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122730759</v>
+        <v>122733126</v>
       </c>
       <c r="B29" t="n">
-        <v>91312</v>
+        <v>78769</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3544,25 +3549,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1506</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3572,10 +3577,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>542045</v>
+        <v>541858</v>
       </c>
       <c r="R29" t="n">
-        <v>7063823</v>
+        <v>7063338</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3634,10 +3639,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122730829</v>
+        <v>122741741</v>
       </c>
       <c r="B30" t="n">
-        <v>78766</v>
+        <v>90920</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3646,25 +3651,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3674,10 +3679,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>542035</v>
+        <v>542064</v>
       </c>
       <c r="R30" t="n">
-        <v>7063816</v>
+        <v>7063777</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3736,10 +3741,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122741763</v>
+        <v>122732264</v>
       </c>
       <c r="B31" t="n">
-        <v>90952</v>
+        <v>82556</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3752,21 +3757,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1202</v>
+        <v>1312</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3776,10 +3781,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>542067</v>
+        <v>541883</v>
       </c>
       <c r="R31" t="n">
-        <v>7063777</v>
+        <v>7063653</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3838,10 +3843,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122741781</v>
+        <v>122730086</v>
       </c>
       <c r="B32" t="n">
-        <v>91301</v>
+        <v>90955</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3850,38 +3855,38 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>2062</v>
+        <v>1202</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Stamåsen, Stamåsen, Ång</t>
+          <t>Lill-Åsberget, Lill-Åsberget, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>542068</v>
+        <v>542258</v>
       </c>
       <c r="R32" t="n">
-        <v>7063778</v>
+        <v>7063917</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3943,7 +3948,7 @@
         <v>122732584</v>
       </c>
       <c r="B33" t="n">
-        <v>97319</v>
+        <v>97322</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4042,10 +4047,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122730246</v>
+        <v>122733041</v>
       </c>
       <c r="B34" t="n">
-        <v>78766</v>
+        <v>90973</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4058,34 +4063,34 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Lill-Åsberget, Lill-Åsberget, Ång</t>
+          <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>542168</v>
+        <v>541873</v>
       </c>
       <c r="R34" t="n">
-        <v>7063849</v>
+        <v>7063379</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4144,10 +4149,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122730499</v>
+        <v>122741691</v>
       </c>
       <c r="B35" t="n">
-        <v>78766</v>
+        <v>56683</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4160,34 +4165,39 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>102612</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Lill-Åsberget, Lill-Åsberget, Ång</t>
+          <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>542132</v>
+        <v>542063</v>
       </c>
       <c r="R35" t="n">
-        <v>7063797</v>
+        <v>7063786</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4246,10 +4256,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122732653</v>
+        <v>122731193</v>
       </c>
       <c r="B36" t="n">
-        <v>90966</v>
+        <v>91353</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4262,21 +4272,16 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1204</v>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>Gränsticka</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4286,10 +4291,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>541760</v>
+        <v>541919</v>
       </c>
       <c r="R36" t="n">
-        <v>7063584</v>
+        <v>7063716</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4348,10 +4353,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122732817</v>
+        <v>122742207</v>
       </c>
       <c r="B37" t="n">
-        <v>56680</v>
+        <v>90973</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4364,39 +4369,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>102612</v>
+        <v>5432</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Stamåsen, Stamåsen, Ång</t>
+          <t>Lill-Åsberget, Lill-Åsberget, Ång</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>541803</v>
+        <v>542238</v>
       </c>
       <c r="R37" t="n">
-        <v>7063479</v>
+        <v>7063973</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4455,10 +4455,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122741376</v>
+        <v>122741763</v>
       </c>
       <c r="B38" t="n">
-        <v>91243</v>
+        <v>90955</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4471,21 +4471,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4495,10 +4495,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>541997</v>
+        <v>542067</v>
       </c>
       <c r="R38" t="n">
-        <v>7063580</v>
+        <v>7063777</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4557,10 +4557,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122732487</v>
+        <v>122729831</v>
       </c>
       <c r="B39" t="n">
-        <v>90952</v>
+        <v>57481</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4573,34 +4573,39 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Stamåsen, Stamåsen, Ång</t>
+          <t>Lill-Åsberget, Lill-Åsberget, Ång</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>541847</v>
+        <v>542249</v>
       </c>
       <c r="R39" t="n">
-        <v>7063615</v>
+        <v>7063942</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -4633,6 +4638,11 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-02-24</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Bohål i torrgran, 2m ovan mark. 5 cm ø. Gott om stående död ved i området.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4659,10 +4669,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122730086</v>
+        <v>122730759</v>
       </c>
       <c r="B40" t="n">
-        <v>90952</v>
+        <v>91315</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4671,38 +4681,38 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1202</v>
+        <v>1506</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Lill-Åsberget, Lill-Åsberget, Ång</t>
+          <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>542258</v>
+        <v>542045</v>
       </c>
       <c r="R40" t="n">
-        <v>7063917</v>
+        <v>7063823</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -4761,10 +4771,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122729831</v>
+        <v>122732657</v>
       </c>
       <c r="B41" t="n">
-        <v>57478</v>
+        <v>90920</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4773,43 +4783,38 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Lill-Åsberget, Lill-Åsberget, Ång</t>
+          <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>542249</v>
+        <v>541761</v>
       </c>
       <c r="R41" t="n">
-        <v>7063942</v>
+        <v>7063583</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -4842,11 +4847,6 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-02-24</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Bohål i torrgran, 2m ovan mark. 5 cm ø. Gott om stående död ved i området.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4873,10 +4873,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122731904</v>
+        <v>122731166</v>
       </c>
       <c r="B42" t="n">
-        <v>78766</v>
+        <v>90973</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4889,21 +4889,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4913,10 +4913,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>541908</v>
+        <v>541922</v>
       </c>
       <c r="R42" t="n">
-        <v>7063682</v>
+        <v>7063717</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -4949,11 +4949,6 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-02-24</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Garnlavsrika partier över hela sluttningen</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4983,7 +4978,7 @@
         <v>122730595</v>
       </c>
       <c r="B43" t="n">
-        <v>90952</v>
+        <v>90955</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5085,7 +5080,7 @@
         <v>122741861</v>
       </c>
       <c r="B44" t="n">
-        <v>79847</v>
+        <v>79850</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5184,10 +5179,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122733041</v>
+        <v>122730004</v>
       </c>
       <c r="B45" t="n">
-        <v>90970</v>
+        <v>90969</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5200,34 +5195,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>5432</v>
+        <v>1204</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Stamåsen, Stamåsen, Ång</t>
+          <t>Lill-Åsberget, Lill-Åsberget, Ång</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>541873</v>
+        <v>542251</v>
       </c>
       <c r="R45" t="n">
-        <v>7063379</v>
+        <v>7063915</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -5286,10 +5281,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122730042</v>
+        <v>122741488</v>
       </c>
       <c r="B46" t="n">
-        <v>91243</v>
+        <v>57497</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5302,34 +5297,39 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>658</v>
+        <v>100049</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Lill-Åsberget, Lill-Åsberget, Ång</t>
+          <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>542248</v>
+        <v>542034</v>
       </c>
       <c r="R46" t="n">
-        <v>7063927</v>
+        <v>7063681</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>

--- a/artfynd/A 3110-2025 artfynd.xlsx
+++ b/artfynd/A 3110-2025 artfynd.xlsx
@@ -1350,10 +1350,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122730042</v>
+        <v>122731904</v>
       </c>
       <c r="B8" t="n">
-        <v>91242</v>
+        <v>78771</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1366,34 +1366,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Lill-Åsberget, Lill-Åsberget, Ång</t>
+          <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>542248</v>
+        <v>541908</v>
       </c>
       <c r="R8" t="n">
-        <v>7063927</v>
+        <v>7063682</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1426,6 +1426,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-02-24</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Garnlavsrika partier över hela sluttningen</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1452,10 +1457,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122732330</v>
+        <v>122742207</v>
       </c>
       <c r="B9" t="n">
-        <v>90920</v>
+        <v>90975</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1464,38 +1469,38 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5447</v>
+        <v>5432</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Stamåsen, Stamåsen, Ång</t>
+          <t>Lill-Åsberget, Lill-Åsberget, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>541875</v>
+        <v>542238</v>
       </c>
       <c r="R9" t="n">
-        <v>7063622</v>
+        <v>7063973</v>
       </c>
       <c r="S9" t="n">
         <v>15</v>
@@ -1554,10 +1559,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122731904</v>
+        <v>122741861</v>
       </c>
       <c r="B10" t="n">
-        <v>78769</v>
+        <v>79852</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1570,34 +1575,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Stamåsen, Stamåsen, Ång</t>
+          <t>Lill-Åsberget, Lill-Åsberget, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>541908</v>
+        <v>542085</v>
       </c>
       <c r="R10" t="n">
-        <v>7063682</v>
+        <v>7063858</v>
       </c>
       <c r="S10" t="n">
         <v>15</v>
@@ -1630,11 +1635,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-02-24</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Garnlavsrika partier över hela sluttningen</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1661,10 +1661,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122730829</v>
+        <v>122730426</v>
       </c>
       <c r="B11" t="n">
-        <v>78769</v>
+        <v>56683</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1677,34 +1677,39 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>102612</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Stamåsen, Stamåsen, Ång</t>
+          <t>Lill-Åsberget, Lill-Åsberget, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>542035</v>
+        <v>542150</v>
       </c>
       <c r="R11" t="n">
-        <v>7063816</v>
+        <v>7063805</v>
       </c>
       <c r="S11" t="n">
         <v>15</v>
@@ -1763,10 +1768,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122732631</v>
+        <v>122733126</v>
       </c>
       <c r="B12" t="n">
-        <v>88306</v>
+        <v>78771</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1779,21 +1784,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>510</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1803,10 +1808,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>541768</v>
+        <v>541858</v>
       </c>
       <c r="R12" t="n">
-        <v>7063586</v>
+        <v>7063338</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1865,10 +1870,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122741376</v>
+        <v>122730177</v>
       </c>
       <c r="B13" t="n">
-        <v>91242</v>
+        <v>56691</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1877,38 +1882,43 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>658</v>
+        <v>100138</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Stamåsen, Stamåsen, Ång</t>
+          <t>Lill-Åsberget, Lill-Åsberget, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>541997</v>
+        <v>542198</v>
       </c>
       <c r="R13" t="n">
-        <v>7063580</v>
+        <v>7063872</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1967,10 +1977,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122732817</v>
+        <v>122733041</v>
       </c>
       <c r="B14" t="n">
-        <v>56683</v>
+        <v>90975</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1983,39 +1993,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>102612</v>
+        <v>5432</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>541803</v>
+        <v>541873</v>
       </c>
       <c r="R14" t="n">
-        <v>7063479</v>
+        <v>7063379</v>
       </c>
       <c r="S14" t="n">
         <v>15</v>
@@ -2074,10 +2079,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122741781</v>
+        <v>122730234</v>
       </c>
       <c r="B15" t="n">
-        <v>91304</v>
+        <v>79852</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2086,38 +2091,38 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2062</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Stamåsen, Stamåsen, Ång</t>
+          <t>Lill-Åsberget, Lill-Åsberget, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>542068</v>
+        <v>542187</v>
       </c>
       <c r="R15" t="n">
-        <v>7063778</v>
+        <v>7063885</v>
       </c>
       <c r="S15" t="n">
         <v>15</v>
@@ -2176,10 +2181,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122732653</v>
+        <v>122730086</v>
       </c>
       <c r="B16" t="n">
-        <v>90969</v>
+        <v>90957</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2192,34 +2197,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1204</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Stamåsen, Stamåsen, Ång</t>
+          <t>Lill-Åsberget, Lill-Åsberget, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>541760</v>
+        <v>542258</v>
       </c>
       <c r="R16" t="n">
-        <v>7063584</v>
+        <v>7063917</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
@@ -2278,10 +2283,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122731014</v>
+        <v>122741513</v>
       </c>
       <c r="B17" t="n">
-        <v>79850</v>
+        <v>90957</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2294,21 +2299,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2318,10 +2323,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>541940</v>
+        <v>542030</v>
       </c>
       <c r="R17" t="n">
-        <v>7063713</v>
+        <v>7063685</v>
       </c>
       <c r="S17" t="n">
         <v>15</v>
@@ -2380,10 +2385,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122731109</v>
+        <v>122741691</v>
       </c>
       <c r="B18" t="n">
-        <v>57481</v>
+        <v>56683</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2396,16 +2401,16 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>102612</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2416,7 +2421,7 @@
       <c r="I18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2425,10 +2430,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>541940</v>
+        <v>542063</v>
       </c>
       <c r="R18" t="n">
-        <v>7063712</v>
+        <v>7063786</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2461,11 +2466,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-02-24</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Äldre ringhack, gammal tall</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2492,10 +2492,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122730499</v>
+        <v>122741763</v>
       </c>
       <c r="B19" t="n">
-        <v>78769</v>
+        <v>90957</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2508,34 +2508,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Lill-Åsberget, Lill-Åsberget, Ång</t>
+          <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>542132</v>
+        <v>542067</v>
       </c>
       <c r="R19" t="n">
-        <v>7063797</v>
+        <v>7063777</v>
       </c>
       <c r="S19" t="n">
         <v>15</v>
@@ -2701,10 +2701,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122730426</v>
+        <v>122730595</v>
       </c>
       <c r="B21" t="n">
-        <v>56683</v>
+        <v>90957</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2717,39 +2717,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>102612</v>
+        <v>1202</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Lill-Åsberget, Lill-Åsberget, Ång</t>
+          <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>542150</v>
+        <v>542097</v>
       </c>
       <c r="R21" t="n">
-        <v>7063805</v>
+        <v>7063815</v>
       </c>
       <c r="S21" t="n">
         <v>15</v>
@@ -2808,10 +2803,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>122730177</v>
+        <v>122731166</v>
       </c>
       <c r="B22" t="n">
-        <v>56691</v>
+        <v>90975</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2820,43 +2815,38 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100138</v>
+        <v>5432</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Lill-Åsberget, Lill-Åsberget, Ång</t>
+          <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>542198</v>
+        <v>541922</v>
       </c>
       <c r="R22" t="n">
-        <v>7063872</v>
+        <v>7063717</v>
       </c>
       <c r="S22" t="n">
         <v>15</v>
@@ -2915,7 +2905,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>122732958</v>
+        <v>122731109</v>
       </c>
       <c r="B23" t="n">
         <v>57481</v>
@@ -2960,10 +2950,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>541820</v>
+        <v>541940</v>
       </c>
       <c r="R23" t="n">
-        <v>7063439</v>
+        <v>7063712</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -3000,7 +2990,7 @@
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Äldre ringhack, &gt;200-årig tall</t>
+          <t>Äldre ringhack, gammal tall</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3027,10 +3017,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122741513</v>
+        <v>122730499</v>
       </c>
       <c r="B24" t="n">
-        <v>90955</v>
+        <v>78771</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3043,34 +3033,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Stamåsen, Stamåsen, Ång</t>
+          <t>Lill-Åsberget, Lill-Åsberget, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>542030</v>
+        <v>542132</v>
       </c>
       <c r="R24" t="n">
-        <v>7063685</v>
+        <v>7063797</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3129,10 +3119,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122730246</v>
+        <v>122732653</v>
       </c>
       <c r="B25" t="n">
-        <v>78769</v>
+        <v>90971</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3145,34 +3135,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>1204</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Lill-Åsberget, Lill-Åsberget, Ång</t>
+          <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>542168</v>
+        <v>541760</v>
       </c>
       <c r="R25" t="n">
-        <v>7063849</v>
+        <v>7063584</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3231,10 +3221,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>122732558</v>
+        <v>122730004</v>
       </c>
       <c r="B26" t="n">
-        <v>97328</v>
+        <v>90971</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3243,38 +3233,38 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>221941</v>
+        <v>1204</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Stamåsen, Stamåsen, Ång</t>
+          <t>Lill-Åsberget, Lill-Åsberget, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>541824</v>
+        <v>542251</v>
       </c>
       <c r="R26" t="n">
-        <v>7063603</v>
+        <v>7063915</v>
       </c>
       <c r="S26" t="n">
         <v>15</v>
@@ -3333,10 +3323,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122732487</v>
+        <v>122730246</v>
       </c>
       <c r="B27" t="n">
-        <v>90955</v>
+        <v>78771</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3349,34 +3339,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Stamåsen, Stamåsen, Ång</t>
+          <t>Lill-Åsberget, Lill-Åsberget, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>541847</v>
+        <v>542168</v>
       </c>
       <c r="R27" t="n">
-        <v>7063615</v>
+        <v>7063849</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3435,10 +3425,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>122730234</v>
+        <v>122732631</v>
       </c>
       <c r="B28" t="n">
-        <v>79850</v>
+        <v>88308</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3451,34 +3441,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6458</v>
+        <v>510</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Lill-Åsberget, Lill-Åsberget, Ång</t>
+          <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>542187</v>
+        <v>541768</v>
       </c>
       <c r="R28" t="n">
-        <v>7063885</v>
+        <v>7063586</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3537,10 +3527,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>122733126</v>
+        <v>122729831</v>
       </c>
       <c r="B29" t="n">
-        <v>78769</v>
+        <v>57481</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3553,34 +3543,39 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Stamåsen, Stamåsen, Ång</t>
+          <t>Lill-Åsberget, Lill-Åsberget, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>541858</v>
+        <v>542249</v>
       </c>
       <c r="R29" t="n">
-        <v>7063338</v>
+        <v>7063942</v>
       </c>
       <c r="S29" t="n">
         <v>15</v>
@@ -3613,6 +3608,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-02-24</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Bohål i torrgran, 2m ovan mark. 5 cm ø. Gott om stående död ved i området.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3639,10 +3639,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122741741</v>
+        <v>122730829</v>
       </c>
       <c r="B30" t="n">
-        <v>90920</v>
+        <v>78771</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3651,25 +3651,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3679,10 +3679,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>542064</v>
+        <v>542035</v>
       </c>
       <c r="R30" t="n">
-        <v>7063777</v>
+        <v>7063816</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3741,10 +3741,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122732264</v>
+        <v>122741488</v>
       </c>
       <c r="B31" t="n">
-        <v>82556</v>
+        <v>57497</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3757,34 +3757,39 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1312</v>
+        <v>100049</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>541883</v>
+        <v>542034</v>
       </c>
       <c r="R31" t="n">
-        <v>7063653</v>
+        <v>7063681</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3843,10 +3848,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>122730086</v>
+        <v>122732264</v>
       </c>
       <c r="B32" t="n">
-        <v>90955</v>
+        <v>82558</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3859,34 +3864,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1202</v>
+        <v>1312</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Lill-Åsberget, Lill-Åsberget, Ång</t>
+          <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>542258</v>
+        <v>541883</v>
       </c>
       <c r="R32" t="n">
-        <v>7063917</v>
+        <v>7063653</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3945,10 +3950,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122732584</v>
+        <v>122730759</v>
       </c>
       <c r="B33" t="n">
-        <v>97322</v>
+        <v>91317</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3957,25 +3962,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>221945</v>
+        <v>1506</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ostticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Skeletocutis odora</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Sacc.) Ginns</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3985,10 +3990,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>541821</v>
+        <v>542045</v>
       </c>
       <c r="R33" t="n">
-        <v>7063616</v>
+        <v>7063823</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -4047,10 +4052,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>122733041</v>
+        <v>122732657</v>
       </c>
       <c r="B34" t="n">
-        <v>90973</v>
+        <v>90922</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4059,25 +4064,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5432</v>
+        <v>5447</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4087,10 +4092,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>541873</v>
+        <v>541761</v>
       </c>
       <c r="R34" t="n">
-        <v>7063379</v>
+        <v>7063583</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4149,10 +4154,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122741691</v>
+        <v>122730042</v>
       </c>
       <c r="B35" t="n">
-        <v>56683</v>
+        <v>91244</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4165,39 +4170,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>102612</v>
+        <v>658</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Stamåsen, Stamåsen, Ång</t>
+          <t>Lill-Åsberget, Lill-Åsberget, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>542063</v>
+        <v>542248</v>
       </c>
       <c r="R35" t="n">
-        <v>7063786</v>
+        <v>7063927</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4256,10 +4256,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>122731193</v>
+        <v>122732958</v>
       </c>
       <c r="B36" t="n">
-        <v>91353</v>
+        <v>57481</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4272,29 +4272,39 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6040186</v>
+        <v>100109</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Leptoporus mollis</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Quél.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>541919</v>
+        <v>541820</v>
       </c>
       <c r="R36" t="n">
-        <v>7063716</v>
+        <v>7063439</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4327,6 +4337,11 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-02-24</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Äldre ringhack, &gt;200-årig tall</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4353,10 +4368,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>122742207</v>
+        <v>122741376</v>
       </c>
       <c r="B37" t="n">
-        <v>90973</v>
+        <v>91244</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4369,34 +4384,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>5432</v>
+        <v>658</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Lill-Åsberget, Lill-Åsberget, Ång</t>
+          <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>542238</v>
+        <v>541997</v>
       </c>
       <c r="R37" t="n">
-        <v>7063973</v>
+        <v>7063580</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4455,10 +4470,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>122741763</v>
+        <v>122731193</v>
       </c>
       <c r="B38" t="n">
-        <v>90955</v>
+        <v>91355</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4471,21 +4486,16 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1202</v>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>Ullticka</t>
-        </is>
+        <v>6040186</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Leptoporus mollis</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Pers.:Fr.) Quél.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4495,10 +4505,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>542067</v>
+        <v>541919</v>
       </c>
       <c r="R38" t="n">
-        <v>7063777</v>
+        <v>7063716</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4557,10 +4567,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>122729831</v>
+        <v>122732817</v>
       </c>
       <c r="B39" t="n">
-        <v>57481</v>
+        <v>56683</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4573,16 +4583,16 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>102612</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -4593,19 +4603,19 @@
       <c r="I39" t="inlineStr"/>
       <c r="M39" t="inlineStr">
         <is>
-          <t>gammalt bo</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Lill-Åsberget, Lill-Åsberget, Ång</t>
+          <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>542249</v>
+        <v>541803</v>
       </c>
       <c r="R39" t="n">
-        <v>7063942</v>
+        <v>7063479</v>
       </c>
       <c r="S39" t="n">
         <v>15</v>
@@ -4638,11 +4648,6 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-02-24</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Bohål i torrgran, 2m ovan mark. 5 cm ø. Gott om stående död ved i området.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4669,10 +4674,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>122730759</v>
+        <v>122732487</v>
       </c>
       <c r="B40" t="n">
-        <v>91315</v>
+        <v>90957</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4681,25 +4686,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1506</v>
+        <v>1202</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Ostticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Skeletocutis odora</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Sacc.) Ginns</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4709,10 +4714,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>542045</v>
+        <v>541847</v>
       </c>
       <c r="R40" t="n">
-        <v>7063823</v>
+        <v>7063615</v>
       </c>
       <c r="S40" t="n">
         <v>15</v>
@@ -4771,10 +4776,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>122732657</v>
+        <v>122731014</v>
       </c>
       <c r="B41" t="n">
-        <v>90920</v>
+        <v>79852</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4783,25 +4788,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>5447</v>
+        <v>6458</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4811,10 +4816,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>541761</v>
+        <v>541940</v>
       </c>
       <c r="R41" t="n">
-        <v>7063583</v>
+        <v>7063713</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -4873,10 +4878,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>122731166</v>
+        <v>122741781</v>
       </c>
       <c r="B42" t="n">
-        <v>90973</v>
+        <v>91306</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4885,25 +4890,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>5432</v>
+        <v>2062</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4913,10 +4918,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>541922</v>
+        <v>542068</v>
       </c>
       <c r="R42" t="n">
-        <v>7063717</v>
+        <v>7063778</v>
       </c>
       <c r="S42" t="n">
         <v>15</v>
@@ -4975,10 +4980,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122730595</v>
+        <v>122732558</v>
       </c>
       <c r="B43" t="n">
-        <v>90955</v>
+        <v>97330</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4987,25 +4992,25 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1202</v>
+        <v>221941</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5015,10 +5020,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>542097</v>
+        <v>541824</v>
       </c>
       <c r="R43" t="n">
-        <v>7063815</v>
+        <v>7063603</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -5077,10 +5082,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122741861</v>
+        <v>122732584</v>
       </c>
       <c r="B44" t="n">
-        <v>79850</v>
+        <v>97324</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5089,38 +5094,38 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6458</v>
+        <v>221945</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Lill-Åsberget, Lill-Åsberget, Ång</t>
+          <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>542085</v>
+        <v>541821</v>
       </c>
       <c r="R44" t="n">
-        <v>7063858</v>
+        <v>7063616</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>
@@ -5179,10 +5184,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>122730004</v>
+        <v>122741741</v>
       </c>
       <c r="B45" t="n">
-        <v>90969</v>
+        <v>90922</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5191,38 +5196,38 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1204</v>
+        <v>5447</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Lill-Åsberget, Lill-Åsberget, Ång</t>
+          <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>542251</v>
+        <v>542064</v>
       </c>
       <c r="R45" t="n">
-        <v>7063915</v>
+        <v>7063777</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -5281,10 +5286,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>122741488</v>
+        <v>122732330</v>
       </c>
       <c r="B46" t="n">
-        <v>57497</v>
+        <v>90922</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5293,43 +5298,38 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>542034</v>
+        <v>541875</v>
       </c>
       <c r="R46" t="n">
-        <v>7063681</v>
+        <v>7063622</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>

--- a/artfynd/A 3110-2025 artfynd.xlsx
+++ b/artfynd/A 3110-2025 artfynd.xlsx
@@ -6097,10 +6097,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>130154406</v>
+        <v>130152471</v>
       </c>
       <c r="B54" t="n">
-        <v>79095</v>
+        <v>91639</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6108,21 +6108,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6132,13 +6132,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>541569</v>
+        <v>542048</v>
       </c>
       <c r="R54" t="n">
-        <v>7063377</v>
+        <v>7063680</v>
       </c>
       <c r="S54" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6165,9 +6165,19 @@
           <t>2025-12-16</t>
         </is>
       </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>12:48</t>
+        </is>
+      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-12-16</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6182,22 +6192,22 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>130152994</v>
+        <v>130153953</v>
       </c>
       <c r="B55" t="n">
-        <v>79095</v>
+        <v>80200</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6205,39 +6215,34 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="K55" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>541785</v>
+        <v>541656</v>
       </c>
       <c r="R55" t="n">
-        <v>7063407</v>
+        <v>7063312</v>
       </c>
       <c r="S55" t="n">
         <v>15</v>
@@ -6267,9 +6272,19 @@
           <t>2025-12-16</t>
         </is>
       </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>14:16</t>
+        </is>
+      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-12-16</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6284,19 +6299,19 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>130153953</v>
+        <v>130153802</v>
       </c>
       <c r="B56" t="n">
         <v>80200</v>
@@ -6331,10 +6346,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>541656</v>
+        <v>541701</v>
       </c>
       <c r="R56" t="n">
-        <v>7063312</v>
+        <v>7063258</v>
       </c>
       <c r="S56" t="n">
         <v>15</v>
@@ -6364,19 +6379,9 @@
           <t>2025-12-16</t>
         </is>
       </c>
-      <c r="Z56" t="inlineStr">
-        <is>
-          <t>14:16</t>
-        </is>
-      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-12-16</t>
-        </is>
-      </c>
-      <c r="AB56" t="inlineStr">
-        <is>
-          <t>14:16</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6391,22 +6396,22 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>130153802</v>
+        <v>130154406</v>
       </c>
       <c r="B57" t="n">
-        <v>80200</v>
+        <v>79095</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6414,21 +6419,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6438,10 +6443,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>541701</v>
+        <v>541569</v>
       </c>
       <c r="R57" t="n">
-        <v>7063258</v>
+        <v>7063377</v>
       </c>
       <c r="S57" t="n">
         <v>15</v>
@@ -6500,10 +6505,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>130152471</v>
+        <v>130152994</v>
       </c>
       <c r="B58" t="n">
-        <v>91639</v>
+        <v>79095</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6511,37 +6516,42 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>542048</v>
+        <v>541785</v>
       </c>
       <c r="R58" t="n">
-        <v>7063680</v>
+        <v>7063407</v>
       </c>
       <c r="S58" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6568,19 +6578,9 @@
           <t>2025-12-16</t>
         </is>
       </c>
-      <c r="Z58" t="inlineStr">
-        <is>
-          <t>12:48</t>
-        </is>
-      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-12-16</t>
-        </is>
-      </c>
-      <c r="AB58" t="inlineStr">
-        <is>
-          <t>12:48</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6595,12 +6595,12 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
@@ -8788,10 +8788,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>130154569</v>
+        <v>130151970</v>
       </c>
       <c r="B80" t="n">
-        <v>57741</v>
+        <v>79095</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8799,39 +8799,34 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
-      <c r="M80" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Stamåsen, Stamåsen, Ång</t>
+          <t>Lill-Åsberget, Lill-Åsberget, Ång</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>541683</v>
+        <v>542334</v>
       </c>
       <c r="R80" t="n">
-        <v>7063551</v>
+        <v>7064066</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8863,7 +8858,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -8873,12 +8868,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>14:57</t>
-        </is>
-      </c>
-      <c r="AC80" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -8905,10 +8895,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>130151970</v>
+        <v>130154569</v>
       </c>
       <c r="B81" t="n">
-        <v>79095</v>
+        <v>57741</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8916,34 +8906,39 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Lill-Åsberget, Lill-Åsberget, Ång</t>
+          <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>542334</v>
+        <v>541683</v>
       </c>
       <c r="R81" t="n">
-        <v>7064066</v>
+        <v>7063551</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8975,7 +8970,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -8985,7 +8980,12 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>14:57</t>
+        </is>
+      </c>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9828,10 +9828,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>130154037</v>
+        <v>130152347</v>
       </c>
       <c r="B90" t="n">
-        <v>57741</v>
+        <v>80200</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9839,42 +9839,37 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
-      <c r="M90" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P90" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>541608</v>
+        <v>542089</v>
       </c>
       <c r="R90" t="n">
-        <v>7063341</v>
+        <v>7063746</v>
       </c>
       <c r="S90" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -9903,7 +9898,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -9913,12 +9908,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>14:25</t>
-        </is>
-      </c>
-      <c r="AC90" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -9945,7 +9935,7 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>130154192</v>
+        <v>130154037</v>
       </c>
       <c r="B91" t="n">
         <v>57741</v>
@@ -9976,7 +9966,7 @@
       <c r="I91" t="inlineStr"/>
       <c r="M91" t="inlineStr">
         <is>
-          <t>gammalt bo</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P91" t="inlineStr">
@@ -9985,10 +9975,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>541590</v>
+        <v>541608</v>
       </c>
       <c r="R91" t="n">
-        <v>7063340</v>
+        <v>7063341</v>
       </c>
       <c r="S91" t="n">
         <v>15</v>
@@ -10018,14 +10008,24 @@
           <t>2025-12-16</t>
         </is>
       </c>
+      <c r="Z91" t="inlineStr">
+        <is>
+          <t>14:25</t>
+        </is>
+      </c>
       <c r="AA91" t="inlineStr">
         <is>
           <t>2025-12-16</t>
         </is>
       </c>
+      <c r="AB91" t="inlineStr">
+        <is>
+          <t>14:25</t>
+        </is>
+      </c>
       <c r="AC91" t="inlineStr">
         <is>
-          <t>Äldre bohål i granhögstubbe, 3m ovan mark</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10040,22 +10040,22 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>130152347</v>
+        <v>130154192</v>
       </c>
       <c r="B92" t="n">
-        <v>80200</v>
+        <v>57741</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10063,37 +10063,42 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="P92" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>542089</v>
+        <v>541590</v>
       </c>
       <c r="R92" t="n">
-        <v>7063746</v>
+        <v>7063340</v>
       </c>
       <c r="S92" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -10120,19 +10125,14 @@
           <t>2025-12-16</t>
         </is>
       </c>
-      <c r="Z92" t="inlineStr">
-        <is>
-          <t>12:41</t>
-        </is>
-      </c>
       <c r="AA92" t="inlineStr">
         <is>
           <t>2025-12-16</t>
         </is>
       </c>
-      <c r="AB92" t="inlineStr">
-        <is>
-          <t>12:41</t>
+      <c r="AC92" t="inlineStr">
+        <is>
+          <t>Äldre bohål i granhögstubbe, 3m ovan mark</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10147,12 +10147,12 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>

--- a/artfynd/A 3110-2025 artfynd.xlsx
+++ b/artfynd/A 3110-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY92"/>
+  <dimension ref="A1:AY111"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8020,10 +8020,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>130153730</v>
+        <v>130152352</v>
       </c>
       <c r="B73" t="n">
-        <v>79095</v>
+        <v>80200</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8031,21 +8031,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8055,13 +8055,13 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>541768</v>
+        <v>542077</v>
       </c>
       <c r="R73" t="n">
-        <v>7063269</v>
+        <v>7063744</v>
       </c>
       <c r="S73" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8088,19 +8088,14 @@
           <t>2025-12-16</t>
         </is>
       </c>
-      <c r="Z73" t="inlineStr">
-        <is>
-          <t>13:58</t>
-        </is>
-      </c>
       <c r="AA73" t="inlineStr">
         <is>
           <t>2025-12-16</t>
         </is>
       </c>
-      <c r="AB73" t="inlineStr">
-        <is>
-          <t>13:58</t>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>På död björk</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8115,22 +8110,22 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>130152352</v>
+        <v>130153766</v>
       </c>
       <c r="B74" t="n">
-        <v>80200</v>
+        <v>57741</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8138,34 +8133,39 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P74" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>542077</v>
+        <v>541750</v>
       </c>
       <c r="R74" t="n">
-        <v>7063744</v>
+        <v>7063250</v>
       </c>
       <c r="S74" t="n">
         <v>15</v>
@@ -8195,14 +8195,24 @@
           <t>2025-12-16</t>
         </is>
       </c>
+      <c r="Z74" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
       <c r="AA74" t="inlineStr">
         <is>
           <t>2025-12-16</t>
         </is>
       </c>
+      <c r="AB74" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
       <c r="AC74" t="inlineStr">
         <is>
-          <t>På död björk</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8217,22 +8227,22 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>130153766</v>
+        <v>130153730</v>
       </c>
       <c r="B75" t="n">
-        <v>57741</v>
+        <v>79095</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8240,42 +8250,37 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
-      <c r="M75" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P75" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>541750</v>
+        <v>541768</v>
       </c>
       <c r="R75" t="n">
-        <v>7063250</v>
+        <v>7063269</v>
       </c>
       <c r="S75" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8304,7 +8309,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8314,12 +8319,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>14:00</t>
-        </is>
-      </c>
-      <c r="AC75" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9828,10 +9828,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>130152347</v>
+        <v>130154037</v>
       </c>
       <c r="B90" t="n">
-        <v>80200</v>
+        <v>57741</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9839,37 +9839,42 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P90" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>542089</v>
+        <v>541608</v>
       </c>
       <c r="R90" t="n">
-        <v>7063746</v>
+        <v>7063341</v>
       </c>
       <c r="S90" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -9898,7 +9903,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -9908,7 +9913,12 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>14:25</t>
+        </is>
+      </c>
+      <c r="AC90" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -9935,7 +9945,7 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>130154037</v>
+        <v>130154192</v>
       </c>
       <c r="B91" t="n">
         <v>57741</v>
@@ -9966,7 +9976,7 @@
       <c r="I91" t="inlineStr"/>
       <c r="M91" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="P91" t="inlineStr">
@@ -9975,10 +9985,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>541608</v>
+        <v>541590</v>
       </c>
       <c r="R91" t="n">
-        <v>7063341</v>
+        <v>7063340</v>
       </c>
       <c r="S91" t="n">
         <v>15</v>
@@ -10008,24 +10018,14 @@
           <t>2025-12-16</t>
         </is>
       </c>
-      <c r="Z91" t="inlineStr">
-        <is>
-          <t>14:25</t>
-        </is>
-      </c>
       <c r="AA91" t="inlineStr">
         <is>
           <t>2025-12-16</t>
         </is>
       </c>
-      <c r="AB91" t="inlineStr">
-        <is>
-          <t>14:25</t>
-        </is>
-      </c>
       <c r="AC91" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>Äldre bohål i granhögstubbe, 3m ovan mark</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10040,22 +10040,22 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>130154192</v>
+        <v>130152347</v>
       </c>
       <c r="B92" t="n">
-        <v>57741</v>
+        <v>80200</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10063,42 +10063,37 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
-      <c r="M92" t="inlineStr">
-        <is>
-          <t>gammalt bo</t>
-        </is>
-      </c>
       <c r="P92" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>541590</v>
+        <v>542089</v>
       </c>
       <c r="R92" t="n">
-        <v>7063340</v>
+        <v>7063746</v>
       </c>
       <c r="S92" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -10125,14 +10120,19 @@
           <t>2025-12-16</t>
         </is>
       </c>
+      <c r="Z92" t="inlineStr">
+        <is>
+          <t>12:41</t>
+        </is>
+      </c>
       <c r="AA92" t="inlineStr">
         <is>
           <t>2025-12-16</t>
         </is>
       </c>
-      <c r="AC92" t="inlineStr">
-        <is>
-          <t>Äldre bohål i granhögstubbe, 3m ovan mark</t>
+      <c r="AB92" t="inlineStr">
+        <is>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10147,15 +10147,1913 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>130228030</v>
+      </c>
+      <c r="B93" t="n">
+        <v>91854</v>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E93" t="n">
+        <v>48</v>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>Lappticka</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>Amylocystis lapponica</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>(Romell) Bondartsev &amp; Singer</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr"/>
+      <c r="P93" t="inlineStr">
+        <is>
+          <t>Stamåsen, Stamåsen, Ång</t>
+        </is>
+      </c>
+      <c r="Q93" t="n">
+        <v>541970</v>
+      </c>
+      <c r="R93" t="n">
+        <v>7063699</v>
+      </c>
+      <c r="S93" t="n">
+        <v>15</v>
+      </c>
+      <c r="T93" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U93" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V93" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W93" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y93" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AA93" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AD93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT93" t="inlineStr"/>
+      <c r="AW93" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX93" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY93" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>130228951</v>
+      </c>
+      <c r="B94" t="n">
+        <v>80200</v>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E94" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr"/>
+      <c r="P94" t="inlineStr">
+        <is>
+          <t>Stamåsen, Stamåsen, Ång</t>
+        </is>
+      </c>
+      <c r="Q94" t="n">
+        <v>541618</v>
+      </c>
+      <c r="R94" t="n">
+        <v>7063274</v>
+      </c>
+      <c r="S94" t="n">
+        <v>15</v>
+      </c>
+      <c r="T94" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U94" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V94" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W94" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y94" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AA94" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AD94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT94" t="inlineStr"/>
+      <c r="AW94" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX94" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY94" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>130227326</v>
+      </c>
+      <c r="B95" t="n">
+        <v>91939</v>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E95" t="n">
+        <v>658</v>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>Fomitopsis rosea</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr"/>
+      <c r="P95" t="inlineStr">
+        <is>
+          <t>Lill-Åsberget, Lill-Åsberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q95" t="n">
+        <v>542243</v>
+      </c>
+      <c r="R95" t="n">
+        <v>7063987</v>
+      </c>
+      <c r="S95" t="n">
+        <v>15</v>
+      </c>
+      <c r="T95" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U95" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V95" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W95" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y95" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AA95" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AD95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT95" t="inlineStr"/>
+      <c r="AW95" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX95" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY95" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>130228013</v>
+      </c>
+      <c r="B96" t="n">
+        <v>91939</v>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E96" t="n">
+        <v>658</v>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>Fomitopsis rosea</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr"/>
+      <c r="P96" t="inlineStr">
+        <is>
+          <t>Stamåsen, Stamåsen, Ång</t>
+        </is>
+      </c>
+      <c r="Q96" t="n">
+        <v>541974</v>
+      </c>
+      <c r="R96" t="n">
+        <v>7063706</v>
+      </c>
+      <c r="S96" t="n">
+        <v>15</v>
+      </c>
+      <c r="T96" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U96" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V96" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W96" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y96" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AA96" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AD96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT96" t="inlineStr"/>
+      <c r="AW96" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX96" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY96" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>130228996</v>
+      </c>
+      <c r="B97" t="n">
+        <v>80200</v>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E97" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr"/>
+      <c r="P97" t="inlineStr">
+        <is>
+          <t>Stamåsen, Stamåsen, Ång</t>
+        </is>
+      </c>
+      <c r="Q97" t="n">
+        <v>541577</v>
+      </c>
+      <c r="R97" t="n">
+        <v>7063273</v>
+      </c>
+      <c r="S97" t="n">
+        <v>15</v>
+      </c>
+      <c r="T97" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U97" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V97" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W97" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y97" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AA97" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AD97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT97" t="inlineStr"/>
+      <c r="AW97" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX97" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY97" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>130229083</v>
+      </c>
+      <c r="B98" t="n">
+        <v>80201</v>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E98" t="n">
+        <v>2081</v>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>Skrovellav</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>Lobaria scrobiculata</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr"/>
+      <c r="P98" t="inlineStr">
+        <is>
+          <t>Stamåsen, Stamåsen, Ång</t>
+        </is>
+      </c>
+      <c r="Q98" t="n">
+        <v>541521</v>
+      </c>
+      <c r="R98" t="n">
+        <v>7063220</v>
+      </c>
+      <c r="S98" t="n">
+        <v>15</v>
+      </c>
+      <c r="T98" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U98" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V98" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W98" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y98" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AA98" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AD98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT98" t="inlineStr"/>
+      <c r="AW98" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX98" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY98" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>130229019</v>
+      </c>
+      <c r="B99" t="n">
+        <v>80201</v>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E99" t="n">
+        <v>2081</v>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>Skrovellav</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>Lobaria scrobiculata</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>(Scop.) DC.</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr"/>
+      <c r="P99" t="inlineStr">
+        <is>
+          <t>Stamåsen, Stamåsen, Ång</t>
+        </is>
+      </c>
+      <c r="Q99" t="n">
+        <v>541571</v>
+      </c>
+      <c r="R99" t="n">
+        <v>7063268</v>
+      </c>
+      <c r="S99" t="n">
+        <v>15</v>
+      </c>
+      <c r="T99" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U99" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V99" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W99" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y99" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AA99" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AD99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT99" t="inlineStr"/>
+      <c r="AW99" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX99" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY99" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>130229726</v>
+      </c>
+      <c r="B100" t="n">
+        <v>57741</v>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E100" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr"/>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P100" t="inlineStr">
+        <is>
+          <t>Stamåsen, Stamåsen, Ång</t>
+        </is>
+      </c>
+      <c r="Q100" t="n">
+        <v>541753</v>
+      </c>
+      <c r="R100" t="n">
+        <v>7063285</v>
+      </c>
+      <c r="S100" t="n">
+        <v>10</v>
+      </c>
+      <c r="T100" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U100" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V100" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W100" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y100" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="Z100" t="inlineStr">
+        <is>
+          <t>14:49</t>
+        </is>
+      </c>
+      <c r="AA100" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AB100" t="inlineStr">
+        <is>
+          <t>14:49</t>
+        </is>
+      </c>
+      <c r="AC100" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT100" t="inlineStr"/>
+      <c r="AW100" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX100" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY100" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>130232684</v>
+      </c>
+      <c r="B101" t="n">
+        <v>80104</v>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E101" t="n">
+        <v>6456</v>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>Skinnlav</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>Leptogium saturninum</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr"/>
+      <c r="P101" t="inlineStr">
+        <is>
+          <t>Lill-Åsberget, Lill-Åsberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q101" t="n">
+        <v>542292</v>
+      </c>
+      <c r="R101" t="n">
+        <v>7063919</v>
+      </c>
+      <c r="S101" t="n">
+        <v>15</v>
+      </c>
+      <c r="T101" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U101" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V101" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W101" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y101" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AA101" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AD101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT101" t="inlineStr"/>
+      <c r="AW101" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX101" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY101" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>130228879</v>
+      </c>
+      <c r="B102" t="n">
+        <v>92094</v>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E102" t="n">
+        <v>1209</v>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>Rynkskinn</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>Hermanssonia centrifuga</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr"/>
+      <c r="P102" t="inlineStr">
+        <is>
+          <t>Stamåsen, Stamåsen, Ång</t>
+        </is>
+      </c>
+      <c r="Q102" t="n">
+        <v>541663</v>
+      </c>
+      <c r="R102" t="n">
+        <v>7063324</v>
+      </c>
+      <c r="S102" t="n">
+        <v>15</v>
+      </c>
+      <c r="T102" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U102" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V102" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W102" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y102" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AA102" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AD102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT102" t="inlineStr"/>
+      <c r="AW102" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX102" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY102" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>130227381</v>
+      </c>
+      <c r="B103" t="n">
+        <v>80200</v>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E103" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr"/>
+      <c r="P103" t="inlineStr">
+        <is>
+          <t>Lill-Åsberget, Lill-Åsberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q103" t="n">
+        <v>542205</v>
+      </c>
+      <c r="R103" t="n">
+        <v>7063951</v>
+      </c>
+      <c r="S103" t="n">
+        <v>15</v>
+      </c>
+      <c r="T103" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U103" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V103" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W103" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y103" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AA103" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AD103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT103" t="inlineStr"/>
+      <c r="AW103" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX103" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY103" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" t="n">
+        <v>130227624</v>
+      </c>
+      <c r="B104" t="n">
+        <v>57741</v>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E104" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr"/>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P104" t="inlineStr">
+        <is>
+          <t>Stamåsen, Stamåsen, Ång</t>
+        </is>
+      </c>
+      <c r="Q104" t="n">
+        <v>542070</v>
+      </c>
+      <c r="R104" t="n">
+        <v>7063767</v>
+      </c>
+      <c r="S104" t="n">
+        <v>15</v>
+      </c>
+      <c r="T104" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U104" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V104" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W104" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y104" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AA104" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AC104" t="inlineStr">
+        <is>
+          <t>Äldre ringhack, gran</t>
+        </is>
+      </c>
+      <c r="AD104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT104" t="inlineStr"/>
+      <c r="AW104" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX104" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY104" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" t="n">
+        <v>130228071</v>
+      </c>
+      <c r="B105" t="n">
+        <v>91605</v>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E105" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr"/>
+      <c r="P105" t="inlineStr">
+        <is>
+          <t>Stamåsen, Stamåsen, Ång</t>
+        </is>
+      </c>
+      <c r="Q105" t="n">
+        <v>541940</v>
+      </c>
+      <c r="R105" t="n">
+        <v>7063661</v>
+      </c>
+      <c r="S105" t="n">
+        <v>15</v>
+      </c>
+      <c r="T105" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U105" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V105" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W105" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y105" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AA105" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AD105" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE105" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG105" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT105" t="inlineStr"/>
+      <c r="AW105" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX105" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY105" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" t="n">
+        <v>130232597</v>
+      </c>
+      <c r="B106" t="n">
+        <v>57741</v>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E106" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr"/>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P106" t="inlineStr">
+        <is>
+          <t>Lill-Åsberget, Lill-Åsberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q106" t="n">
+        <v>542247</v>
+      </c>
+      <c r="R106" t="n">
+        <v>7063890</v>
+      </c>
+      <c r="S106" t="n">
+        <v>15</v>
+      </c>
+      <c r="T106" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U106" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V106" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W106" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y106" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AA106" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AC106" t="inlineStr">
+        <is>
+          <t>Färska ringhack, gran</t>
+        </is>
+      </c>
+      <c r="AD106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT106" t="inlineStr"/>
+      <c r="AW106" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX106" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY106" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" t="n">
+        <v>130227321</v>
+      </c>
+      <c r="B107" t="n">
+        <v>91641</v>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E107" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr"/>
+      <c r="P107" t="inlineStr">
+        <is>
+          <t>Lill-Åsberget, Lill-Åsberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q107" t="n">
+        <v>542243</v>
+      </c>
+      <c r="R107" t="n">
+        <v>7063987</v>
+      </c>
+      <c r="S107" t="n">
+        <v>15</v>
+      </c>
+      <c r="T107" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U107" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V107" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W107" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y107" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AA107" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AD107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT107" t="inlineStr"/>
+      <c r="AW107" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX107" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY107" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" t="n">
+        <v>130232341</v>
+      </c>
+      <c r="B108" t="n">
+        <v>56931</v>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E108" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr"/>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="P108" t="inlineStr">
+        <is>
+          <t>Stamåsen, Stamåsen, Ång</t>
+        </is>
+      </c>
+      <c r="Q108" t="n">
+        <v>542026</v>
+      </c>
+      <c r="R108" t="n">
+        <v>7063537</v>
+      </c>
+      <c r="S108" t="n">
+        <v>15</v>
+      </c>
+      <c r="T108" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U108" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V108" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W108" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y108" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AA108" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AD108" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE108" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG108" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT108" t="inlineStr"/>
+      <c r="AW108" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX108" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY108" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" t="n">
+        <v>130229089</v>
+      </c>
+      <c r="B109" t="n">
+        <v>80200</v>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E109" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr"/>
+      <c r="P109" t="inlineStr">
+        <is>
+          <t>Stamåsen, Stamåsen, Ång</t>
+        </is>
+      </c>
+      <c r="Q109" t="n">
+        <v>541521</v>
+      </c>
+      <c r="R109" t="n">
+        <v>7063220</v>
+      </c>
+      <c r="S109" t="n">
+        <v>15</v>
+      </c>
+      <c r="T109" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U109" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V109" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W109" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y109" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AA109" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AD109" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE109" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG109" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT109" t="inlineStr"/>
+      <c r="AW109" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX109" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY109" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" t="n">
+        <v>130228880</v>
+      </c>
+      <c r="B110" t="n">
+        <v>91641</v>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E110" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr"/>
+      <c r="P110" t="inlineStr">
+        <is>
+          <t>Stamåsen, Stamåsen, Ång</t>
+        </is>
+      </c>
+      <c r="Q110" t="n">
+        <v>541663</v>
+      </c>
+      <c r="R110" t="n">
+        <v>7063324</v>
+      </c>
+      <c r="S110" t="n">
+        <v>15</v>
+      </c>
+      <c r="T110" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U110" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V110" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W110" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y110" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AA110" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AD110" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE110" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG110" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT110" t="inlineStr"/>
+      <c r="AW110" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX110" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY110" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" t="n">
+        <v>130227562</v>
+      </c>
+      <c r="B111" t="n">
+        <v>57741</v>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E111" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr"/>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P111" t="inlineStr">
+        <is>
+          <t>Lill-Åsberget, Lill-Åsberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q111" t="n">
+        <v>542148</v>
+      </c>
+      <c r="R111" t="n">
+        <v>7063819</v>
+      </c>
+      <c r="S111" t="n">
+        <v>15</v>
+      </c>
+      <c r="T111" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U111" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V111" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W111" t="inlineStr">
+        <is>
+          <t>Ström</t>
+        </is>
+      </c>
+      <c r="Y111" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AA111" t="inlineStr">
+        <is>
+          <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AC111" t="inlineStr">
+        <is>
+          <t>Ringhack, tall</t>
+        </is>
+      </c>
+      <c r="AD111" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE111" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG111" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT111" t="inlineStr"/>
+      <c r="AW111" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX111" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY111" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 3110-2025 artfynd.xlsx
+++ b/artfynd/A 3110-2025 artfynd.xlsx
@@ -5388,32 +5388,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>130154078</v>
+        <v>130154007</v>
       </c>
       <c r="B47" t="n">
-        <v>79095</v>
+        <v>80229</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5423,10 +5423,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>541577</v>
+        <v>541615</v>
       </c>
       <c r="R47" t="n">
-        <v>7063340</v>
+        <v>7063313</v>
       </c>
       <c r="S47" t="n">
         <v>15</v>
@@ -5456,19 +5456,9 @@
           <t>2025-12-16</t>
         </is>
       </c>
-      <c r="Z47" t="inlineStr">
-        <is>
-          <t>14:28</t>
-        </is>
-      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-12-16</t>
-        </is>
-      </c>
-      <c r="AB47" t="inlineStr">
-        <is>
-          <t>14:28</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5483,19 +5473,19 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>130153573</v>
+        <v>130154078</v>
       </c>
       <c r="B48" t="n">
         <v>79095</v>
@@ -5530,10 +5520,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>541822</v>
+        <v>541577</v>
       </c>
       <c r="R48" t="n">
-        <v>7063308</v>
+        <v>7063340</v>
       </c>
       <c r="S48" t="n">
         <v>15</v>
@@ -5563,9 +5553,19 @@
           <t>2025-12-16</t>
         </is>
       </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>14:28</t>
+        </is>
+      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-12-16</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5580,44 +5580,44 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>130154007</v>
+        <v>130153573</v>
       </c>
       <c r="B49" t="n">
-        <v>80229</v>
+        <v>79095</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5627,10 +5627,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>541615</v>
+        <v>541822</v>
       </c>
       <c r="R49" t="n">
-        <v>7063313</v>
+        <v>7063308</v>
       </c>
       <c r="S49" t="n">
         <v>15</v>
@@ -6097,10 +6097,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>130152471</v>
+        <v>130153953</v>
       </c>
       <c r="B54" t="n">
-        <v>91639</v>
+        <v>80200</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6108,21 +6108,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6132,13 +6132,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>542048</v>
+        <v>541656</v>
       </c>
       <c r="R54" t="n">
-        <v>7063680</v>
+        <v>7063312</v>
       </c>
       <c r="S54" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6167,7 +6167,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6177,7 +6177,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6204,7 +6204,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>130153953</v>
+        <v>130153802</v>
       </c>
       <c r="B55" t="n">
         <v>80200</v>
@@ -6239,10 +6239,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>541656</v>
+        <v>541701</v>
       </c>
       <c r="R55" t="n">
-        <v>7063312</v>
+        <v>7063258</v>
       </c>
       <c r="S55" t="n">
         <v>15</v>
@@ -6272,19 +6272,9 @@
           <t>2025-12-16</t>
         </is>
       </c>
-      <c r="Z55" t="inlineStr">
-        <is>
-          <t>14:16</t>
-        </is>
-      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-12-16</t>
-        </is>
-      </c>
-      <c r="AB55" t="inlineStr">
-        <is>
-          <t>14:16</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6299,22 +6289,22 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>130153802</v>
+        <v>130152471</v>
       </c>
       <c r="B56" t="n">
-        <v>80200</v>
+        <v>91641</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6322,21 +6312,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6346,13 +6336,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>541701</v>
+        <v>542048</v>
       </c>
       <c r="R56" t="n">
-        <v>7063258</v>
+        <v>7063680</v>
       </c>
       <c r="S56" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6379,9 +6369,19 @@
           <t>2025-12-16</t>
         </is>
       </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>12:48</t>
+        </is>
+      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-12-16</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6396,12 +6396,12 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
@@ -6607,10 +6607,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>130152623</v>
+        <v>130153842</v>
       </c>
       <c r="B59" t="n">
-        <v>79095</v>
+        <v>91662</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6618,21 +6618,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6642,10 +6642,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>541908</v>
+        <v>541694</v>
       </c>
       <c r="R59" t="n">
-        <v>7063597</v>
+        <v>7063239</v>
       </c>
       <c r="S59" t="n">
         <v>15</v>
@@ -6704,10 +6704,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>130153842</v>
+        <v>130152977</v>
       </c>
       <c r="B60" t="n">
-        <v>91660</v>
+        <v>79095</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6715,21 +6715,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6739,13 +6739,13 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>541694</v>
+        <v>541780</v>
       </c>
       <c r="R60" t="n">
-        <v>7063239</v>
+        <v>7063439</v>
       </c>
       <c r="S60" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -6772,9 +6772,19 @@
           <t>2025-12-16</t>
         </is>
       </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>13:18</t>
+        </is>
+      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-12-16</t>
+        </is>
+      </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6789,19 +6799,19 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>130152977</v>
+        <v>130152623</v>
       </c>
       <c r="B61" t="n">
         <v>79095</v>
@@ -6836,13 +6846,13 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>541780</v>
+        <v>541908</v>
       </c>
       <c r="R61" t="n">
-        <v>7063439</v>
+        <v>7063597</v>
       </c>
       <c r="S61" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -6869,19 +6879,9 @@
           <t>2025-12-16</t>
         </is>
       </c>
-      <c r="Z61" t="inlineStr">
-        <is>
-          <t>13:18</t>
-        </is>
-      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-12-16</t>
-        </is>
-      </c>
-      <c r="AB61" t="inlineStr">
-        <is>
-          <t>13:18</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6896,12 +6896,12 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
@@ -6911,7 +6911,7 @@
         <v>130152037</v>
       </c>
       <c r="B62" t="n">
-        <v>91937</v>
+        <v>91939</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7005,10 +7005,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>130152010</v>
+        <v>130152528</v>
       </c>
       <c r="B63" t="n">
-        <v>80200</v>
+        <v>57738</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7016,34 +7016,39 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Lill-Åsberget, Lill-Åsberget, Ång</t>
+          <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>542347</v>
+        <v>542003</v>
       </c>
       <c r="R63" t="n">
-        <v>7064044</v>
+        <v>7063641</v>
       </c>
       <c r="S63" t="n">
         <v>15</v>
@@ -7102,10 +7107,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>130152528</v>
+        <v>130152102</v>
       </c>
       <c r="B64" t="n">
-        <v>57738</v>
+        <v>79095</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7113,39 +7118,34 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Stamåsen, Stamåsen, Ång</t>
+          <t>Lill-Åsberget, Lill-Åsberget, Ång</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>542003</v>
+        <v>542330</v>
       </c>
       <c r="R64" t="n">
-        <v>7063641</v>
+        <v>7063952</v>
       </c>
       <c r="S64" t="n">
         <v>15</v>
@@ -7204,10 +7204,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>130152102</v>
+        <v>130152010</v>
       </c>
       <c r="B65" t="n">
-        <v>79095</v>
+        <v>80200</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7215,21 +7215,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7239,10 +7239,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>542330</v>
+        <v>542347</v>
       </c>
       <c r="R65" t="n">
-        <v>7063952</v>
+        <v>7064044</v>
       </c>
       <c r="S65" t="n">
         <v>15</v>
@@ -7301,10 +7301,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>130152789</v>
+        <v>130152774</v>
       </c>
       <c r="B66" t="n">
-        <v>83073</v>
+        <v>57741</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7312,37 +7312,42 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>541769</v>
+        <v>541786</v>
       </c>
       <c r="R66" t="n">
-        <v>7063539</v>
+        <v>7063538</v>
       </c>
       <c r="S66" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7369,9 +7374,19 @@
           <t>2025-12-16</t>
         </is>
       </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>13:08</t>
+        </is>
+      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-12-16</t>
+        </is>
+      </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7386,12 +7401,12 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
@@ -7495,10 +7510,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>130152602</v>
+        <v>130152789</v>
       </c>
       <c r="B68" t="n">
-        <v>79095</v>
+        <v>83073</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7506,21 +7521,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7530,13 +7545,13 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>541973</v>
+        <v>541769</v>
       </c>
       <c r="R68" t="n">
-        <v>7063647</v>
+        <v>7063539</v>
       </c>
       <c r="S68" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -7563,19 +7578,9 @@
           <t>2025-12-16</t>
         </is>
       </c>
-      <c r="Z68" t="inlineStr">
-        <is>
-          <t>12:57</t>
-        </is>
-      </c>
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-12-16</t>
-        </is>
-      </c>
-      <c r="AB68" t="inlineStr">
-        <is>
-          <t>12:57</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7590,19 +7595,19 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>130153922</v>
+        <v>130152602</v>
       </c>
       <c r="B69" t="n">
         <v>79095</v>
@@ -7637,13 +7642,13 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>541656</v>
+        <v>541973</v>
       </c>
       <c r="R69" t="n">
-        <v>7063282</v>
+        <v>7063647</v>
       </c>
       <c r="S69" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -7672,7 +7677,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -7682,7 +7687,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>14:13</t>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7709,10 +7714,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>130152774</v>
+        <v>130153922</v>
       </c>
       <c r="B70" t="n">
-        <v>57741</v>
+        <v>79095</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7720,42 +7725,37 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P70" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>541786</v>
+        <v>541656</v>
       </c>
       <c r="R70" t="n">
-        <v>7063538</v>
+        <v>7063282</v>
       </c>
       <c r="S70" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -7784,7 +7784,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -7794,7 +7794,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8122,10 +8122,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>130153766</v>
+        <v>130153730</v>
       </c>
       <c r="B74" t="n">
-        <v>57741</v>
+        <v>79095</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8133,42 +8133,37 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
-      <c r="M74" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P74" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>541750</v>
+        <v>541768</v>
       </c>
       <c r="R74" t="n">
-        <v>7063250</v>
+        <v>7063269</v>
       </c>
       <c r="S74" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8197,7 +8192,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8207,12 +8202,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>14:00</t>
-        </is>
-      </c>
-      <c r="AC74" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8239,10 +8229,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>130153730</v>
+        <v>130153766</v>
       </c>
       <c r="B75" t="n">
-        <v>79095</v>
+        <v>57741</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8250,37 +8240,42 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P75" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>541768</v>
+        <v>541750</v>
       </c>
       <c r="R75" t="n">
-        <v>7063269</v>
+        <v>7063250</v>
       </c>
       <c r="S75" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8309,7 +8304,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8319,7 +8314,12 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8346,10 +8346,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>130153074</v>
+        <v>130154525</v>
       </c>
       <c r="B76" t="n">
-        <v>79095</v>
+        <v>57741</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8357,34 +8357,39 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P76" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>541807</v>
+        <v>541592</v>
       </c>
       <c r="R76" t="n">
-        <v>7063402</v>
+        <v>7063490</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8416,7 +8421,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -8426,7 +8431,12 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>14:51</t>
+        </is>
+      </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8453,7 +8463,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>130153365</v>
+        <v>130153074</v>
       </c>
       <c r="B77" t="n">
         <v>79095</v>
@@ -8488,10 +8498,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>541860</v>
+        <v>541807</v>
       </c>
       <c r="R77" t="n">
-        <v>7063366</v>
+        <v>7063402</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8523,7 +8533,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -8533,7 +8543,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8560,49 +8570,45 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>130154401</v>
+        <v>130153365</v>
       </c>
       <c r="B78" t="n">
-        <v>98831</v>
+        <v>79095</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>541577</v>
+        <v>541860</v>
       </c>
       <c r="R78" t="n">
-        <v>7063340</v>
+        <v>7063366</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8634,7 +8640,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -8644,7 +8650,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8671,38 +8677,37 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>130154525</v>
+        <v>130154401</v>
       </c>
       <c r="B79" t="n">
-        <v>57741</v>
+        <v>98833</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr"/>
-      <c r="M79" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>10</t>
         </is>
       </c>
       <c r="P79" t="inlineStr">
@@ -8711,10 +8716,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>541592</v>
+        <v>541577</v>
       </c>
       <c r="R79" t="n">
-        <v>7063490</v>
+        <v>7063340</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8746,7 +8751,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -8756,12 +8761,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>14:51</t>
-        </is>
-      </c>
-      <c r="AC79" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9012,27 +9012,27 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>130154023</v>
+        <v>130154014</v>
       </c>
       <c r="B82" t="n">
-        <v>79095</v>
+        <v>80235</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -9047,10 +9047,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>541595</v>
+        <v>541603</v>
       </c>
       <c r="R82" t="n">
-        <v>7063307</v>
+        <v>7063297</v>
       </c>
       <c r="S82" t="n">
         <v>15</v>
@@ -9109,27 +9109,27 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>130154014</v>
+        <v>130154023</v>
       </c>
       <c r="B83" t="n">
-        <v>80235</v>
+        <v>79095</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6463</v>
+        <v>6425</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -9144,10 +9144,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>541603</v>
+        <v>541595</v>
       </c>
       <c r="R83" t="n">
-        <v>7063297</v>
+        <v>7063307</v>
       </c>
       <c r="S83" t="n">
         <v>15</v>
@@ -9520,7 +9520,7 @@
         <v>130153013</v>
       </c>
       <c r="B87" t="n">
-        <v>91603</v>
+        <v>91605</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9828,10 +9828,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>130154037</v>
+        <v>130152347</v>
       </c>
       <c r="B90" t="n">
-        <v>57741</v>
+        <v>80200</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9839,42 +9839,37 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
-      <c r="M90" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P90" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>541608</v>
+        <v>542089</v>
       </c>
       <c r="R90" t="n">
-        <v>7063341</v>
+        <v>7063746</v>
       </c>
       <c r="S90" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -9903,7 +9898,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -9913,12 +9908,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>14:25</t>
-        </is>
-      </c>
-      <c r="AC90" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -9945,7 +9935,7 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>130154192</v>
+        <v>130154037</v>
       </c>
       <c r="B91" t="n">
         <v>57741</v>
@@ -9976,7 +9966,7 @@
       <c r="I91" t="inlineStr"/>
       <c r="M91" t="inlineStr">
         <is>
-          <t>gammalt bo</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P91" t="inlineStr">
@@ -9985,10 +9975,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>541590</v>
+        <v>541608</v>
       </c>
       <c r="R91" t="n">
-        <v>7063340</v>
+        <v>7063341</v>
       </c>
       <c r="S91" t="n">
         <v>15</v>
@@ -10018,14 +10008,24 @@
           <t>2025-12-16</t>
         </is>
       </c>
+      <c r="Z91" t="inlineStr">
+        <is>
+          <t>14:25</t>
+        </is>
+      </c>
       <c r="AA91" t="inlineStr">
         <is>
           <t>2025-12-16</t>
         </is>
       </c>
+      <c r="AB91" t="inlineStr">
+        <is>
+          <t>14:25</t>
+        </is>
+      </c>
       <c r="AC91" t="inlineStr">
         <is>
-          <t>Äldre bohål i granhögstubbe, 3m ovan mark</t>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10040,22 +10040,22 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>130152347</v>
+        <v>130154192</v>
       </c>
       <c r="B92" t="n">
-        <v>80200</v>
+        <v>57741</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10063,37 +10063,42 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>gammalt bo</t>
+        </is>
+      </c>
       <c r="P92" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>542089</v>
+        <v>541590</v>
       </c>
       <c r="R92" t="n">
-        <v>7063746</v>
+        <v>7063340</v>
       </c>
       <c r="S92" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -10120,19 +10125,14 @@
           <t>2025-12-16</t>
         </is>
       </c>
-      <c r="Z92" t="inlineStr">
-        <is>
-          <t>12:41</t>
-        </is>
-      </c>
       <c r="AA92" t="inlineStr">
         <is>
           <t>2025-12-16</t>
         </is>
       </c>
-      <c r="AB92" t="inlineStr">
-        <is>
-          <t>12:41</t>
+      <c r="AC92" t="inlineStr">
+        <is>
+          <t>Äldre bohål i granhögstubbe, 3m ovan mark</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10147,12 +10147,12 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
@@ -10256,10 +10256,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>130228951</v>
+        <v>130227326</v>
       </c>
       <c r="B94" t="n">
-        <v>80200</v>
+        <v>91939</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10267,34 +10267,34 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Stamåsen, Stamåsen, Ång</t>
+          <t>Lill-Åsberget, Lill-Åsberget, Ång</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>541618</v>
+        <v>542243</v>
       </c>
       <c r="R94" t="n">
-        <v>7063274</v>
+        <v>7063987</v>
       </c>
       <c r="S94" t="n">
         <v>15</v>
@@ -10353,10 +10353,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>130227326</v>
+        <v>130228951</v>
       </c>
       <c r="B95" t="n">
-        <v>91939</v>
+        <v>80200</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10364,34 +10364,34 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Lill-Åsberget, Lill-Åsberget, Ång</t>
+          <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>542243</v>
+        <v>541618</v>
       </c>
       <c r="R95" t="n">
-        <v>7063987</v>
+        <v>7063274</v>
       </c>
       <c r="S95" t="n">
         <v>15</v>
@@ -10644,10 +10644,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>130229083</v>
+        <v>130229726</v>
       </c>
       <c r="B98" t="n">
-        <v>80201</v>
+        <v>57741</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10655,37 +10655,42 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P98" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>541521</v>
+        <v>541753</v>
       </c>
       <c r="R98" t="n">
-        <v>7063220</v>
+        <v>7063285</v>
       </c>
       <c r="S98" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T98" t="inlineStr">
         <is>
@@ -10712,9 +10717,24 @@
           <t>2025-12-20</t>
         </is>
       </c>
+      <c r="Z98" t="inlineStr">
+        <is>
+          <t>14:49</t>
+        </is>
+      </c>
       <c r="AA98" t="inlineStr">
         <is>
           <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AB98" t="inlineStr">
+        <is>
+          <t>14:49</t>
+        </is>
+      </c>
+      <c r="AC98" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -10729,12 +10749,12 @@
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
@@ -10838,10 +10858,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>130229726</v>
+        <v>130229083</v>
       </c>
       <c r="B100" t="n">
-        <v>57741</v>
+        <v>80201</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10849,42 +10869,37 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
-      <c r="M100" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P100" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>541753</v>
+        <v>541521</v>
       </c>
       <c r="R100" t="n">
-        <v>7063285</v>
+        <v>7063220</v>
       </c>
       <c r="S100" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T100" t="inlineStr">
         <is>
@@ -10911,24 +10926,9 @@
           <t>2025-12-20</t>
         </is>
       </c>
-      <c r="Z100" t="inlineStr">
-        <is>
-          <t>14:49</t>
-        </is>
-      </c>
       <c r="AA100" t="inlineStr">
         <is>
           <t>2025-12-20</t>
-        </is>
-      </c>
-      <c r="AB100" t="inlineStr">
-        <is>
-          <t>14:49</t>
-        </is>
-      </c>
-      <c r="AC100" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -10943,12 +10943,12 @@
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
@@ -11246,50 +11246,45 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>130227624</v>
+        <v>130228071</v>
       </c>
       <c r="B104" t="n">
-        <v>57741</v>
+        <v>91605</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
-      <c r="M104" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P104" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>542070</v>
+        <v>541940</v>
       </c>
       <c r="R104" t="n">
-        <v>7063767</v>
+        <v>7063661</v>
       </c>
       <c r="S104" t="n">
         <v>15</v>
@@ -11322,11 +11317,6 @@
       <c r="AA104" t="inlineStr">
         <is>
           <t>2025-12-20</t>
-        </is>
-      </c>
-      <c r="AC104" t="inlineStr">
-        <is>
-          <t>Äldre ringhack, gran</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11353,45 +11343,50 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>130228071</v>
+        <v>130227624</v>
       </c>
       <c r="B105" t="n">
-        <v>91605</v>
+        <v>57741</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P105" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>541940</v>
+        <v>542070</v>
       </c>
       <c r="R105" t="n">
-        <v>7063661</v>
+        <v>7063767</v>
       </c>
       <c r="S105" t="n">
         <v>15</v>
@@ -11424,6 +11419,11 @@
       <c r="AA105" t="inlineStr">
         <is>
           <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AC105" t="inlineStr">
+        <is>
+          <t>Äldre ringhack, gran</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11557,45 +11557,50 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>130227321</v>
+        <v>130232341</v>
       </c>
       <c r="B107" t="n">
-        <v>91641</v>
+        <v>56931</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>1202</v>
+        <v>100138</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P107" t="inlineStr">
         <is>
-          <t>Lill-Åsberget, Lill-Åsberget, Ång</t>
+          <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>542243</v>
+        <v>542026</v>
       </c>
       <c r="R107" t="n">
-        <v>7063987</v>
+        <v>7063537</v>
       </c>
       <c r="S107" t="n">
         <v>15</v>
@@ -11654,50 +11659,45 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>130232341</v>
+        <v>130227321</v>
       </c>
       <c r="B108" t="n">
-        <v>56931</v>
+        <v>91641</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>100138</v>
+        <v>1202</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
-      <c r="M108" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P108" t="inlineStr">
         <is>
-          <t>Stamåsen, Stamåsen, Ång</t>
+          <t>Lill-Åsberget, Lill-Åsberget, Ång</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>542026</v>
+        <v>542243</v>
       </c>
       <c r="R108" t="n">
-        <v>7063537</v>
+        <v>7063987</v>
       </c>
       <c r="S108" t="n">
         <v>15</v>

--- a/artfynd/A 3110-2025 artfynd.xlsx
+++ b/artfynd/A 3110-2025 artfynd.xlsx
@@ -5391,7 +5391,7 @@
         <v>130154007</v>
       </c>
       <c r="B47" t="n">
-        <v>80229</v>
+        <v>80314</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5488,7 +5488,7 @@
         <v>130154078</v>
       </c>
       <c r="B48" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5595,7 +5595,7 @@
         <v>130153573</v>
       </c>
       <c r="B49" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5692,7 +5692,7 @@
         <v>130153774</v>
       </c>
       <c r="B50" t="n">
-        <v>80200</v>
+        <v>80285</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5789,7 +5789,7 @@
         <v>130153973</v>
       </c>
       <c r="B51" t="n">
-        <v>80200</v>
+        <v>80285</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5883,10 +5883,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>130152521</v>
+        <v>130152070</v>
       </c>
       <c r="B52" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5914,14 +5914,14 @@
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Stamåsen, Stamåsen, Ång</t>
+          <t>Lill-Åsberget, Lill-Åsberget, Ång</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>541998</v>
+        <v>542344</v>
       </c>
       <c r="R52" t="n">
-        <v>7063666</v>
+        <v>7064036</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5953,7 +5953,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -5963,7 +5963,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5990,10 +5990,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>130152070</v>
+        <v>130152521</v>
       </c>
       <c r="B53" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6021,14 +6021,14 @@
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Lill-Åsberget, Lill-Åsberget, Ång</t>
+          <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>542344</v>
+        <v>541998</v>
       </c>
       <c r="R53" t="n">
-        <v>7064036</v>
+        <v>7063666</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6060,7 +6060,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6070,7 +6070,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6100,7 +6100,7 @@
         <v>130153953</v>
       </c>
       <c r="B54" t="n">
-        <v>80200</v>
+        <v>80285</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6204,10 +6204,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>130153802</v>
+        <v>130152471</v>
       </c>
       <c r="B55" t="n">
-        <v>80200</v>
+        <v>91728</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6215,21 +6215,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6239,13 +6239,13 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>541701</v>
+        <v>542048</v>
       </c>
       <c r="R55" t="n">
-        <v>7063258</v>
+        <v>7063680</v>
       </c>
       <c r="S55" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6272,9 +6272,19 @@
           <t>2025-12-16</t>
         </is>
       </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>12:48</t>
+        </is>
+      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>2025-12-16</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6289,22 +6299,22 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>130152471</v>
+        <v>130153802</v>
       </c>
       <c r="B56" t="n">
-        <v>91641</v>
+        <v>80285</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6312,21 +6322,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6336,13 +6346,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>542048</v>
+        <v>541701</v>
       </c>
       <c r="R56" t="n">
-        <v>7063680</v>
+        <v>7063258</v>
       </c>
       <c r="S56" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6369,19 +6379,9 @@
           <t>2025-12-16</t>
         </is>
       </c>
-      <c r="Z56" t="inlineStr">
-        <is>
-          <t>12:48</t>
-        </is>
-      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-12-16</t>
-        </is>
-      </c>
-      <c r="AB56" t="inlineStr">
-        <is>
-          <t>12:48</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6396,12 +6396,12 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
@@ -6411,7 +6411,7 @@
         <v>130154406</v>
       </c>
       <c r="B57" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6508,7 +6508,7 @@
         <v>130152994</v>
       </c>
       <c r="B58" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6607,10 +6607,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>130153842</v>
+        <v>130152623</v>
       </c>
       <c r="B59" t="n">
-        <v>91662</v>
+        <v>79180</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6618,21 +6618,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6642,10 +6642,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>541694</v>
+        <v>541908</v>
       </c>
       <c r="R59" t="n">
-        <v>7063239</v>
+        <v>7063597</v>
       </c>
       <c r="S59" t="n">
         <v>15</v>
@@ -6704,10 +6704,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>130152977</v>
+        <v>130153842</v>
       </c>
       <c r="B60" t="n">
-        <v>79095</v>
+        <v>91749</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6715,21 +6715,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6739,13 +6739,13 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>541780</v>
+        <v>541694</v>
       </c>
       <c r="R60" t="n">
-        <v>7063439</v>
+        <v>7063239</v>
       </c>
       <c r="S60" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -6772,19 +6772,9 @@
           <t>2025-12-16</t>
         </is>
       </c>
-      <c r="Z60" t="inlineStr">
-        <is>
-          <t>13:18</t>
-        </is>
-      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-12-16</t>
-        </is>
-      </c>
-      <c r="AB60" t="inlineStr">
-        <is>
-          <t>13:18</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6799,22 +6789,22 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>130152623</v>
+        <v>130152977</v>
       </c>
       <c r="B61" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6846,13 +6836,13 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>541908</v>
+        <v>541780</v>
       </c>
       <c r="R61" t="n">
-        <v>7063597</v>
+        <v>7063439</v>
       </c>
       <c r="S61" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -6879,9 +6869,19 @@
           <t>2025-12-16</t>
         </is>
       </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>13:18</t>
+        </is>
+      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-12-16</t>
+        </is>
+      </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6896,12 +6896,12 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
@@ -6911,7 +6911,7 @@
         <v>130152037</v>
       </c>
       <c r="B62" t="n">
-        <v>91939</v>
+        <v>92026</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7008,7 +7008,7 @@
         <v>130152528</v>
       </c>
       <c r="B63" t="n">
-        <v>57738</v>
+        <v>57823</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7110,7 +7110,7 @@
         <v>130152102</v>
       </c>
       <c r="B64" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7207,7 +7207,7 @@
         <v>130152010</v>
       </c>
       <c r="B65" t="n">
-        <v>80200</v>
+        <v>80285</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7301,10 +7301,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>130152774</v>
+        <v>130152789</v>
       </c>
       <c r="B66" t="n">
-        <v>57741</v>
+        <v>83158</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7312,42 +7312,37 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>541786</v>
+        <v>541769</v>
       </c>
       <c r="R66" t="n">
-        <v>7063538</v>
+        <v>7063539</v>
       </c>
       <c r="S66" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7374,19 +7369,9 @@
           <t>2025-12-16</t>
         </is>
       </c>
-      <c r="Z66" t="inlineStr">
-        <is>
-          <t>13:08</t>
-        </is>
-      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-12-16</t>
-        </is>
-      </c>
-      <c r="AB66" t="inlineStr">
-        <is>
-          <t>13:08</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7401,22 +7386,22 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>130154006</v>
+        <v>130153060</v>
       </c>
       <c r="B67" t="n">
-        <v>80200</v>
+        <v>57823</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7424,34 +7409,39 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P67" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>541614</v>
+        <v>541839</v>
       </c>
       <c r="R67" t="n">
-        <v>7063281</v>
+        <v>7063371</v>
       </c>
       <c r="S67" t="n">
         <v>15</v>
@@ -7510,10 +7500,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>130152789</v>
+        <v>130152602</v>
       </c>
       <c r="B68" t="n">
-        <v>83073</v>
+        <v>79180</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7521,21 +7511,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7545,13 +7535,13 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>541769</v>
+        <v>541973</v>
       </c>
       <c r="R68" t="n">
-        <v>7063539</v>
+        <v>7063647</v>
       </c>
       <c r="S68" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -7578,9 +7568,19 @@
           <t>2025-12-16</t>
         </is>
       </c>
+      <c r="Z68" t="inlineStr">
+        <is>
+          <t>12:57</t>
+        </is>
+      </c>
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-12-16</t>
+        </is>
+      </c>
+      <c r="AB68" t="inlineStr">
+        <is>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7595,22 +7595,22 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>130152602</v>
+        <v>130152774</v>
       </c>
       <c r="B69" t="n">
-        <v>79095</v>
+        <v>57826</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7618,34 +7618,39 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>541973</v>
+        <v>541786</v>
       </c>
       <c r="R69" t="n">
-        <v>7063647</v>
+        <v>7063538</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7677,7 +7682,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -7687,7 +7692,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7717,7 +7722,7 @@
         <v>130153922</v>
       </c>
       <c r="B70" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7821,10 +7826,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>130153060</v>
+        <v>130154006</v>
       </c>
       <c r="B71" t="n">
-        <v>57738</v>
+        <v>80285</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7832,39 +7837,34 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P71" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>541839</v>
+        <v>541614</v>
       </c>
       <c r="R71" t="n">
-        <v>7063371</v>
+        <v>7063281</v>
       </c>
       <c r="S71" t="n">
         <v>15</v>
@@ -7926,7 +7926,7 @@
         <v>130154548</v>
       </c>
       <c r="B72" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8023,7 +8023,7 @@
         <v>130152352</v>
       </c>
       <c r="B73" t="n">
-        <v>80200</v>
+        <v>80285</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8122,10 +8122,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>130153730</v>
+        <v>130153766</v>
       </c>
       <c r="B74" t="n">
-        <v>79095</v>
+        <v>57826</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8133,37 +8133,42 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P74" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>541768</v>
+        <v>541750</v>
       </c>
       <c r="R74" t="n">
-        <v>7063269</v>
+        <v>7063250</v>
       </c>
       <c r="S74" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8192,7 +8197,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8202,7 +8207,12 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8229,10 +8239,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>130153766</v>
+        <v>130153730</v>
       </c>
       <c r="B75" t="n">
-        <v>57741</v>
+        <v>79180</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8240,42 +8250,37 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
-      <c r="M75" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P75" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>541750</v>
+        <v>541768</v>
       </c>
       <c r="R75" t="n">
-        <v>7063250</v>
+        <v>7063269</v>
       </c>
       <c r="S75" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8304,7 +8309,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8314,12 +8319,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>14:00</t>
-        </is>
-      </c>
-      <c r="AC75" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8346,10 +8346,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>130154525</v>
+        <v>130153074</v>
       </c>
       <c r="B76" t="n">
-        <v>57741</v>
+        <v>79180</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8357,39 +8357,34 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
-      <c r="M76" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P76" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>541592</v>
+        <v>541807</v>
       </c>
       <c r="R76" t="n">
-        <v>7063490</v>
+        <v>7063402</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8421,7 +8416,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -8431,12 +8426,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>14:51</t>
-        </is>
-      </c>
-      <c r="AC76" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8463,45 +8453,49 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>130153074</v>
+        <v>130154401</v>
       </c>
       <c r="B77" t="n">
-        <v>79095</v>
+        <v>98920</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P77" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>541807</v>
+        <v>541577</v>
       </c>
       <c r="R77" t="n">
-        <v>7063402</v>
+        <v>7063340</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8533,7 +8527,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -8543,7 +8537,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8570,10 +8564,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>130153365</v>
+        <v>130154525</v>
       </c>
       <c r="B78" t="n">
-        <v>79095</v>
+        <v>57826</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8581,34 +8575,39 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P78" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>541860</v>
+        <v>541592</v>
       </c>
       <c r="R78" t="n">
-        <v>7063366</v>
+        <v>7063490</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8640,7 +8639,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -8650,7 +8649,12 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>14:51</t>
+        </is>
+      </c>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8677,49 +8681,45 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>130154401</v>
+        <v>130153365</v>
       </c>
       <c r="B79" t="n">
-        <v>98833</v>
+        <v>79180</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>541577</v>
+        <v>541860</v>
       </c>
       <c r="R79" t="n">
-        <v>7063340</v>
+        <v>7063366</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8751,7 +8751,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -8761,7 +8761,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8791,7 +8791,7 @@
         <v>130151970</v>
       </c>
       <c r="B80" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8898,7 +8898,7 @@
         <v>130154569</v>
       </c>
       <c r="B81" t="n">
-        <v>57741</v>
+        <v>57826</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9015,7 +9015,7 @@
         <v>130154014</v>
       </c>
       <c r="B82" t="n">
-        <v>80235</v>
+        <v>80320</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9112,7 +9112,7 @@
         <v>130154023</v>
       </c>
       <c r="B83" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9209,7 +9209,7 @@
         <v>130152372</v>
       </c>
       <c r="B84" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9303,32 +9303,32 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>130153121</v>
+        <v>130153013</v>
       </c>
       <c r="B85" t="n">
-        <v>79095</v>
+        <v>91692</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9338,10 +9338,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>541827</v>
+        <v>541792</v>
       </c>
       <c r="R85" t="n">
-        <v>7063362</v>
+        <v>7063398</v>
       </c>
       <c r="S85" t="n">
         <v>15</v>
@@ -9371,19 +9371,9 @@
           <t>2025-12-16</t>
         </is>
       </c>
-      <c r="Z85" t="inlineStr">
-        <is>
-          <t>13:34</t>
-        </is>
-      </c>
       <c r="AA85" t="inlineStr">
         <is>
           <t>2025-12-16</t>
-        </is>
-      </c>
-      <c r="AB85" t="inlineStr">
-        <is>
-          <t>13:34</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9398,12 +9388,12 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
@@ -9413,7 +9403,7 @@
         <v>130153494</v>
       </c>
       <c r="B86" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9517,32 +9507,32 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>130153013</v>
+        <v>130153121</v>
       </c>
       <c r="B87" t="n">
-        <v>91605</v>
+        <v>79180</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9552,10 +9542,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>541792</v>
+        <v>541827</v>
       </c>
       <c r="R87" t="n">
-        <v>7063398</v>
+        <v>7063362</v>
       </c>
       <c r="S87" t="n">
         <v>15</v>
@@ -9585,9 +9575,19 @@
           <t>2025-12-16</t>
         </is>
       </c>
+      <c r="Z87" t="inlineStr">
+        <is>
+          <t>13:34</t>
+        </is>
+      </c>
       <c r="AA87" t="inlineStr">
         <is>
           <t>2025-12-16</t>
+        </is>
+      </c>
+      <c r="AB87" t="inlineStr">
+        <is>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9602,12 +9602,12 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
@@ -9617,7 +9617,7 @@
         <v>130153689</v>
       </c>
       <c r="B88" t="n">
-        <v>57741</v>
+        <v>57826</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9734,7 +9734,7 @@
         <v>130152767</v>
       </c>
       <c r="B89" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9828,10 +9828,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>130152347</v>
+        <v>130154037</v>
       </c>
       <c r="B90" t="n">
-        <v>80200</v>
+        <v>57826</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9839,37 +9839,42 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P90" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>542089</v>
+        <v>541608</v>
       </c>
       <c r="R90" t="n">
-        <v>7063746</v>
+        <v>7063341</v>
       </c>
       <c r="S90" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -9898,7 +9903,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -9908,7 +9913,12 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>14:25</t>
+        </is>
+      </c>
+      <c r="AC90" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -9935,10 +9945,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>130154037</v>
+        <v>130152347</v>
       </c>
       <c r="B91" t="n">
-        <v>57741</v>
+        <v>80285</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9946,42 +9956,37 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
-      <c r="M91" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P91" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>541608</v>
+        <v>542089</v>
       </c>
       <c r="R91" t="n">
-        <v>7063341</v>
+        <v>7063746</v>
       </c>
       <c r="S91" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -10010,7 +10015,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>14:25</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -10020,12 +10025,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>14:25</t>
-        </is>
-      </c>
-      <c r="AC91" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10055,7 +10055,7 @@
         <v>130154192</v>
       </c>
       <c r="B92" t="n">
-        <v>57741</v>
+        <v>57826</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10162,7 +10162,7 @@
         <v>130228030</v>
       </c>
       <c r="B93" t="n">
-        <v>91854</v>
+        <v>91941</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10256,10 +10256,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>130227326</v>
+        <v>130228951</v>
       </c>
       <c r="B94" t="n">
-        <v>91939</v>
+        <v>80285</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10267,34 +10267,34 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Lill-Åsberget, Lill-Åsberget, Ång</t>
+          <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>542243</v>
+        <v>541618</v>
       </c>
       <c r="R94" t="n">
-        <v>7063987</v>
+        <v>7063274</v>
       </c>
       <c r="S94" t="n">
         <v>15</v>
@@ -10353,10 +10353,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>130228951</v>
+        <v>130227326</v>
       </c>
       <c r="B95" t="n">
-        <v>80200</v>
+        <v>92026</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10364,34 +10364,34 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Stamåsen, Stamåsen, Ång</t>
+          <t>Lill-Åsberget, Lill-Åsberget, Ång</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>541618</v>
+        <v>542243</v>
       </c>
       <c r="R95" t="n">
-        <v>7063274</v>
+        <v>7063987</v>
       </c>
       <c r="S95" t="n">
         <v>15</v>
@@ -10453,7 +10453,7 @@
         <v>130228013</v>
       </c>
       <c r="B96" t="n">
-        <v>91939</v>
+        <v>92026</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10550,7 +10550,7 @@
         <v>130228996</v>
       </c>
       <c r="B97" t="n">
-        <v>80200</v>
+        <v>80285</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10647,7 +10647,7 @@
         <v>130229726</v>
       </c>
       <c r="B98" t="n">
-        <v>57741</v>
+        <v>57826</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10764,7 +10764,7 @@
         <v>130229019</v>
       </c>
       <c r="B99" t="n">
-        <v>80201</v>
+        <v>80286</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10861,7 +10861,7 @@
         <v>130229083</v>
       </c>
       <c r="B100" t="n">
-        <v>80201</v>
+        <v>80286</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10958,7 +10958,7 @@
         <v>130232684</v>
       </c>
       <c r="B101" t="n">
-        <v>80104</v>
+        <v>80189</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11055,7 +11055,7 @@
         <v>130228879</v>
       </c>
       <c r="B102" t="n">
-        <v>92094</v>
+        <v>92181</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11152,7 +11152,7 @@
         <v>130227381</v>
       </c>
       <c r="B103" t="n">
-        <v>80200</v>
+        <v>80285</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11249,7 +11249,7 @@
         <v>130228071</v>
       </c>
       <c r="B104" t="n">
-        <v>91605</v>
+        <v>91692</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11346,7 +11346,7 @@
         <v>130227624</v>
       </c>
       <c r="B105" t="n">
-        <v>57741</v>
+        <v>57826</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11453,7 +11453,7 @@
         <v>130232597</v>
       </c>
       <c r="B106" t="n">
-        <v>57741</v>
+        <v>57826</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11560,7 +11560,7 @@
         <v>130232341</v>
       </c>
       <c r="B107" t="n">
-        <v>56931</v>
+        <v>57016</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11662,7 +11662,7 @@
         <v>130227321</v>
       </c>
       <c r="B108" t="n">
-        <v>91641</v>
+        <v>91728</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11759,7 +11759,7 @@
         <v>130229089</v>
       </c>
       <c r="B109" t="n">
-        <v>80200</v>
+        <v>80285</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11856,7 +11856,7 @@
         <v>130228880</v>
       </c>
       <c r="B110" t="n">
-        <v>91641</v>
+        <v>91728</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11953,7 +11953,7 @@
         <v>130227562</v>
       </c>
       <c r="B111" t="n">
-        <v>57741</v>
+        <v>57826</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>

--- a/artfynd/A 3110-2025 artfynd.xlsx
+++ b/artfynd/A 3110-2025 artfynd.xlsx
@@ -6097,10 +6097,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>130154406</v>
+        <v>130153953</v>
       </c>
       <c r="B54" t="n">
-        <v>79180</v>
+        <v>80285</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6108,21 +6108,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6132,10 +6132,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>541569</v>
+        <v>541656</v>
       </c>
       <c r="R54" t="n">
-        <v>7063377</v>
+        <v>7063312</v>
       </c>
       <c r="S54" t="n">
         <v>15</v>
@@ -6165,9 +6165,19 @@
           <t>2025-12-16</t>
         </is>
       </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>14:16</t>
+        </is>
+      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-12-16</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6182,22 +6192,22 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>130152994</v>
+        <v>130153802</v>
       </c>
       <c r="B55" t="n">
-        <v>79180</v>
+        <v>80285</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6205,39 +6215,34 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="K55" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>541785</v>
+        <v>541701</v>
       </c>
       <c r="R55" t="n">
-        <v>7063407</v>
+        <v>7063258</v>
       </c>
       <c r="S55" t="n">
         <v>15</v>
@@ -6296,10 +6301,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>130153953</v>
+        <v>130152471</v>
       </c>
       <c r="B56" t="n">
-        <v>80285</v>
+        <v>91728</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6307,21 +6312,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6331,13 +6336,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>541656</v>
+        <v>542048</v>
       </c>
       <c r="R56" t="n">
-        <v>7063312</v>
+        <v>7063680</v>
       </c>
       <c r="S56" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6366,7 +6371,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6376,7 +6381,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6403,10 +6408,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>130153802</v>
+        <v>130154406</v>
       </c>
       <c r="B57" t="n">
-        <v>80285</v>
+        <v>79180</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6414,21 +6419,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6438,10 +6443,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>541701</v>
+        <v>541569</v>
       </c>
       <c r="R57" t="n">
-        <v>7063258</v>
+        <v>7063377</v>
       </c>
       <c r="S57" t="n">
         <v>15</v>
@@ -6500,10 +6505,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>130152471</v>
+        <v>130152994</v>
       </c>
       <c r="B58" t="n">
-        <v>91728</v>
+        <v>79180</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6511,37 +6516,42 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>542048</v>
+        <v>541785</v>
       </c>
       <c r="R58" t="n">
-        <v>7063680</v>
+        <v>7063407</v>
       </c>
       <c r="S58" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6568,19 +6578,9 @@
           <t>2025-12-16</t>
         </is>
       </c>
-      <c r="Z58" t="inlineStr">
-        <is>
-          <t>12:48</t>
-        </is>
-      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-12-16</t>
-        </is>
-      </c>
-      <c r="AB58" t="inlineStr">
-        <is>
-          <t>12:48</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6595,12 +6595,12 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
@@ -11557,50 +11557,45 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>130232341</v>
+        <v>130227321</v>
       </c>
       <c r="B107" t="n">
-        <v>57016</v>
+        <v>91728</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>100138</v>
+        <v>1202</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
-      <c r="M107" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P107" t="inlineStr">
         <is>
-          <t>Stamåsen, Stamåsen, Ång</t>
+          <t>Lill-Åsberget, Lill-Åsberget, Ång</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>542026</v>
+        <v>542243</v>
       </c>
       <c r="R107" t="n">
-        <v>7063537</v>
+        <v>7063987</v>
       </c>
       <c r="S107" t="n">
         <v>15</v>
@@ -11659,45 +11654,50 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>130227321</v>
+        <v>130232341</v>
       </c>
       <c r="B108" t="n">
-        <v>91728</v>
+        <v>57016</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>1202</v>
+        <v>100138</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P108" t="inlineStr">
         <is>
-          <t>Lill-Åsberget, Lill-Åsberget, Ång</t>
+          <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>542243</v>
+        <v>542026</v>
       </c>
       <c r="R108" t="n">
-        <v>7063987</v>
+        <v>7063537</v>
       </c>
       <c r="S108" t="n">
         <v>15</v>

--- a/artfynd/A 3110-2025 artfynd.xlsx
+++ b/artfynd/A 3110-2025 artfynd.xlsx
@@ -6097,10 +6097,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>130153953</v>
+        <v>130154406</v>
       </c>
       <c r="B54" t="n">
-        <v>80285</v>
+        <v>79180</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6108,21 +6108,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6132,10 +6132,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>541656</v>
+        <v>541569</v>
       </c>
       <c r="R54" t="n">
-        <v>7063312</v>
+        <v>7063377</v>
       </c>
       <c r="S54" t="n">
         <v>15</v>
@@ -6165,19 +6165,9 @@
           <t>2025-12-16</t>
         </is>
       </c>
-      <c r="Z54" t="inlineStr">
-        <is>
-          <t>14:16</t>
-        </is>
-      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-12-16</t>
-        </is>
-      </c>
-      <c r="AB54" t="inlineStr">
-        <is>
-          <t>14:16</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6192,22 +6182,22 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>130153802</v>
+        <v>130152994</v>
       </c>
       <c r="B55" t="n">
-        <v>80285</v>
+        <v>79180</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6215,34 +6205,39 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>541701</v>
+        <v>541785</v>
       </c>
       <c r="R55" t="n">
-        <v>7063258</v>
+        <v>7063407</v>
       </c>
       <c r="S55" t="n">
         <v>15</v>
@@ -6301,10 +6296,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>130152471</v>
+        <v>130153953</v>
       </c>
       <c r="B56" t="n">
-        <v>91728</v>
+        <v>80285</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6312,21 +6307,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6336,13 +6331,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>542048</v>
+        <v>541656</v>
       </c>
       <c r="R56" t="n">
-        <v>7063680</v>
+        <v>7063312</v>
       </c>
       <c r="S56" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6371,7 +6366,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6381,7 +6376,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6408,10 +6403,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>130154406</v>
+        <v>130153802</v>
       </c>
       <c r="B57" t="n">
-        <v>79180</v>
+        <v>80285</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6419,21 +6414,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6443,10 +6438,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>541569</v>
+        <v>541701</v>
       </c>
       <c r="R57" t="n">
-        <v>7063377</v>
+        <v>7063258</v>
       </c>
       <c r="S57" t="n">
         <v>15</v>
@@ -6505,10 +6500,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>130152994</v>
+        <v>130152471</v>
       </c>
       <c r="B58" t="n">
-        <v>79180</v>
+        <v>91728</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6516,42 +6511,37 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="K58" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>541785</v>
+        <v>542048</v>
       </c>
       <c r="R58" t="n">
-        <v>7063407</v>
+        <v>7063680</v>
       </c>
       <c r="S58" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6578,9 +6568,19 @@
           <t>2025-12-16</t>
         </is>
       </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>12:48</t>
+        </is>
+      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-12-16</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6595,12 +6595,12 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
@@ -7005,10 +7005,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>130152102</v>
+        <v>130152010</v>
       </c>
       <c r="B63" t="n">
-        <v>79180</v>
+        <v>80285</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7016,21 +7016,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7040,10 +7040,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>542330</v>
+        <v>542347</v>
       </c>
       <c r="R63" t="n">
-        <v>7063952</v>
+        <v>7064044</v>
       </c>
       <c r="S63" t="n">
         <v>15</v>
@@ -7102,10 +7102,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>130152010</v>
+        <v>130152528</v>
       </c>
       <c r="B64" t="n">
-        <v>80285</v>
+        <v>57823</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7113,34 +7113,39 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Lill-Åsberget, Lill-Åsberget, Ång</t>
+          <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>542347</v>
+        <v>542003</v>
       </c>
       <c r="R64" t="n">
-        <v>7064044</v>
+        <v>7063641</v>
       </c>
       <c r="S64" t="n">
         <v>15</v>
@@ -7199,10 +7204,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>130152528</v>
+        <v>130152102</v>
       </c>
       <c r="B65" t="n">
-        <v>57823</v>
+        <v>79180</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7210,39 +7215,34 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Stamåsen, Stamåsen, Ång</t>
+          <t>Lill-Åsberget, Lill-Åsberget, Ång</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>542003</v>
+        <v>542330</v>
       </c>
       <c r="R65" t="n">
-        <v>7063641</v>
+        <v>7063952</v>
       </c>
       <c r="S65" t="n">
         <v>15</v>
@@ -8020,10 +8020,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>130153766</v>
+        <v>130153730</v>
       </c>
       <c r="B73" t="n">
-        <v>57826</v>
+        <v>79180</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8031,42 +8031,37 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
-      <c r="M73" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P73" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>541750</v>
+        <v>541768</v>
       </c>
       <c r="R73" t="n">
-        <v>7063250</v>
+        <v>7063269</v>
       </c>
       <c r="S73" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8095,7 +8090,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8105,12 +8100,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>14:00</t>
-        </is>
-      </c>
-      <c r="AC73" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8239,10 +8229,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>130153730</v>
+        <v>130153766</v>
       </c>
       <c r="B75" t="n">
-        <v>79180</v>
+        <v>57826</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8250,37 +8240,42 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P75" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>541768</v>
+        <v>541750</v>
       </c>
       <c r="R75" t="n">
-        <v>7063269</v>
+        <v>7063250</v>
       </c>
       <c r="S75" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8309,7 +8304,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8319,7 +8314,12 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -11246,45 +11246,50 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>130228071</v>
+        <v>130227624</v>
       </c>
       <c r="B104" t="n">
-        <v>91692</v>
+        <v>57826</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P104" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>541940</v>
+        <v>542070</v>
       </c>
       <c r="R104" t="n">
-        <v>7063661</v>
+        <v>7063767</v>
       </c>
       <c r="S104" t="n">
         <v>15</v>
@@ -11317,6 +11322,11 @@
       <c r="AA104" t="inlineStr">
         <is>
           <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AC104" t="inlineStr">
+        <is>
+          <t>Äldre ringhack, gran</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11343,50 +11353,45 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>130227624</v>
+        <v>130228071</v>
       </c>
       <c r="B105" t="n">
-        <v>57826</v>
+        <v>91692</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
-      <c r="M105" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P105" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>542070</v>
+        <v>541940</v>
       </c>
       <c r="R105" t="n">
-        <v>7063767</v>
+        <v>7063661</v>
       </c>
       <c r="S105" t="n">
         <v>15</v>
@@ -11419,11 +11424,6 @@
       <c r="AA105" t="inlineStr">
         <is>
           <t>2025-12-20</t>
-        </is>
-      </c>
-      <c r="AC105" t="inlineStr">
-        <is>
-          <t>Äldre ringhack, gran</t>
         </is>
       </c>
       <c r="AD105" t="b">

--- a/artfynd/A 3110-2025 artfynd.xlsx
+++ b/artfynd/A 3110-2025 artfynd.xlsx
@@ -6097,10 +6097,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>130154406</v>
+        <v>130153953</v>
       </c>
       <c r="B54" t="n">
-        <v>79180</v>
+        <v>80285</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6108,21 +6108,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6132,10 +6132,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>541569</v>
+        <v>541656</v>
       </c>
       <c r="R54" t="n">
-        <v>7063377</v>
+        <v>7063312</v>
       </c>
       <c r="S54" t="n">
         <v>15</v>
@@ -6165,9 +6165,19 @@
           <t>2025-12-16</t>
         </is>
       </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>14:16</t>
+        </is>
+      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-12-16</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6182,22 +6192,22 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>130152994</v>
+        <v>130153802</v>
       </c>
       <c r="B55" t="n">
-        <v>79180</v>
+        <v>80285</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6205,39 +6215,34 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="K55" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>541785</v>
+        <v>541701</v>
       </c>
       <c r="R55" t="n">
-        <v>7063407</v>
+        <v>7063258</v>
       </c>
       <c r="S55" t="n">
         <v>15</v>
@@ -6296,10 +6301,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>130153953</v>
+        <v>130152471</v>
       </c>
       <c r="B56" t="n">
-        <v>80285</v>
+        <v>91728</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6307,21 +6312,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6331,13 +6336,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>541656</v>
+        <v>542048</v>
       </c>
       <c r="R56" t="n">
-        <v>7063312</v>
+        <v>7063680</v>
       </c>
       <c r="S56" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6366,7 +6371,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6376,7 +6381,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6403,10 +6408,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>130153802</v>
+        <v>130154406</v>
       </c>
       <c r="B57" t="n">
-        <v>80285</v>
+        <v>79180</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6414,21 +6419,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6438,10 +6443,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>541701</v>
+        <v>541569</v>
       </c>
       <c r="R57" t="n">
-        <v>7063258</v>
+        <v>7063377</v>
       </c>
       <c r="S57" t="n">
         <v>15</v>
@@ -6500,10 +6505,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>130152471</v>
+        <v>130152994</v>
       </c>
       <c r="B58" t="n">
-        <v>91728</v>
+        <v>79180</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6511,37 +6516,42 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>542048</v>
+        <v>541785</v>
       </c>
       <c r="R58" t="n">
-        <v>7063680</v>
+        <v>7063407</v>
       </c>
       <c r="S58" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6568,19 +6578,9 @@
           <t>2025-12-16</t>
         </is>
       </c>
-      <c r="Z58" t="inlineStr">
-        <is>
-          <t>12:48</t>
-        </is>
-      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-12-16</t>
-        </is>
-      </c>
-      <c r="AB58" t="inlineStr">
-        <is>
-          <t>12:48</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6595,12 +6595,12 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
@@ -7005,10 +7005,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>130152010</v>
+        <v>130152102</v>
       </c>
       <c r="B63" t="n">
-        <v>80285</v>
+        <v>79180</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7016,21 +7016,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7040,10 +7040,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>542347</v>
+        <v>542330</v>
       </c>
       <c r="R63" t="n">
-        <v>7064044</v>
+        <v>7063952</v>
       </c>
       <c r="S63" t="n">
         <v>15</v>
@@ -7102,10 +7102,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>130152528</v>
+        <v>130152010</v>
       </c>
       <c r="B64" t="n">
-        <v>57823</v>
+        <v>80285</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7113,39 +7113,34 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Stamåsen, Stamåsen, Ång</t>
+          <t>Lill-Åsberget, Lill-Åsberget, Ång</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>542003</v>
+        <v>542347</v>
       </c>
       <c r="R64" t="n">
-        <v>7063641</v>
+        <v>7064044</v>
       </c>
       <c r="S64" t="n">
         <v>15</v>
@@ -7204,10 +7199,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>130152102</v>
+        <v>130152528</v>
       </c>
       <c r="B65" t="n">
-        <v>79180</v>
+        <v>57823</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7215,34 +7210,39 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Lill-Åsberget, Lill-Åsberget, Ång</t>
+          <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>542330</v>
+        <v>542003</v>
       </c>
       <c r="R65" t="n">
-        <v>7063952</v>
+        <v>7063641</v>
       </c>
       <c r="S65" t="n">
         <v>15</v>
@@ -8020,10 +8020,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>130153730</v>
+        <v>130153766</v>
       </c>
       <c r="B73" t="n">
-        <v>79180</v>
+        <v>57826</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8031,37 +8031,42 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P73" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>541768</v>
+        <v>541750</v>
       </c>
       <c r="R73" t="n">
-        <v>7063269</v>
+        <v>7063250</v>
       </c>
       <c r="S73" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8090,7 +8095,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8100,7 +8105,12 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8229,10 +8239,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>130153766</v>
+        <v>130153730</v>
       </c>
       <c r="B75" t="n">
-        <v>57826</v>
+        <v>79180</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8240,42 +8250,37 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
-      <c r="M75" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P75" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>541750</v>
+        <v>541768</v>
       </c>
       <c r="R75" t="n">
-        <v>7063250</v>
+        <v>7063269</v>
       </c>
       <c r="S75" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8304,7 +8309,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8314,12 +8319,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>14:00</t>
-        </is>
-      </c>
-      <c r="AC75" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9303,32 +9303,32 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>130153013</v>
+        <v>130153121</v>
       </c>
       <c r="B85" t="n">
-        <v>91692</v>
+        <v>79180</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9338,10 +9338,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>541792</v>
+        <v>541827</v>
       </c>
       <c r="R85" t="n">
-        <v>7063398</v>
+        <v>7063362</v>
       </c>
       <c r="S85" t="n">
         <v>15</v>
@@ -9371,9 +9371,19 @@
           <t>2025-12-16</t>
         </is>
       </c>
+      <c r="Z85" t="inlineStr">
+        <is>
+          <t>13:34</t>
+        </is>
+      </c>
       <c r="AA85" t="inlineStr">
         <is>
           <t>2025-12-16</t>
+        </is>
+      </c>
+      <c r="AB85" t="inlineStr">
+        <is>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9388,19 +9398,19 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>130153121</v>
+        <v>130153494</v>
       </c>
       <c r="B86" t="n">
         <v>79180</v>
@@ -9435,13 +9445,13 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>541827</v>
+        <v>541836</v>
       </c>
       <c r="R86" t="n">
-        <v>7063362</v>
+        <v>7063316</v>
       </c>
       <c r="S86" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -9470,7 +9480,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -9480,7 +9490,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9507,32 +9517,32 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>130153494</v>
+        <v>130153013</v>
       </c>
       <c r="B87" t="n">
-        <v>79180</v>
+        <v>91692</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9542,13 +9552,13 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>541836</v>
+        <v>541792</v>
       </c>
       <c r="R87" t="n">
-        <v>7063316</v>
+        <v>7063398</v>
       </c>
       <c r="S87" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -9575,19 +9585,9 @@
           <t>2025-12-16</t>
         </is>
       </c>
-      <c r="Z87" t="inlineStr">
-        <is>
-          <t>13:48</t>
-        </is>
-      </c>
       <c r="AA87" t="inlineStr">
         <is>
           <t>2025-12-16</t>
-        </is>
-      </c>
-      <c r="AB87" t="inlineStr">
-        <is>
-          <t>13:48</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9602,12 +9602,12 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
@@ -11246,50 +11246,45 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>130227624</v>
+        <v>130228071</v>
       </c>
       <c r="B104" t="n">
-        <v>57826</v>
+        <v>91692</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
-      <c r="M104" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P104" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>542070</v>
+        <v>541940</v>
       </c>
       <c r="R104" t="n">
-        <v>7063767</v>
+        <v>7063661</v>
       </c>
       <c r="S104" t="n">
         <v>15</v>
@@ -11322,11 +11317,6 @@
       <c r="AA104" t="inlineStr">
         <is>
           <t>2025-12-20</t>
-        </is>
-      </c>
-      <c r="AC104" t="inlineStr">
-        <is>
-          <t>Äldre ringhack, gran</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11353,45 +11343,50 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>130228071</v>
+        <v>130227624</v>
       </c>
       <c r="B105" t="n">
-        <v>91692</v>
+        <v>57826</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P105" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>541940</v>
+        <v>542070</v>
       </c>
       <c r="R105" t="n">
-        <v>7063661</v>
+        <v>7063767</v>
       </c>
       <c r="S105" t="n">
         <v>15</v>
@@ -11424,6 +11419,11 @@
       <c r="AA105" t="inlineStr">
         <is>
           <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AC105" t="inlineStr">
+        <is>
+          <t>Äldre ringhack, gran</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11557,45 +11557,50 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>130227321</v>
+        <v>130232341</v>
       </c>
       <c r="B107" t="n">
-        <v>91728</v>
+        <v>57016</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>1202</v>
+        <v>100138</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P107" t="inlineStr">
         <is>
-          <t>Lill-Åsberget, Lill-Åsberget, Ång</t>
+          <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>542243</v>
+        <v>542026</v>
       </c>
       <c r="R107" t="n">
-        <v>7063987</v>
+        <v>7063537</v>
       </c>
       <c r="S107" t="n">
         <v>15</v>
@@ -11654,50 +11659,45 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>130232341</v>
+        <v>130227321</v>
       </c>
       <c r="B108" t="n">
-        <v>57016</v>
+        <v>91728</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>100138</v>
+        <v>1202</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
-      <c r="M108" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P108" t="inlineStr">
         <is>
-          <t>Stamåsen, Stamåsen, Ång</t>
+          <t>Lill-Åsberget, Lill-Åsberget, Ång</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>542026</v>
+        <v>542243</v>
       </c>
       <c r="R108" t="n">
-        <v>7063537</v>
+        <v>7063987</v>
       </c>
       <c r="S108" t="n">
         <v>15</v>

--- a/artfynd/A 3110-2025 artfynd.xlsx
+++ b/artfynd/A 3110-2025 artfynd.xlsx
@@ -5388,32 +5388,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>130154078</v>
+        <v>130154007</v>
       </c>
       <c r="B47" t="n">
-        <v>79180</v>
+        <v>80317</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5423,10 +5423,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>541577</v>
+        <v>541615</v>
       </c>
       <c r="R47" t="n">
-        <v>7063340</v>
+        <v>7063313</v>
       </c>
       <c r="S47" t="n">
         <v>15</v>
@@ -5456,19 +5456,9 @@
           <t>2025-12-16</t>
         </is>
       </c>
-      <c r="Z47" t="inlineStr">
-        <is>
-          <t>14:28</t>
-        </is>
-      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-12-16</t>
-        </is>
-      </c>
-      <c r="AB47" t="inlineStr">
-        <is>
-          <t>14:28</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5483,22 +5473,22 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>130153573</v>
+        <v>130154078</v>
       </c>
       <c r="B48" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5530,10 +5520,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>541822</v>
+        <v>541577</v>
       </c>
       <c r="R48" t="n">
-        <v>7063308</v>
+        <v>7063340</v>
       </c>
       <c r="S48" t="n">
         <v>15</v>
@@ -5563,9 +5553,19 @@
           <t>2025-12-16</t>
         </is>
       </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>14:28</t>
+        </is>
+      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-12-16</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5580,44 +5580,44 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>130154007</v>
+        <v>130153573</v>
       </c>
       <c r="B49" t="n">
-        <v>80314</v>
+        <v>79183</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5627,10 +5627,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>541615</v>
+        <v>541822</v>
       </c>
       <c r="R49" t="n">
-        <v>7063313</v>
+        <v>7063308</v>
       </c>
       <c r="S49" t="n">
         <v>15</v>
@@ -5692,7 +5692,7 @@
         <v>130153774</v>
       </c>
       <c r="B50" t="n">
-        <v>80285</v>
+        <v>80288</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5789,7 +5789,7 @@
         <v>130153973</v>
       </c>
       <c r="B51" t="n">
-        <v>80285</v>
+        <v>80288</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5886,7 +5886,7 @@
         <v>130152521</v>
       </c>
       <c r="B52" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5993,7 +5993,7 @@
         <v>130152070</v>
       </c>
       <c r="B53" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6097,10 +6097,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>130153953</v>
+        <v>130152471</v>
       </c>
       <c r="B54" t="n">
-        <v>80285</v>
+        <v>91731</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6108,21 +6108,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6132,13 +6132,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>541656</v>
+        <v>542048</v>
       </c>
       <c r="R54" t="n">
-        <v>7063312</v>
+        <v>7063680</v>
       </c>
       <c r="S54" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6167,7 +6167,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6177,7 +6177,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6204,10 +6204,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>130153802</v>
+        <v>130154406</v>
       </c>
       <c r="B55" t="n">
-        <v>80285</v>
+        <v>79183</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6215,21 +6215,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6239,10 +6239,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>541701</v>
+        <v>541569</v>
       </c>
       <c r="R55" t="n">
-        <v>7063258</v>
+        <v>7063377</v>
       </c>
       <c r="S55" t="n">
         <v>15</v>
@@ -6301,10 +6301,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>130152471</v>
+        <v>130152994</v>
       </c>
       <c r="B56" t="n">
-        <v>91728</v>
+        <v>79183</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6312,37 +6312,42 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>542048</v>
+        <v>541785</v>
       </c>
       <c r="R56" t="n">
-        <v>7063680</v>
+        <v>7063407</v>
       </c>
       <c r="S56" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6369,19 +6374,9 @@
           <t>2025-12-16</t>
         </is>
       </c>
-      <c r="Z56" t="inlineStr">
-        <is>
-          <t>12:48</t>
-        </is>
-      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>2025-12-16</t>
-        </is>
-      </c>
-      <c r="AB56" t="inlineStr">
-        <is>
-          <t>12:48</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6396,22 +6391,22 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>130154406</v>
+        <v>130153953</v>
       </c>
       <c r="B57" t="n">
-        <v>79180</v>
+        <v>80288</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6419,21 +6414,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6443,10 +6438,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>541569</v>
+        <v>541656</v>
       </c>
       <c r="R57" t="n">
-        <v>7063377</v>
+        <v>7063312</v>
       </c>
       <c r="S57" t="n">
         <v>15</v>
@@ -6476,9 +6471,19 @@
           <t>2025-12-16</t>
         </is>
       </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>14:16</t>
+        </is>
+      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>2025-12-16</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6493,22 +6498,22 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>130152994</v>
+        <v>130153802</v>
       </c>
       <c r="B58" t="n">
-        <v>79180</v>
+        <v>80288</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6516,39 +6521,34 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="K58" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>541785</v>
+        <v>541701</v>
       </c>
       <c r="R58" t="n">
-        <v>7063407</v>
+        <v>7063258</v>
       </c>
       <c r="S58" t="n">
         <v>15</v>
@@ -6610,7 +6610,7 @@
         <v>130153842</v>
       </c>
       <c r="B59" t="n">
-        <v>91749</v>
+        <v>91752</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6707,7 +6707,7 @@
         <v>130152977</v>
       </c>
       <c r="B60" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6814,7 +6814,7 @@
         <v>130152623</v>
       </c>
       <c r="B61" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6911,7 +6911,7 @@
         <v>130152037</v>
       </c>
       <c r="B62" t="n">
-        <v>92026</v>
+        <v>92029</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7005,10 +7005,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>130152102</v>
+        <v>130152010</v>
       </c>
       <c r="B63" t="n">
-        <v>79180</v>
+        <v>80288</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7016,21 +7016,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7040,10 +7040,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>542330</v>
+        <v>542347</v>
       </c>
       <c r="R63" t="n">
-        <v>7063952</v>
+        <v>7064044</v>
       </c>
       <c r="S63" t="n">
         <v>15</v>
@@ -7102,10 +7102,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>130152010</v>
+        <v>130152102</v>
       </c>
       <c r="B64" t="n">
-        <v>80285</v>
+        <v>79183</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7113,21 +7113,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7137,10 +7137,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>542347</v>
+        <v>542330</v>
       </c>
       <c r="R64" t="n">
-        <v>7064044</v>
+        <v>7063952</v>
       </c>
       <c r="S64" t="n">
         <v>15</v>
@@ -7301,10 +7301,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>130152789</v>
+        <v>130154006</v>
       </c>
       <c r="B66" t="n">
-        <v>83158</v>
+        <v>80288</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7312,21 +7312,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6440</v>
+        <v>6458</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7336,10 +7336,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>541769</v>
+        <v>541614</v>
       </c>
       <c r="R66" t="n">
-        <v>7063539</v>
+        <v>7063281</v>
       </c>
       <c r="S66" t="n">
         <v>15</v>
@@ -7398,10 +7398,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>130152602</v>
+        <v>130152774</v>
       </c>
       <c r="B67" t="n">
-        <v>79180</v>
+        <v>57826</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7409,34 +7409,39 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P67" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>541973</v>
+        <v>541786</v>
       </c>
       <c r="R67" t="n">
-        <v>7063647</v>
+        <v>7063538</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7468,7 +7473,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7478,7 +7483,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>12:57</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7505,10 +7510,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>130153922</v>
+        <v>130152789</v>
       </c>
       <c r="B68" t="n">
-        <v>79180</v>
+        <v>83161</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7516,21 +7521,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7540,10 +7545,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>541656</v>
+        <v>541769</v>
       </c>
       <c r="R68" t="n">
-        <v>7063282</v>
+        <v>7063539</v>
       </c>
       <c r="S68" t="n">
         <v>15</v>
@@ -7573,19 +7578,9 @@
           <t>2025-12-16</t>
         </is>
       </c>
-      <c r="Z68" t="inlineStr">
-        <is>
-          <t>14:13</t>
-        </is>
-      </c>
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-12-16</t>
-        </is>
-      </c>
-      <c r="AB68" t="inlineStr">
-        <is>
-          <t>14:13</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7600,22 +7595,22 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>130153060</v>
+        <v>130152602</v>
       </c>
       <c r="B69" t="n">
-        <v>57823</v>
+        <v>79183</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7623,42 +7618,37 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>541839</v>
+        <v>541973</v>
       </c>
       <c r="R69" t="n">
-        <v>7063371</v>
+        <v>7063647</v>
       </c>
       <c r="S69" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -7685,9 +7675,19 @@
           <t>2025-12-16</t>
         </is>
       </c>
+      <c r="Z69" t="inlineStr">
+        <is>
+          <t>12:57</t>
+        </is>
+      </c>
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-12-16</t>
+        </is>
+      </c>
+      <c r="AB69" t="inlineStr">
+        <is>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7702,22 +7702,22 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>130154006</v>
+        <v>130153922</v>
       </c>
       <c r="B70" t="n">
-        <v>80285</v>
+        <v>79183</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7725,21 +7725,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7749,10 +7749,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>541614</v>
+        <v>541656</v>
       </c>
       <c r="R70" t="n">
-        <v>7063281</v>
+        <v>7063282</v>
       </c>
       <c r="S70" t="n">
         <v>15</v>
@@ -7782,9 +7782,19 @@
           <t>2025-12-16</t>
         </is>
       </c>
+      <c r="Z70" t="inlineStr">
+        <is>
+          <t>14:13</t>
+        </is>
+      </c>
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-12-16</t>
+        </is>
+      </c>
+      <c r="AB70" t="inlineStr">
+        <is>
+          <t>14:13</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7799,22 +7809,22 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>130152774</v>
+        <v>130153060</v>
       </c>
       <c r="B71" t="n">
-        <v>57826</v>
+        <v>57823</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7822,16 +7832,16 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -7851,13 +7861,13 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>541786</v>
+        <v>541839</v>
       </c>
       <c r="R71" t="n">
-        <v>7063538</v>
+        <v>7063371</v>
       </c>
       <c r="S71" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -7884,19 +7894,9 @@
           <t>2025-12-16</t>
         </is>
       </c>
-      <c r="Z71" t="inlineStr">
-        <is>
-          <t>13:08</t>
-        </is>
-      </c>
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-12-16</t>
-        </is>
-      </c>
-      <c r="AB71" t="inlineStr">
-        <is>
-          <t>13:08</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7911,12 +7911,12 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
@@ -7926,7 +7926,7 @@
         <v>130154548</v>
       </c>
       <c r="B72" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8137,10 +8137,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>130152352</v>
+        <v>130153730</v>
       </c>
       <c r="B74" t="n">
-        <v>80285</v>
+        <v>79183</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8148,21 +8148,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8172,13 +8172,13 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>542077</v>
+        <v>541768</v>
       </c>
       <c r="R74" t="n">
-        <v>7063744</v>
+        <v>7063269</v>
       </c>
       <c r="S74" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8205,14 +8205,19 @@
           <t>2025-12-16</t>
         </is>
       </c>
+      <c r="Z74" t="inlineStr">
+        <is>
+          <t>13:58</t>
+        </is>
+      </c>
       <c r="AA74" t="inlineStr">
         <is>
           <t>2025-12-16</t>
         </is>
       </c>
-      <c r="AC74" t="inlineStr">
-        <is>
-          <t>På död björk</t>
+      <c r="AB74" t="inlineStr">
+        <is>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8227,22 +8232,22 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>130153730</v>
+        <v>130152352</v>
       </c>
       <c r="B75" t="n">
-        <v>79180</v>
+        <v>80288</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8250,21 +8255,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8274,13 +8279,13 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>541768</v>
+        <v>542077</v>
       </c>
       <c r="R75" t="n">
-        <v>7063269</v>
+        <v>7063744</v>
       </c>
       <c r="S75" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8307,19 +8312,14 @@
           <t>2025-12-16</t>
         </is>
       </c>
-      <c r="Z75" t="inlineStr">
-        <is>
-          <t>13:58</t>
-        </is>
-      </c>
       <c r="AA75" t="inlineStr">
         <is>
           <t>2025-12-16</t>
         </is>
       </c>
-      <c r="AB75" t="inlineStr">
-        <is>
-          <t>13:58</t>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>På död björk</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8334,12 +8334,12 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
@@ -8349,7 +8349,7 @@
         <v>130154401</v>
       </c>
       <c r="B76" t="n">
-        <v>98920</v>
+        <v>98923</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8460,7 +8460,7 @@
         <v>130153074</v>
       </c>
       <c r="B77" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8567,7 +8567,7 @@
         <v>130153365</v>
       </c>
       <c r="B78" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8788,10 +8788,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>130151970</v>
+        <v>130154569</v>
       </c>
       <c r="B80" t="n">
-        <v>79180</v>
+        <v>57826</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8799,34 +8799,39 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Lill-Åsberget, Lill-Åsberget, Ång</t>
+          <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>542334</v>
+        <v>541683</v>
       </c>
       <c r="R80" t="n">
-        <v>7064066</v>
+        <v>7063551</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8858,7 +8863,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>14:57</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -8868,7 +8873,12 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>14:57</t>
+        </is>
+      </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -8895,10 +8905,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>130154569</v>
+        <v>130151970</v>
       </c>
       <c r="B81" t="n">
-        <v>57826</v>
+        <v>79183</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8906,39 +8916,34 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
-      <c r="M81" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Stamåsen, Stamåsen, Ång</t>
+          <t>Lill-Åsberget, Lill-Åsberget, Ång</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>541683</v>
+        <v>542334</v>
       </c>
       <c r="R81" t="n">
-        <v>7063551</v>
+        <v>7064066</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8970,7 +8975,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>14:57</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -8980,12 +8985,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>14:57</t>
-        </is>
-      </c>
-      <c r="AC81" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9015,7 +9015,7 @@
         <v>130154023</v>
       </c>
       <c r="B82" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9112,7 +9112,7 @@
         <v>130154014</v>
       </c>
       <c r="B83" t="n">
-        <v>80320</v>
+        <v>80323</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9209,7 +9209,7 @@
         <v>130152372</v>
       </c>
       <c r="B84" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9303,32 +9303,32 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>130153121</v>
+        <v>130153013</v>
       </c>
       <c r="B85" t="n">
-        <v>79180</v>
+        <v>91695</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9338,10 +9338,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>541827</v>
+        <v>541792</v>
       </c>
       <c r="R85" t="n">
-        <v>7063362</v>
+        <v>7063398</v>
       </c>
       <c r="S85" t="n">
         <v>15</v>
@@ -9371,19 +9371,9 @@
           <t>2025-12-16</t>
         </is>
       </c>
-      <c r="Z85" t="inlineStr">
-        <is>
-          <t>13:34</t>
-        </is>
-      </c>
       <c r="AA85" t="inlineStr">
         <is>
           <t>2025-12-16</t>
-        </is>
-      </c>
-      <c r="AB85" t="inlineStr">
-        <is>
-          <t>13:34</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9398,22 +9388,22 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>130153494</v>
+        <v>130153121</v>
       </c>
       <c r="B86" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9445,13 +9435,13 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>541836</v>
+        <v>541827</v>
       </c>
       <c r="R86" t="n">
-        <v>7063316</v>
+        <v>7063362</v>
       </c>
       <c r="S86" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -9480,7 +9470,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -9490,7 +9480,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9517,32 +9507,32 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>130153013</v>
+        <v>130153494</v>
       </c>
       <c r="B87" t="n">
-        <v>91692</v>
+        <v>79183</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9552,13 +9542,13 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>541792</v>
+        <v>541836</v>
       </c>
       <c r="R87" t="n">
-        <v>7063398</v>
+        <v>7063316</v>
       </c>
       <c r="S87" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -9585,9 +9575,19 @@
           <t>2025-12-16</t>
         </is>
       </c>
+      <c r="Z87" t="inlineStr">
+        <is>
+          <t>13:48</t>
+        </is>
+      </c>
       <c r="AA87" t="inlineStr">
         <is>
           <t>2025-12-16</t>
+        </is>
+      </c>
+      <c r="AB87" t="inlineStr">
+        <is>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9602,12 +9602,12 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
@@ -9734,7 +9734,7 @@
         <v>130152767</v>
       </c>
       <c r="B89" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9831,7 +9831,7 @@
         <v>130152347</v>
       </c>
       <c r="B90" t="n">
-        <v>80285</v>
+        <v>80288</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10162,7 +10162,7 @@
         <v>130228030</v>
       </c>
       <c r="B93" t="n">
-        <v>91941</v>
+        <v>91944</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10256,10 +10256,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>130227326</v>
+        <v>130228951</v>
       </c>
       <c r="B94" t="n">
-        <v>92026</v>
+        <v>80288</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10267,34 +10267,34 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Lill-Åsberget, Lill-Åsberget, Ång</t>
+          <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>542243</v>
+        <v>541618</v>
       </c>
       <c r="R94" t="n">
-        <v>7063987</v>
+        <v>7063274</v>
       </c>
       <c r="S94" t="n">
         <v>15</v>
@@ -10353,10 +10353,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>130228951</v>
+        <v>130227326</v>
       </c>
       <c r="B95" t="n">
-        <v>80285</v>
+        <v>92029</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10364,34 +10364,34 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Stamåsen, Stamåsen, Ång</t>
+          <t>Lill-Åsberget, Lill-Åsberget, Ång</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>541618</v>
+        <v>542243</v>
       </c>
       <c r="R95" t="n">
-        <v>7063274</v>
+        <v>7063987</v>
       </c>
       <c r="S95" t="n">
         <v>15</v>
@@ -10453,7 +10453,7 @@
         <v>130228013</v>
       </c>
       <c r="B96" t="n">
-        <v>92026</v>
+        <v>92029</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10550,7 +10550,7 @@
         <v>130228996</v>
       </c>
       <c r="B97" t="n">
-        <v>80285</v>
+        <v>80288</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10647,7 +10647,7 @@
         <v>130229019</v>
       </c>
       <c r="B98" t="n">
-        <v>80286</v>
+        <v>80289</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10744,7 +10744,7 @@
         <v>130229083</v>
       </c>
       <c r="B99" t="n">
-        <v>80286</v>
+        <v>80289</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10958,7 +10958,7 @@
         <v>130232684</v>
       </c>
       <c r="B101" t="n">
-        <v>80189</v>
+        <v>80192</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11055,7 +11055,7 @@
         <v>130228879</v>
       </c>
       <c r="B102" t="n">
-        <v>92181</v>
+        <v>92184</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11152,7 +11152,7 @@
         <v>130227381</v>
       </c>
       <c r="B103" t="n">
-        <v>80285</v>
+        <v>80288</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11249,7 +11249,7 @@
         <v>130228071</v>
       </c>
       <c r="B104" t="n">
-        <v>91692</v>
+        <v>91695</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11557,50 +11557,45 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>130232341</v>
+        <v>130227321</v>
       </c>
       <c r="B107" t="n">
-        <v>57016</v>
+        <v>91731</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>100138</v>
+        <v>1202</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
-      <c r="M107" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P107" t="inlineStr">
         <is>
-          <t>Stamåsen, Stamåsen, Ång</t>
+          <t>Lill-Åsberget, Lill-Åsberget, Ång</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>542026</v>
+        <v>542243</v>
       </c>
       <c r="R107" t="n">
-        <v>7063537</v>
+        <v>7063987</v>
       </c>
       <c r="S107" t="n">
         <v>15</v>
@@ -11659,45 +11654,50 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>130227321</v>
+        <v>130232341</v>
       </c>
       <c r="B108" t="n">
-        <v>91728</v>
+        <v>57016</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>1202</v>
+        <v>100138</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P108" t="inlineStr">
         <is>
-          <t>Lill-Åsberget, Lill-Åsberget, Ång</t>
+          <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>542243</v>
+        <v>542026</v>
       </c>
       <c r="R108" t="n">
-        <v>7063987</v>
+        <v>7063537</v>
       </c>
       <c r="S108" t="n">
         <v>15</v>
@@ -11759,7 +11759,7 @@
         <v>130229089</v>
       </c>
       <c r="B109" t="n">
-        <v>80285</v>
+        <v>80288</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11856,7 +11856,7 @@
         <v>130228880</v>
       </c>
       <c r="B110" t="n">
-        <v>91728</v>
+        <v>91731</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>

--- a/artfynd/A 3110-2025 artfynd.xlsx
+++ b/artfynd/A 3110-2025 artfynd.xlsx
@@ -5388,32 +5388,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>130154007</v>
+        <v>130154078</v>
       </c>
       <c r="B47" t="n">
-        <v>80317</v>
+        <v>79209</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5423,10 +5423,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>541615</v>
+        <v>541577</v>
       </c>
       <c r="R47" t="n">
-        <v>7063313</v>
+        <v>7063340</v>
       </c>
       <c r="S47" t="n">
         <v>15</v>
@@ -5456,9 +5456,19 @@
           <t>2025-12-16</t>
         </is>
       </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>14:28</t>
+        </is>
+      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-12-16</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5473,22 +5483,22 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>130154078</v>
+        <v>130153573</v>
       </c>
       <c r="B48" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5520,10 +5530,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>541577</v>
+        <v>541822</v>
       </c>
       <c r="R48" t="n">
-        <v>7063340</v>
+        <v>7063308</v>
       </c>
       <c r="S48" t="n">
         <v>15</v>
@@ -5553,19 +5563,9 @@
           <t>2025-12-16</t>
         </is>
       </c>
-      <c r="Z48" t="inlineStr">
-        <is>
-          <t>14:28</t>
-        </is>
-      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-12-16</t>
-        </is>
-      </c>
-      <c r="AB48" t="inlineStr">
-        <is>
-          <t>14:28</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5580,44 +5580,44 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>130153573</v>
+        <v>130154007</v>
       </c>
       <c r="B49" t="n">
-        <v>79183</v>
+        <v>80343</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5627,10 +5627,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>541822</v>
+        <v>541615</v>
       </c>
       <c r="R49" t="n">
-        <v>7063308</v>
+        <v>7063313</v>
       </c>
       <c r="S49" t="n">
         <v>15</v>
@@ -5692,7 +5692,7 @@
         <v>130153774</v>
       </c>
       <c r="B50" t="n">
-        <v>80288</v>
+        <v>80314</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5789,7 +5789,7 @@
         <v>130153973</v>
       </c>
       <c r="B51" t="n">
-        <v>80288</v>
+        <v>80314</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5883,10 +5883,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>130152521</v>
+        <v>130152070</v>
       </c>
       <c r="B52" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5914,14 +5914,14 @@
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Stamåsen, Stamåsen, Ång</t>
+          <t>Lill-Åsberget, Lill-Åsberget, Ång</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>541998</v>
+        <v>542344</v>
       </c>
       <c r="R52" t="n">
-        <v>7063666</v>
+        <v>7064036</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5953,7 +5953,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -5963,7 +5963,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>12:52</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5990,10 +5990,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>130152070</v>
+        <v>130152521</v>
       </c>
       <c r="B53" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6021,14 +6021,14 @@
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Lill-Åsberget, Lill-Åsberget, Ång</t>
+          <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>542344</v>
+        <v>541998</v>
       </c>
       <c r="R53" t="n">
-        <v>7064036</v>
+        <v>7063666</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6060,7 +6060,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6070,7 +6070,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:52</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6097,10 +6097,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>130152471</v>
+        <v>130152994</v>
       </c>
       <c r="B54" t="n">
-        <v>91731</v>
+        <v>79209</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6108,37 +6108,42 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>542048</v>
+        <v>541785</v>
       </c>
       <c r="R54" t="n">
-        <v>7063680</v>
+        <v>7063407</v>
       </c>
       <c r="S54" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6165,19 +6170,9 @@
           <t>2025-12-16</t>
         </is>
       </c>
-      <c r="Z54" t="inlineStr">
-        <is>
-          <t>12:48</t>
-        </is>
-      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>2025-12-16</t>
-        </is>
-      </c>
-      <c r="AB54" t="inlineStr">
-        <is>
-          <t>12:48</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6192,12 +6187,12 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
@@ -6207,7 +6202,7 @@
         <v>130154406</v>
       </c>
       <c r="B55" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6301,10 +6296,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>130152994</v>
+        <v>130153802</v>
       </c>
       <c r="B56" t="n">
-        <v>79183</v>
+        <v>80314</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6312,39 +6307,34 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="K56" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>541785</v>
+        <v>541701</v>
       </c>
       <c r="R56" t="n">
-        <v>7063407</v>
+        <v>7063258</v>
       </c>
       <c r="S56" t="n">
         <v>15</v>
@@ -6406,7 +6396,7 @@
         <v>130153953</v>
       </c>
       <c r="B57" t="n">
-        <v>80288</v>
+        <v>80314</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6510,10 +6500,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>130153802</v>
+        <v>130152471</v>
       </c>
       <c r="B58" t="n">
-        <v>80288</v>
+        <v>91757</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6521,21 +6511,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6545,13 +6535,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>541701</v>
+        <v>542048</v>
       </c>
       <c r="R58" t="n">
-        <v>7063258</v>
+        <v>7063680</v>
       </c>
       <c r="S58" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6578,9 +6568,19 @@
           <t>2025-12-16</t>
         </is>
       </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>12:48</t>
+        </is>
+      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>2025-12-16</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6595,12 +6595,12 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
@@ -6610,7 +6610,7 @@
         <v>130153842</v>
       </c>
       <c r="B59" t="n">
-        <v>91752</v>
+        <v>91778</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6704,10 +6704,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>130152977</v>
+        <v>130152623</v>
       </c>
       <c r="B60" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6739,13 +6739,13 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>541780</v>
+        <v>541908</v>
       </c>
       <c r="R60" t="n">
-        <v>7063439</v>
+        <v>7063597</v>
       </c>
       <c r="S60" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -6772,19 +6772,9 @@
           <t>2025-12-16</t>
         </is>
       </c>
-      <c r="Z60" t="inlineStr">
-        <is>
-          <t>13:18</t>
-        </is>
-      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-12-16</t>
-        </is>
-      </c>
-      <c r="AB60" t="inlineStr">
-        <is>
-          <t>13:18</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6799,22 +6789,22 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>130152623</v>
+        <v>130152977</v>
       </c>
       <c r="B61" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6846,13 +6836,13 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>541908</v>
+        <v>541780</v>
       </c>
       <c r="R61" t="n">
-        <v>7063597</v>
+        <v>7063439</v>
       </c>
       <c r="S61" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -6879,9 +6869,19 @@
           <t>2025-12-16</t>
         </is>
       </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>13:18</t>
+        </is>
+      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-12-16</t>
+        </is>
+      </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6896,12 +6896,12 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
@@ -6911,7 +6911,7 @@
         <v>130152037</v>
       </c>
       <c r="B62" t="n">
-        <v>92029</v>
+        <v>92055</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7008,7 +7008,7 @@
         <v>130152010</v>
       </c>
       <c r="B63" t="n">
-        <v>80288</v>
+        <v>80314</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7102,10 +7102,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>130152102</v>
+        <v>130152528</v>
       </c>
       <c r="B64" t="n">
-        <v>79183</v>
+        <v>57849</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7113,34 +7113,39 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Lill-Åsberget, Lill-Åsberget, Ång</t>
+          <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>542330</v>
+        <v>542003</v>
       </c>
       <c r="R64" t="n">
-        <v>7063952</v>
+        <v>7063641</v>
       </c>
       <c r="S64" t="n">
         <v>15</v>
@@ -7199,10 +7204,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>130152528</v>
+        <v>130152102</v>
       </c>
       <c r="B65" t="n">
-        <v>57823</v>
+        <v>79209</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7210,39 +7215,34 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Stamåsen, Stamåsen, Ång</t>
+          <t>Lill-Åsberget, Lill-Åsberget, Ång</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>542003</v>
+        <v>542330</v>
       </c>
       <c r="R65" t="n">
-        <v>7063641</v>
+        <v>7063952</v>
       </c>
       <c r="S65" t="n">
         <v>15</v>
@@ -7301,10 +7301,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>130154006</v>
+        <v>130152789</v>
       </c>
       <c r="B66" t="n">
-        <v>80288</v>
+        <v>83187</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7312,21 +7312,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6458</v>
+        <v>6440</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7336,10 +7336,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>541614</v>
+        <v>541769</v>
       </c>
       <c r="R66" t="n">
-        <v>7063281</v>
+        <v>7063539</v>
       </c>
       <c r="S66" t="n">
         <v>15</v>
@@ -7398,10 +7398,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>130152774</v>
+        <v>130154006</v>
       </c>
       <c r="B67" t="n">
-        <v>57826</v>
+        <v>80314</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7409,42 +7409,37 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P67" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>541786</v>
+        <v>541614</v>
       </c>
       <c r="R67" t="n">
-        <v>7063538</v>
+        <v>7063281</v>
       </c>
       <c r="S67" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7471,19 +7466,9 @@
           <t>2025-12-16</t>
         </is>
       </c>
-      <c r="Z67" t="inlineStr">
-        <is>
-          <t>13:08</t>
-        </is>
-      </c>
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-12-16</t>
-        </is>
-      </c>
-      <c r="AB67" t="inlineStr">
-        <is>
-          <t>13:08</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7498,22 +7483,22 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>130152789</v>
+        <v>130152774</v>
       </c>
       <c r="B68" t="n">
-        <v>83161</v>
+        <v>57852</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7521,37 +7506,42 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6440</v>
+        <v>100109</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>541769</v>
+        <v>541786</v>
       </c>
       <c r="R68" t="n">
-        <v>7063539</v>
+        <v>7063538</v>
       </c>
       <c r="S68" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -7578,9 +7568,19 @@
           <t>2025-12-16</t>
         </is>
       </c>
+      <c r="Z68" t="inlineStr">
+        <is>
+          <t>13:08</t>
+        </is>
+      </c>
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-12-16</t>
+        </is>
+      </c>
+      <c r="AB68" t="inlineStr">
+        <is>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7595,22 +7595,22 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>130152602</v>
+        <v>130153060</v>
       </c>
       <c r="B69" t="n">
-        <v>79183</v>
+        <v>57849</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7618,37 +7618,42 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>541973</v>
+        <v>541839</v>
       </c>
       <c r="R69" t="n">
-        <v>7063647</v>
+        <v>7063371</v>
       </c>
       <c r="S69" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -7675,19 +7680,9 @@
           <t>2025-12-16</t>
         </is>
       </c>
-      <c r="Z69" t="inlineStr">
-        <is>
-          <t>12:57</t>
-        </is>
-      </c>
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-12-16</t>
-        </is>
-      </c>
-      <c r="AB69" t="inlineStr">
-        <is>
-          <t>12:57</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7702,12 +7697,12 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
@@ -7717,7 +7712,7 @@
         <v>130153922</v>
       </c>
       <c r="B70" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7821,10 +7816,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>130153060</v>
+        <v>130152602</v>
       </c>
       <c r="B71" t="n">
-        <v>57823</v>
+        <v>79209</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7832,42 +7827,37 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P71" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>541839</v>
+        <v>541973</v>
       </c>
       <c r="R71" t="n">
-        <v>7063371</v>
+        <v>7063647</v>
       </c>
       <c r="S71" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -7894,9 +7884,19 @@
           <t>2025-12-16</t>
         </is>
       </c>
+      <c r="Z71" t="inlineStr">
+        <is>
+          <t>12:57</t>
+        </is>
+      </c>
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-12-16</t>
+        </is>
+      </c>
+      <c r="AB71" t="inlineStr">
+        <is>
+          <t>12:57</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7911,12 +7911,12 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
@@ -7926,7 +7926,7 @@
         <v>130154548</v>
       </c>
       <c r="B72" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8020,10 +8020,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>130153766</v>
+        <v>130152352</v>
       </c>
       <c r="B73" t="n">
-        <v>57826</v>
+        <v>80314</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8031,39 +8031,34 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
-      <c r="M73" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P73" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>541750</v>
+        <v>542077</v>
       </c>
       <c r="R73" t="n">
-        <v>7063250</v>
+        <v>7063744</v>
       </c>
       <c r="S73" t="n">
         <v>15</v>
@@ -8093,24 +8088,14 @@
           <t>2025-12-16</t>
         </is>
       </c>
-      <c r="Z73" t="inlineStr">
-        <is>
-          <t>14:00</t>
-        </is>
-      </c>
       <c r="AA73" t="inlineStr">
         <is>
           <t>2025-12-16</t>
         </is>
       </c>
-      <c r="AB73" t="inlineStr">
-        <is>
-          <t>14:00</t>
-        </is>
-      </c>
       <c r="AC73" t="inlineStr">
         <is>
-          <t>Ringhack på tall</t>
+          <t>På död björk</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8125,22 +8110,22 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>130153730</v>
+        <v>130153766</v>
       </c>
       <c r="B74" t="n">
-        <v>79183</v>
+        <v>57852</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8148,37 +8133,42 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P74" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>541768</v>
+        <v>541750</v>
       </c>
       <c r="R74" t="n">
-        <v>7063269</v>
+        <v>7063250</v>
       </c>
       <c r="S74" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8207,7 +8197,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8217,7 +8207,12 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8244,10 +8239,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>130152352</v>
+        <v>130153730</v>
       </c>
       <c r="B75" t="n">
-        <v>80288</v>
+        <v>79209</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8255,21 +8250,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8279,13 +8274,13 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>542077</v>
+        <v>541768</v>
       </c>
       <c r="R75" t="n">
-        <v>7063744</v>
+        <v>7063269</v>
       </c>
       <c r="S75" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8312,14 +8307,19 @@
           <t>2025-12-16</t>
         </is>
       </c>
+      <c r="Z75" t="inlineStr">
+        <is>
+          <t>13:58</t>
+        </is>
+      </c>
       <c r="AA75" t="inlineStr">
         <is>
           <t>2025-12-16</t>
         </is>
       </c>
-      <c r="AC75" t="inlineStr">
-        <is>
-          <t>På död björk</t>
+      <c r="AB75" t="inlineStr">
+        <is>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8334,61 +8334,57 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>130154401</v>
+        <v>130153074</v>
       </c>
       <c r="B76" t="n">
-        <v>98923</v>
+        <v>79209</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>541577</v>
+        <v>541807</v>
       </c>
       <c r="R76" t="n">
-        <v>7063340</v>
+        <v>7063402</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8420,7 +8416,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -8430,7 +8426,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>13:29</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8457,10 +8453,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>130153074</v>
+        <v>130153365</v>
       </c>
       <c r="B77" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8492,10 +8488,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>541807</v>
+        <v>541860</v>
       </c>
       <c r="R77" t="n">
-        <v>7063402</v>
+        <v>7063366</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8527,7 +8523,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -8537,7 +8533,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>13:29</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8564,10 +8560,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>130153365</v>
+        <v>130154525</v>
       </c>
       <c r="B78" t="n">
-        <v>79183</v>
+        <v>57852</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8575,34 +8571,39 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P78" t="inlineStr">
         <is>
           <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>541860</v>
+        <v>541592</v>
       </c>
       <c r="R78" t="n">
-        <v>7063366</v>
+        <v>7063490</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8634,7 +8635,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -8644,7 +8645,12 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>14:51</t>
+        </is>
+      </c>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>Ringhack på tall</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8671,38 +8677,37 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>130154525</v>
+        <v>130154401</v>
       </c>
       <c r="B79" t="n">
-        <v>57826</v>
+        <v>98949</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr"/>
-      <c r="M79" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>10</t>
         </is>
       </c>
       <c r="P79" t="inlineStr">
@@ -8711,10 +8716,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>541592</v>
+        <v>541577</v>
       </c>
       <c r="R79" t="n">
-        <v>7063490</v>
+        <v>7063340</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8746,7 +8751,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -8756,12 +8761,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>14:51</t>
-        </is>
-      </c>
-      <c r="AC79" t="inlineStr">
-        <is>
-          <t>Ringhack på tall</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8791,7 +8791,7 @@
         <v>130154569</v>
       </c>
       <c r="B80" t="n">
-        <v>57826</v>
+        <v>57852</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8908,7 +8908,7 @@
         <v>130151970</v>
       </c>
       <c r="B81" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9015,7 +9015,7 @@
         <v>130154023</v>
       </c>
       <c r="B82" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9112,7 +9112,7 @@
         <v>130154014</v>
       </c>
       <c r="B83" t="n">
-        <v>80323</v>
+        <v>80349</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9209,7 +9209,7 @@
         <v>130152372</v>
       </c>
       <c r="B84" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9306,7 +9306,7 @@
         <v>130153013</v>
       </c>
       <c r="B85" t="n">
-        <v>91695</v>
+        <v>91721</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9400,10 +9400,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>130153121</v>
+        <v>130153494</v>
       </c>
       <c r="B86" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9435,13 +9435,13 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>541827</v>
+        <v>541836</v>
       </c>
       <c r="R86" t="n">
-        <v>7063362</v>
+        <v>7063316</v>
       </c>
       <c r="S86" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -9470,7 +9470,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -9480,7 +9480,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>13:48</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9507,10 +9507,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>130153494</v>
+        <v>130153121</v>
       </c>
       <c r="B87" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9542,13 +9542,13 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>541836</v>
+        <v>541827</v>
       </c>
       <c r="R87" t="n">
-        <v>7063316</v>
+        <v>7063362</v>
       </c>
       <c r="S87" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -9577,7 +9577,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -9587,7 +9587,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>13:48</t>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9617,7 +9617,7 @@
         <v>130153689</v>
       </c>
       <c r="B88" t="n">
-        <v>57826</v>
+        <v>57852</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9734,7 +9734,7 @@
         <v>130152767</v>
       </c>
       <c r="B89" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9831,7 +9831,7 @@
         <v>130152347</v>
       </c>
       <c r="B90" t="n">
-        <v>80288</v>
+        <v>80314</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9938,7 +9938,7 @@
         <v>130154037</v>
       </c>
       <c r="B91" t="n">
-        <v>57826</v>
+        <v>57852</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10055,7 +10055,7 @@
         <v>130154192</v>
       </c>
       <c r="B92" t="n">
-        <v>57826</v>
+        <v>57852</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10162,7 +10162,7 @@
         <v>130228030</v>
       </c>
       <c r="B93" t="n">
-        <v>91944</v>
+        <v>91970</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10256,10 +10256,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>130228951</v>
+        <v>130227326</v>
       </c>
       <c r="B94" t="n">
-        <v>80288</v>
+        <v>92055</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10267,34 +10267,34 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Stamåsen, Stamåsen, Ång</t>
+          <t>Lill-Åsberget, Lill-Åsberget, Ång</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>541618</v>
+        <v>542243</v>
       </c>
       <c r="R94" t="n">
-        <v>7063274</v>
+        <v>7063987</v>
       </c>
       <c r="S94" t="n">
         <v>15</v>
@@ -10353,10 +10353,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>130227326</v>
+        <v>130228951</v>
       </c>
       <c r="B95" t="n">
-        <v>92029</v>
+        <v>80314</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10364,34 +10364,34 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Lill-Åsberget, Lill-Åsberget, Ång</t>
+          <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>542243</v>
+        <v>541618</v>
       </c>
       <c r="R95" t="n">
-        <v>7063987</v>
+        <v>7063274</v>
       </c>
       <c r="S95" t="n">
         <v>15</v>
@@ -10453,7 +10453,7 @@
         <v>130228013</v>
       </c>
       <c r="B96" t="n">
-        <v>92029</v>
+        <v>92055</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10550,7 +10550,7 @@
         <v>130228996</v>
       </c>
       <c r="B97" t="n">
-        <v>80288</v>
+        <v>80314</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10647,7 +10647,7 @@
         <v>130229019</v>
       </c>
       <c r="B98" t="n">
-        <v>80289</v>
+        <v>80315</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10744,7 +10744,7 @@
         <v>130229083</v>
       </c>
       <c r="B99" t="n">
-        <v>80289</v>
+        <v>80315</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10841,7 +10841,7 @@
         <v>130229726</v>
       </c>
       <c r="B100" t="n">
-        <v>57826</v>
+        <v>57852</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -10958,7 +10958,7 @@
         <v>130232684</v>
       </c>
       <c r="B101" t="n">
-        <v>80192</v>
+        <v>80218</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11055,7 +11055,7 @@
         <v>130228879</v>
       </c>
       <c r="B102" t="n">
-        <v>92184</v>
+        <v>92210</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -11152,7 +11152,7 @@
         <v>130227381</v>
       </c>
       <c r="B103" t="n">
-        <v>80288</v>
+        <v>80314</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11249,7 +11249,7 @@
         <v>130228071</v>
       </c>
       <c r="B104" t="n">
-        <v>91695</v>
+        <v>91721</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -11346,7 +11346,7 @@
         <v>130227624</v>
       </c>
       <c r="B105" t="n">
-        <v>57826</v>
+        <v>57852</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -11453,7 +11453,7 @@
         <v>130232597</v>
       </c>
       <c r="B106" t="n">
-        <v>57826</v>
+        <v>57852</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -11560,7 +11560,7 @@
         <v>130227321</v>
       </c>
       <c r="B107" t="n">
-        <v>91731</v>
+        <v>91757</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -11657,7 +11657,7 @@
         <v>130232341</v>
       </c>
       <c r="B108" t="n">
-        <v>57016</v>
+        <v>57042</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -11759,7 +11759,7 @@
         <v>130229089</v>
       </c>
       <c r="B109" t="n">
-        <v>80288</v>
+        <v>80314</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -11853,10 +11853,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>130228880</v>
+        <v>130227562</v>
       </c>
       <c r="B110" t="n">
-        <v>91731</v>
+        <v>57852</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -11864,34 +11864,39 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>Stamåsen, Stamåsen, Ång</t>
+          <t>Lill-Åsberget, Lill-Åsberget, Ång</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>541663</v>
+        <v>542148</v>
       </c>
       <c r="R110" t="n">
-        <v>7063324</v>
+        <v>7063819</v>
       </c>
       <c r="S110" t="n">
         <v>15</v>
@@ -11924,6 +11929,11 @@
       <c r="AA110" t="inlineStr">
         <is>
           <t>2025-12-20</t>
+        </is>
+      </c>
+      <c r="AC110" t="inlineStr">
+        <is>
+          <t>Ringhack, tall</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -11950,10 +11960,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>130227562</v>
+        <v>130228880</v>
       </c>
       <c r="B111" t="n">
-        <v>57826</v>
+        <v>91757</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -11961,39 +11971,34 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
-      <c r="M111" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>Lill-Åsberget, Lill-Åsberget, Ång</t>
+          <t>Stamåsen, Stamåsen, Ång</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>542148</v>
+        <v>541663</v>
       </c>
       <c r="R111" t="n">
-        <v>7063819</v>
+        <v>7063324</v>
       </c>
       <c r="S111" t="n">
         <v>15</v>
@@ -12026,11 +12031,6 @@
       <c r="AA111" t="inlineStr">
         <is>
           <t>2025-12-20</t>
-        </is>
-      </c>
-      <c r="AC111" t="inlineStr">
-        <is>
-          <t>Ringhack, tall</t>
         </is>
       </c>
       <c r="AD111" t="b">
